--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D344"/>
+  <dimension ref="A1:D353"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1240</v>
+        <v>1303</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>996</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4">
@@ -461,13 +461,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
@@ -489,7 +489,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -503,7 +503,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -517,13 +517,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B9">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="10">
@@ -531,13 +531,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B10">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -545,13 +545,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B11">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -590,10 +590,10 @@
         <v>39</v>
       </c>
       <c r="C14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -640,30 +640,30 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>kaua_limamma</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B18">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>mmmarc20</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B19">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -671,7 +671,7 @@
         <v>combintel</v>
       </c>
       <c r="B20">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -696,30 +696,30 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>cleyton_jesuss</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B22">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>121</v>
       </c>
       <c r="D22">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>god.motivacao</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B23">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C23">
-        <v>117</v>
+        <v>4</v>
       </c>
       <c r="D23">
-        <v>34</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24">
@@ -1228,41 +1228,41 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ravenrodriguez___</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B60">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C60">
+        <v>8</v>
+      </c>
+      <c r="D60">
         <v>3</v>
-      </c>
-      <c r="D60">
-        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -1270,16 +1270,16 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>marcos_tailandess</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2026,13 +2026,13 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>treinaadorrafael</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117">
         <v>0</v>
@@ -2040,21 +2040,21 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>benjafloripabjj</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B118">
         <v>1</v>
       </c>
       <c r="C118">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,13 +2082,13 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121">
         <v>0</v>
@@ -2096,13 +2096,13 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>fagnerosensei</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>030sami</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -2124,21 +2124,21 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>guiiviieira_</v>
+        <v>030sami</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,21 +2152,21 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>cshigueo</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>emerson_lucaszx</v>
+        <v>cshigueo</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>danni_goncalves12</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>mttsm._</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>andrealvess02</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>gildojiu</v>
+        <v>mttsm._</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>kawannsennast</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>yurimartins1_</v>
+        <v>gildojiu</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>matheusteodoro_1</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,13 +2306,13 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>kael_lyto</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>kalindrafaria</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,27 +2334,27 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>cristianpsicologo</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B139">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C139">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D139">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>juanx.pontes</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B140">
         <v>1</v>
       </c>
       <c r="C140">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -2362,21 +2362,21 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>select_from_joao</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C141">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>yeslifeacademia</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ojaimerocha</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,13 +2404,13 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>tonketjudes</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -2418,13 +2418,13 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>_eliasffx</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -2432,21 +2432,21 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>pdfiv</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>mariaraimundad940</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>gabesantos.13</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>euvitormirandaa</v>
+        <v>pdfiv</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>thompsonborralho</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>frankikolimabjj</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>alerrandrojj</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>anahangelica</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>minotaurinho</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>lara.rpr</v>
+        <v>anahangelica</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>codasqueves</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>yan_touro.7766</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>carolinne.xwp</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>davicorbella</v>
+        <v>codasqueves</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>artemio_bjj</v>
+        <v>davicorbella</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>katiaecarreraf</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>geraldocnetomma</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,21 +2712,21 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>pedro_pavin_</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C166">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D166">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>xavyeroficial</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>maryanagandra</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,21 +2754,21 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>eliandropires</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>charlesanthony2466</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>draanapaulaponceano</v>
+        <v>eliandropires</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>saj_photo_miami</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>alternativaremocoes</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>benivalentinn</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>navarro_9430</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>_puroosso88</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>_rayysp</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>cami.terra_</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>gabicardoson</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>martta.mariah</v>
+        <v>_rayysp</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>wlt_miguel</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>jaonevesz</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>pietroshz</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>___neller</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>_bety_marcal</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>guilhermeefelix__</v>
+        <v>pietroshz</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>pativinisf</v>
+        <v>___neller</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>judadany</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>andre_alcausa</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>_fernunes</v>
+        <v>pativinisf</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>aloirmarcal</v>
+        <v>judadany</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>gilberto_7606</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>_fernunes</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>flazuera14</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>camii_bonfim</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>danlouiz.jj</v>
+        <v>flazuera14</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>gabriel_trevelin</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>y.arthur_01</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>muricunha</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>victorhenriquebjj</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>_lsanchess_</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>__bielgg</v>
+        <v>muricunha</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>mr__rlk01</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>vitor_buck</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>fran.ruys</v>
+        <v>__bielgg</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>wesley_bjjvc</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>sambagabrieloficial</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>peacegrappler</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>aliferpaulo_</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>_alcantara.bru</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>cesar.boanerges</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>alexandreconsentino</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,13 +3454,13 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>rafaela_duaartee</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C219">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D219">
         <v>0</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>andre.legendre.10</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,13 +3496,13 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>phillipe.harry</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C222">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>andrejetx</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>leandro_motiv4</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>olga.oliveira013</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>andrejetx</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>leosacraa</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>gutocriativo</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>igorfso_</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>leosacraa</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>lay_roqs</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>bigjota.artist</v>
+        <v>igorfso_</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>mth_fernandes031</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>turmanmma</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>gustavomohallem</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>atlta.marc0s</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>arturbambam</v>
+        <v>turmanmma</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,13 +3748,13 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>marinealcausa</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C240">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D240">
         <v>0</v>
@@ -3762,13 +3762,13 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>emersonriosmma</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B241">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C241">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D241">
         <v>0</v>
@@ -3776,41 +3776,41 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>luizcosta_mma</v>
+        <v>arturbambam</v>
       </c>
       <c r="B242">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C242">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D242">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>giulia.fasolato</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B243">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C243">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D243">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>michelle_mirele</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B244">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C244">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D244">
         <v>0</v>
@@ -3818,13 +3818,13 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>danielfranzesilva</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C245">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D245">
         <v>0</v>
@@ -3832,35 +3832,35 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>ednilsonkaicai</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B246">
         <v>0</v>
       </c>
       <c r="C246">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D246">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B247">
         <v>0</v>
       </c>
       <c r="C247">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D247">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>dayanaa1511</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B248">
         <v>0</v>
@@ -3869,54 +3869,54 @@
         <v>2</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>vanessamelomma</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B249">
         <v>0</v>
       </c>
       <c r="C249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D249">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>leonardopateira</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B250">
         <v>0</v>
       </c>
       <c r="C250">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D250">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>rahikikhalid</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B251">
         <v>0</v>
       </c>
       <c r="C251">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D251">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>manumito.oficial</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3925,12 +3925,12 @@
         <v>2</v>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>carlosnoelblack</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3939,12 +3939,12 @@
         <v>2</v>
       </c>
       <c r="D253">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -3953,12 +3953,12 @@
         <v>2</v>
       </c>
       <c r="D254">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>lokomemo_protetores</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>coutz11</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -3986,21 +3986,21 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>orlando_alfa09</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B257">
         <v>0</v>
       </c>
       <c r="C257">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D257">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>vitorshowman</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>4lissson</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B259">
         <v>0</v>
@@ -4028,21 +4028,21 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>danilofernandescf</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B260">
         <v>0</v>
       </c>
       <c r="C260">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D260">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>bryandazuera</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>ommariotti</v>
+        <v>coutz11</v>
       </c>
       <c r="B262">
         <v>0</v>
@@ -4070,41 +4070,41 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>brodschack_</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B263">
         <v>0</v>
       </c>
       <c r="C263">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D263">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>_vpft</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B264">
         <v>0</v>
       </c>
       <c r="C264">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D264">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>4lissson</v>
       </c>
       <c r="B265">
         <v>0</v>
       </c>
       <c r="C265">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D265">
         <v>0</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>helenaseveribjj</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4121,12 +4121,12 @@
         <v>1</v>
       </c>
       <c r="D266">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>_kainanlima</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B267">
         <v>0</v>
@@ -4135,12 +4135,12 @@
         <v>1</v>
       </c>
       <c r="D267">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>jimmy_indioap</v>
+        <v>ommariotti</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -4149,12 +4149,12 @@
         <v>1</v>
       </c>
       <c r="D268">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>omar_alneaimi</v>
+        <v>brodschack_</v>
       </c>
       <c r="B269">
         <v>0</v>
@@ -4163,12 +4163,12 @@
         <v>1</v>
       </c>
       <c r="D269">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>victor_brunopersonal</v>
+        <v>_vpft</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4177,12 +4177,12 @@
         <v>1</v>
       </c>
       <c r="D270">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>motumbo_team</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4191,12 +4191,12 @@
         <v>1</v>
       </c>
       <c r="D271">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>vanemessina</v>
+        <v>janjaovix</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4205,12 +4205,12 @@
         <v>1</v>
       </c>
       <c r="D272">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>dadwillians</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4219,12 +4219,12 @@
         <v>1</v>
       </c>
       <c r="D273">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>thalytabjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>esteticaluharruda</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>chubotaru_lilu</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>eusoufernandosaito</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>dandraco_</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>sejamotivadorofc</v>
+        <v>vanemessina</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>tpapereira</v>
+        <v>dadwillians</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>kfcampeoes</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>herrickmarinho</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>rafaelcmjj</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>cristianomarcello</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>_gabrielpego</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>taylor_71kg</v>
+        <v>dandraco_</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>doraasivla</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>pe.mirandas</v>
+        <v>tpapereira</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>leaoanaalice</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>caioparangole</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>sabrinaalsilva</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>eglaudiomma</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>strong_stg_oficial</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>ricardotofanello</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>taporondebruno</v>
+        <v>doraasivla</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>anamatias.m</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>claudio_marchese_7</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>1000ton_n</v>
+        <v>caioparangole</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>paulo.titoo</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>vitorcosta_mma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>couragemma</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>romulerasilva</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>edergama.mma</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>alineanne_</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>julckreis</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>andreza.thais.1</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>benicius_edu</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>michele_mixa</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>joaolauar_</v>
+        <v>couragemma</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>igorbrasileiro01</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>felipeocalmon</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>rejr_mma</v>
+        <v>alineanne_</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>deivssonmanin</v>
+        <v>julckreis</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>andrey_m_s_</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>vidaldanin</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>barbaracontadora</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>natalves5</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>boradepodcastoficial</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>audizioandrade</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>isadoragolimpio</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>dudu.acabamentos</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>katlembrenda</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>aline.amaral21</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>tamysregina</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>guilhermews1994</v>
+        <v>natalves5</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>percepcar</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>kevin.mota95</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>_marcos_.71</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B334">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>douglas_vitor8</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B335">
         <v>0</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>raulcarvalho1010</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>roginbrito</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>meirelesmma</v>
+        <v>tamysregina</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>dvlucc2k26_</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>armysenju</v>
+        <v>percepcar</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>f.ostini</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>fher.nando_</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,28 +5204,154 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
+        <v>douglas_vitor8</v>
+      </c>
+      <c r="B344">
+        <v>0</v>
+      </c>
+      <c r="C344">
+        <v>1</v>
+      </c>
+      <c r="D344">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>gemeaslauraebrenda</v>
+      </c>
+      <c r="B345">
+        <v>0</v>
+      </c>
+      <c r="C345">
+        <v>1</v>
+      </c>
+      <c r="D345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>raulcarvalho1010</v>
+      </c>
+      <c r="B346">
+        <v>0</v>
+      </c>
+      <c r="C346">
+        <v>1</v>
+      </c>
+      <c r="D346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>roginbrito</v>
+      </c>
+      <c r="B347">
+        <v>0</v>
+      </c>
+      <c r="C347">
+        <v>1</v>
+      </c>
+      <c r="D347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>meirelesmma</v>
+      </c>
+      <c r="B348">
+        <v>0</v>
+      </c>
+      <c r="C348">
+        <v>1</v>
+      </c>
+      <c r="D348">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B349">
+        <v>0</v>
+      </c>
+      <c r="C349">
+        <v>1</v>
+      </c>
+      <c r="D349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>armysenju</v>
+      </c>
+      <c r="B350">
+        <v>0</v>
+      </c>
+      <c r="C350">
+        <v>1</v>
+      </c>
+      <c r="D350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>f.ostini</v>
+      </c>
+      <c r="B351">
+        <v>0</v>
+      </c>
+      <c r="C351">
+        <v>1</v>
+      </c>
+      <c r="D351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>fher.nando_</v>
+      </c>
+      <c r="B352">
+        <v>0</v>
+      </c>
+      <c r="C352">
+        <v>1</v>
+      </c>
+      <c r="D352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
         <v>cristiannogueira.vtt</v>
       </c>
-      <c r="B344">
-        <v>0</v>
-      </c>
-      <c r="C344">
-        <v>1</v>
-      </c>
-      <c r="D344">
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+      <c r="D353">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D344"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D353"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D52"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5246,13 +5372,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>268</v>
+        <v>331</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>263</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3">
@@ -5260,41 +5386,41 @@
         <v>hugo7jj</v>
       </c>
       <c r="B3">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B4">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>rm.nicki</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
@@ -5302,7 +5428,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B6">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -5316,7 +5442,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -5344,13 +5470,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B9">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -5386,13 +5512,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B12">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
         <v>9</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -5417,10 +5543,10 @@
         <v>3</v>
       </c>
       <c r="C14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -5467,24 +5593,24 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>_beegomes_</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>karen.ottoni</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -5495,10 +5621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>alfredo_miras</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -5509,7 +5635,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mmmarc20</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -5523,7 +5649,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>badboykillermma</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -5537,7 +5663,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>gra_jpereira</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -5551,7 +5677,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ninjatheorist</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -5565,16 +5691,16 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>god.motivacao</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -5593,10 +5719,10 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>livreseseguras</v>
+        <v>combintel</v>
       </c>
       <c r="B27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -5607,7 +5733,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ronemayanmorais</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -5621,7 +5747,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>pedrinhosbjj</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -5635,7 +5761,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>combintel</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -5663,10 +5789,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>kalindrafaria</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -5677,7 +5803,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>enzoferrari680</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -5686,12 +5812,12 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>gustavomohallem</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -5705,21 +5831,21 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>atlta.marc0s</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>arturbambam</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -5733,41 +5859,41 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>tabajaraharu</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>eliassilverio</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>benjafloripabjj</v>
+        <v>arturbambam</v>
       </c>
       <c r="B39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -5775,13 +5901,13 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>f.ostini</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -5789,13 +5915,13 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>marcos_tailandess</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -5803,13 +5929,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>fher.nando_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -5817,21 +5943,147 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
+        <v>marcos_tailandess</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>tabajaraharu</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>eliassilverio</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>izabeldelfino_</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>janjaovix</v>
+      </c>
+      <c r="B47">
+        <v>0</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>guerreirammaofc</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>benjafloripabjj</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>f.ostini</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>fher.nando_</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
         <v>cristiannogueira.vtt</v>
       </c>
-      <c r="B43">
-        <v>0</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43">
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D43"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D353"/>
+  <dimension ref="A1:D359"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1303</v>
+        <v>1346</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>1055</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4">
@@ -489,7 +489,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C7">
         <v>7</v>
@@ -503,7 +503,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -517,13 +517,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B9">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10">
@@ -531,13 +531,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B10">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -545,7 +545,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B11">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -587,69 +587,69 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B14">
+        <v>40</v>
+      </c>
+      <c r="C14">
+        <v>34</v>
+      </c>
+      <c r="D14">
         <v>39</v>
-      </c>
-      <c r="C14">
-        <v>33</v>
-      </c>
-      <c r="D14">
-        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ronemayanmorais</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C15">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>bellsouza816</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B16">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>erik_.mma</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B17">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>mmmarc20</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B18">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -671,13 +671,13 @@
         <v>combintel</v>
       </c>
       <c r="B20">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -702,7 +702,7 @@
         <v>8</v>
       </c>
       <c r="C22">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D22">
         <v>38</v>
@@ -1284,24 +1284,24 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>mah__vergueiro</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B64">
         <v>3</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B65">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -1312,7 +1312,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B66">
         <v>4</v>
@@ -1326,21 +1326,21 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>ninjatheorist</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>shawlin13oficial</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B68">
         <v>2</v>
@@ -1349,12 +1349,12 @@
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>dogodoyfoto</v>
+        <v>febrancatti</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -1410,27 +1410,27 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>reifernandes</v>
+        <v>z.proddd</v>
       </c>
       <c r="B73">
         <v>2</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>daniel_dias_214</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B74">
         <v>2</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -1438,97 +1438,97 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>reifernandes</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>alexsandra_kairos</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>f.luan_11</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>vitorpetrino</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>jcchagas_</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>anderson.logan.35</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>marifferreirac</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B81">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81">
         <v>1</v>
@@ -1536,77 +1536,77 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>odeivisoncardoso</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B82">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C82">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>maca.mariotti</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B83">
         <v>1</v>
       </c>
       <c r="C83">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D83">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>adriano.trator</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>s__simone__</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D85">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>kaua_limaofc</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>clouddhidden</v>
+        <v>s__simone__</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -1620,35 +1620,35 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>lucascardosol__</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>ruangzk</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>livreseseguras</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -1662,41 +1662,41 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>ismaeldaniell</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>douglasipvr_mma</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D93">
         <v>2</v>
@@ -1704,13 +1704,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>tassiogiloficial</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B94">
         <v>2</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -1718,21 +1718,21 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>vnciuss__df</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>jhee_dias</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B96">
         <v>2</v>
@@ -1746,49 +1746,49 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>albertoleandromoco</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>pauloserrati</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>fredoctmma</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -1797,26 +1797,26 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>diegopaivajj</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fabaotipster</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -1830,35 +1830,35 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>joegam3r</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>mimuniz.bjj</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>orafao1</v>
+        <v>joegam3r</v>
       </c>
       <c r="B105">
         <v>2</v>
@@ -1872,7 +1872,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>fabi.godooy</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B106">
         <v>2</v>
@@ -1886,35 +1886,35 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>leobahiamma</v>
+        <v>orafao1</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107">
         <v>0</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108">
         <v>0</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -1928,7 +1928,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>heltoncm2002</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>raelduraes</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>mineirinho_jj</v>
+        <v>raelduraes</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>graalino</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>lopesbrunao</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>pedrinhosbjj</v>
+        <v>graalino</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,21 +2026,21 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>marc0s.azv</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117">
         <v>0</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,35 +2054,35 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>treinaadorrafael</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B119">
         <v>1</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -2124,13 +2124,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>fagnerosensei</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -2138,13 +2138,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>030sami</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -2152,21 +2152,21 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>guiiviieira_</v>
+        <v>030sami</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>kalindrafaria</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B140">
         <v>1</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -2362,35 +2362,35 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>cristianpsicologo</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B141">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C141">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D141">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C142">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,35 +2432,35 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>antonioemanuel.13</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D146">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>tonketjudes</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,35 +2754,35 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C169">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D169">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>aliferpaulo_</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>_alcantara.bru</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,13 +3496,13 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B222">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C222">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D222">
         <v>0</v>
@@ -3510,13 +3510,13 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C223">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D223">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>gustavomohallem</v>
+        <v>turmanmma</v>
       </c>
       <c r="B240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>atlta.marc0s</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>arturbambam</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>hermaan10_</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,13 +3832,13 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>marinealcausa</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C246">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D246">
         <v>0</v>
@@ -3846,13 +3846,13 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>emersonriosmma</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B247">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C247">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D247">
         <v>0</v>
@@ -3860,41 +3860,41 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>luizcosta_mma</v>
+        <v>markakasocks</v>
       </c>
       <c r="B248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C248">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D248">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>giulia.fasolato</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C249">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D249">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>michelle_mirele</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B250">
         <v>0</v>
       </c>
       <c r="C250">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D250">
         <v>0</v>
@@ -3902,13 +3902,13 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>danielfranzesilva</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B251">
         <v>0</v>
       </c>
       <c r="C251">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D251">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>ednilsonkaicai</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B252">
         <v>0</v>
@@ -3925,12 +3925,12 @@
         <v>2</v>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B253">
         <v>0</v>
@@ -3939,46 +3939,46 @@
         <v>2</v>
       </c>
       <c r="D253">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>dayanaa1511</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B254">
         <v>0</v>
       </c>
       <c r="C254">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D254">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>vanessamelomma</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B255">
         <v>0</v>
       </c>
       <c r="C255">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D255">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>leonardopateira</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B256">
         <v>0</v>
       </c>
       <c r="C256">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D256">
         <v>1</v>
@@ -3986,13 +3986,13 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>rahikikhalid</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B257">
         <v>0</v>
       </c>
       <c r="C257">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D257">
         <v>1</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>manumito.oficial</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B258">
         <v>0</v>
@@ -4009,40 +4009,40 @@
         <v>2</v>
       </c>
       <c r="D258">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>carlosnoelblack</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B259">
         <v>0</v>
       </c>
       <c r="C259">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D259">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B260">
         <v>0</v>
       </c>
       <c r="C260">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D260">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>lokomemo_protetores</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -4056,21 +4056,21 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>coutz11</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B262">
         <v>0</v>
       </c>
       <c r="C262">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D262">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>orlando_alfa09</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B263">
         <v>0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>vitorshowman</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B264">
         <v>0</v>
@@ -4098,21 +4098,21 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>4lissson</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B265">
         <v>0</v>
       </c>
       <c r="C265">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D265">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>danilofernandescf</v>
+        <v>coutz11</v>
       </c>
       <c r="B266">
         <v>0</v>
@@ -4126,49 +4126,49 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>bryandazuera</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B267">
         <v>0</v>
       </c>
       <c r="C267">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D267">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>ommariotti</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B268">
         <v>0</v>
       </c>
       <c r="C268">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D268">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>brodschack_</v>
+        <v>4lissson</v>
       </c>
       <c r="B269">
         <v>0</v>
       </c>
       <c r="C269">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D269">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>_vpft</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B270">
         <v>0</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>izabeldelfino_</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B271">
         <v>0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>janjaovix</v>
+        <v>ommariotti</v>
       </c>
       <c r="B272">
         <v>0</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>guerreirammaofc</v>
+        <v>brodschack_</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4233,12 +4233,12 @@
         <v>1</v>
       </c>
       <c r="D274">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>helenaseveribjj</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B275">
         <v>0</v>
@@ -4247,12 +4247,12 @@
         <v>1</v>
       </c>
       <c r="D275">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>_kainanlima</v>
+        <v>janjaovix</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -4261,12 +4261,12 @@
         <v>1</v>
       </c>
       <c r="D276">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>jimmy_indioap</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B277">
         <v>0</v>
@@ -4275,12 +4275,12 @@
         <v>1</v>
       </c>
       <c r="D277">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>omar_alneaimi</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B278">
         <v>0</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>victor_brunopersonal</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>motumbo_team</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>vanemessina</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>dadwillians</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>thalytabjj</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>esteticaluharruda</v>
+        <v>vanemessina</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>chubotaru_lilu</v>
+        <v>dadwillians</v>
       </c>
       <c r="B286">
         <v>0</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>eusoufernandosaito</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>dandraco_</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>sejamotivadorofc</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>tpapereira</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B291">
         <v>0</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>kfcampeoes</v>
+        <v>dandraco_</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>herrickmarinho</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>rafaelcmjj</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>cristianomarcello</v>
+        <v>tpapereira</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>_gabrielpego</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>taylor_71kg</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>doraasivla</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>pe.mirandas</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>leaoanaalice</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>caioparangole</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>sabrinaalsilva</v>
+        <v>doraasivla</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>eglaudiomma</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>strong_stg_oficial</v>
+        <v>caioparangole</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>ricardotofanello</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>taporondebruno</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>anamatias.m</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>claudio_marchese_7</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>1000ton_n</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>paulo.titoo</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>vitorcosta_mma</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>couragemma</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>romulerasilva</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>edergama.mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>alineanne_</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>julckreis</v>
+        <v>couragemma</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>andreza.thais.1</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>benicius_edu</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>alineanne_</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>michele_mixa</v>
+        <v>julckreis</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>joaolauar_</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>igorbrasileiro01</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>felipeocalmon</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>rejr_mma</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>deivssonmanin</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>andrey_m_s_</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>vidaldanin</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>barbaracontadora</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>natalves5</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>boradepodcastoficial</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>audizioandrade</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B334">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>isadoragolimpio</v>
+        <v>natalves5</v>
       </c>
       <c r="B335">
         <v>0</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>dudu.acabamentos</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>katlembrenda</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>aline.amaral21</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>tamysregina</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>guilhermews1994</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>percepcar</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>kevin.mota95</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>_marcos_.71</v>
+        <v>tamysregina</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>douglas_vitor8</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B344">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>percepcar</v>
       </c>
       <c r="B345">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>raulcarvalho1010</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>roginbrito</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>meirelesmma</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>dvlucc2k26_</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B349">
         <v>0</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>armysenju</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B350">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>f.ostini</v>
+        <v>roginbrito</v>
       </c>
       <c r="B351">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>fher.nando_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B352">
         <v>0</v>
@@ -5330,28 +5330,112 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B353">
+        <v>0</v>
+      </c>
+      <c r="C353">
+        <v>1</v>
+      </c>
+      <c r="D353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>armysenju</v>
+      </c>
+      <c r="B354">
+        <v>0</v>
+      </c>
+      <c r="C354">
+        <v>1</v>
+      </c>
+      <c r="D354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>f.ostini</v>
+      </c>
+      <c r="B355">
+        <v>0</v>
+      </c>
+      <c r="C355">
+        <v>1</v>
+      </c>
+      <c r="D355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>fher.nando_</v>
+      </c>
+      <c r="B356">
+        <v>0</v>
+      </c>
+      <c r="C356">
+        <v>1</v>
+      </c>
+      <c r="D356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
         <v>cristiannogueira.vtt</v>
       </c>
-      <c r="B353">
-        <v>0</v>
-      </c>
-      <c r="C353">
-        <v>1</v>
-      </c>
-      <c r="D353">
+      <c r="B357">
+        <v>0</v>
+      </c>
+      <c r="C357">
+        <v>1</v>
+      </c>
+      <c r="D357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>bastazinifilho</v>
+      </c>
+      <c r="B358">
+        <v>0</v>
+      </c>
+      <c r="C358">
+        <v>1</v>
+      </c>
+      <c r="D358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>pammygaryo</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>1</v>
+      </c>
+      <c r="D359">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D353"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D359"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D59"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5372,13 +5456,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>331</v>
+        <v>374</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>322</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3">
@@ -5386,7 +5470,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B3">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -5400,41 +5484,41 @@
         <v>rm.nicki</v>
       </c>
       <c r="B4">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B5">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>rpsantos_mma</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -5442,7 +5526,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -5470,13 +5554,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B9">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
@@ -5495,21 +5579,21 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>anaaj_camargo</v>
+        <v>pg_grappling</v>
       </c>
       <c r="B11">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>pg_grappling</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B12">
         <v>12</v>
@@ -5523,13 +5607,13 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>cleyton_jesuss</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>7</v>
@@ -5537,80 +5621,80 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ryangandraufc</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>aline.r15</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>irmandadefightteam</v>
+        <v>combintel</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>excelentfightcompetition</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>god.motivacao</v>
+        <v>aline.r15</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C18">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>mmmarc20</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B19">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -5621,10 +5705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>_beegomes_</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -5635,10 +5719,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>karen.ottoni</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -5649,7 +5733,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>alfredo_miras</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B22">
         <v>2</v>
@@ -5663,7 +5747,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>badboykillermma</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -5677,13 +5761,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>gra_jpereira</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -5691,7 +5775,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ninjatheorist</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -5705,7 +5789,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>maxgandra</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -5714,12 +5798,12 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>combintel</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -5728,15 +5812,15 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>livreseseguras</v>
+        <v>z.proddd</v>
       </c>
       <c r="B28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -5747,10 +5831,10 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ronemayanmorais</v>
+        <v>maxgandra</v>
       </c>
       <c r="B29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -5761,7 +5845,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>pedrinhosbjj</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -5775,7 +5859,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>pedromadeira.s</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -5789,21 +5873,21 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>marc0s.azv</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -5817,7 +5901,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>kalindrafaria</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -5826,40 +5910,40 @@
         <v>0</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>antonioemanuel.13</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C35">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>enzoferrari680</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>gustavomohallem</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -5873,7 +5957,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>atlta.marc0s</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -5887,7 +5971,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -5901,7 +5985,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>arturbambam</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -5915,7 +5999,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>hermaan10_</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -5929,7 +6013,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -5943,69 +6027,69 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>marcos_tailandess</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>tabajaraharu</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>eliassilverio</v>
+        <v>markakasocks</v>
       </c>
       <c r="B45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>izabeldelfino_</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>janjaovix</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B47">
         <v>0</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -6013,7 +6097,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>guerreirammaofc</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -6027,7 +6111,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>benjafloripabjj</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -6036,12 +6120,12 @@
         <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>f.ostini</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -6050,12 +6134,12 @@
         <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>fher.nando_</v>
+        <v>janjaovix</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -6064,26 +6148,124 @@
         <v>1</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
+        <v>guerreirammaofc</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>benjafloripabjj</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>f.ostini</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>fher.nando_</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>1</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
         <v>cristiannogueira.vtt</v>
       </c>
-      <c r="B52">
-        <v>0</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52">
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
+        <v>bastazinifilho</v>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>luanlacerda_ufc_61kg</v>
+      </c>
+      <c r="B58">
+        <v>0</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>pammygaryo</v>
+      </c>
+      <c r="B59">
+        <v>0</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D59"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D359"/>
+  <dimension ref="A1:D398"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1346</v>
+        <v>1422</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>1095</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4">
@@ -461,41 +461,41 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B5">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C5">
         <v>9</v>
       </c>
       <c r="D5">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>pedr00jj</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B6">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D6">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>pablofiorindi</v>
+        <v>pedr00jj</v>
       </c>
       <c r="B7">
         <v>157</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D7">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -601,13 +601,13 @@
         <v>mmmarc20</v>
       </c>
       <c r="B15">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
@@ -615,7 +615,7 @@
         <v>ronemayanmorais</v>
       </c>
       <c r="B16">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -671,13 +671,13 @@
         <v>combintel</v>
       </c>
       <c r="B20">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C20">
         <v>1</v>
       </c>
       <c r="D20">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -780,44 +780,44 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B28">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>pedromadeira.s</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B29">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>eliassilverio</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
@@ -825,7 +825,7 @@
         <v>cjrnavalha</v>
       </c>
       <c r="B31">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -850,35 +850,35 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>_beegomes_</v>
+        <v>maxgandra</v>
       </c>
       <c r="B33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>maxgandra</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>tawanregismma</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B35">
         <v>7</v>
@@ -887,18 +887,18 @@
         <v>1</v>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>karen.ottoni</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B36">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -906,167 +906,167 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>rrafaelins</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B37">
+        <v>5</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
         <v>4</v>
-      </c>
-      <c r="C37">
-        <v>4</v>
-      </c>
-      <c r="D37">
-        <v>5</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>italothearcher</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B39">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>vndcardoso</v>
+        <v>italothearcher</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>juniordiasmma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B41">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>badboykillermma</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>gdazuera</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C43">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>enzoferrari680</v>
+        <v>gdazuera</v>
       </c>
       <c r="B44">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B45">
         <v>6</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B46">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>eolucasrosa</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>dagestan0920</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B48">
         <v>5</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -1074,13 +1074,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C49">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -1088,27 +1088,27 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>_.maduoliveira_</v>
+        <v>paxlucta</v>
       </c>
       <c r="B50">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D50">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B51">
         <v>3</v>
       </c>
       <c r="C51">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -1116,21 +1116,21 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>glm.barbosa</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>excelentfightcompetition</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B53">
         <v>2</v>
@@ -1144,27 +1144,27 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>marcelogabrielmma</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B55">
         <v>3</v>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D55">
         <v>3</v>
@@ -1172,111 +1172,111 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56">
+        <v>4</v>
+      </c>
+      <c r="D56">
         <v>3</v>
-      </c>
-      <c r="D56">
-        <v>5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>gabrielsouzamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B57">
         <v>2</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D57">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B58">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>alfredo_miras</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>marcos_tailandess</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ravenrodriguez___</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B61">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C61">
+        <v>8</v>
+      </c>
+      <c r="D61">
         <v>3</v>
-      </c>
-      <c r="D61">
-        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -1284,16 +1284,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>marc0s.azv</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -1984,21 +1984,21 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>pedrinhosbjj</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,13 +2068,13 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B120">
         <v>1</v>
       </c>
       <c r="C120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D120">
         <v>1</v>
@@ -2082,27 +2082,27 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>treinaadorrafael</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>benjafloripabjj</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -2110,13 +2110,13 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>fernando.mma</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -2124,13 +2124,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -2138,13 +2138,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,13 +2166,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>guiiviieira_</v>
+        <v>030sami</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B140">
         <v>1</v>
       </c>
       <c r="C140">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -2362,13 +2362,13 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>kalindrafaria</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -2376,27 +2376,27 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>cristianpsicologo</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C142">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D142">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>juanx.pontes</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -2404,13 +2404,13 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>select_from_joao</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -2418,13 +2418,13 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>yeslifeacademia</v>
+        <v>andreibjj</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -2432,41 +2432,41 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ojaimerocha</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C146">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>antonioemanuel.13</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D147">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>tonketjudes</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B148">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -2474,13 +2474,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>_eliasffx</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B149">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -2488,13 +2488,13 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>pdfiv</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B150">
         <v>1</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -2502,27 +2502,27 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>mariaraimundad940</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D151">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>gabesantos.13</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B152">
         <v>1</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -2530,13 +2530,13 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>euvitormirandaa</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B153">
         <v>1</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>thompsonborralho</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>frankikolimabjj</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>alerrandrojj</v>
+        <v>pdfiv</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>anahangelica</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>minotaurinho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>lara.rpr</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>codasqueves</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>yan_touro.7766</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>carolinne.xwp</v>
+        <v>anahangelica</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>davicorbella</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>artemio_bjj</v>
+        <v>codasqueves</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>katiaecarreraf</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>geraldocnetomma</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,21 +2768,21 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>pedro_pavin_</v>
+        <v>davicorbella</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C170">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D170">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>xavyeroficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>maryanagandra</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>eliandropires</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>charlesanthony2466</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,21 +2852,21 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>draanapaulaponceano</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>saj_photo_miami</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>alternativaremocoes</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>benivalentinn</v>
+        <v>eliandropires</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>navarro_9430</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>_puroosso88</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>_rayysp</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>cami.terra_</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>gabicardoson</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>martta.mariah</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>wlt_miguel</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>jaonevesz</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>pietroshz</v>
+        <v>_rayysp</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>___neller</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>_bety_marcal</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>guilhermeefelix__</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>pativinisf</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>judadany</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>andre_alcausa</v>
+        <v>pietroshz</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>_fernunes</v>
+        <v>___neller</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>aloirmarcal</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>gilberto_7606</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>pativinisf</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>flazuera14</v>
+        <v>judadany</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>camii_bonfim</v>
+        <v>_fernunes</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>danlouiz.jj</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>gabriel_trevelin</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>y.arthur_01</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>muricunha</v>
+        <v>flazuera14</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>victorhenriquebjj</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>_lsanchess_</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>__bielgg</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>mr__rlk01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>vitor_buck</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>fran.ruys</v>
+        <v>muricunha</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>wesley_bjjvc</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>sambagabrieloficial</v>
+        <v>__bielgg</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>peacegrappler</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>aliferpaulo_</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>_alcantara.bru</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>cesar.boanerges</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>alexandreconsentino</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,13 +3510,13 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>rafaela_duaartee</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B223">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C223">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D223">
         <v>0</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>andre.legendre.10</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>phillipe.harry</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>andrejetx</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,13 +3580,13 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>leandro_motiv4</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C228">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D228">
         <v>0</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>olga.oliveira013</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>leosacraa</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>gutocriativo</v>
+        <v>andrejetx</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>igorfso_</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>lay_roqs</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>bigjota.artist</v>
+        <v>leosacraa</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>mth_fernandes031</v>
+        <v>igorfso_</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>turmanmma</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>gustavomohallem</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>atlta.marc0s</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>arturbambam</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>hermaan10_</v>
+        <v>turmanmma</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>danieljsantoss_</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>rodrigojansen_</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>markakasocks</v>
+        <v>arturbambam</v>
       </c>
       <c r="B248">
         <v>1</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>hunter.mccrary</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B249">
         <v>1</v>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>marinealcausa</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C250">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D250">
         <v>0</v>
@@ -3902,13 +3902,13 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>emersonriosmma</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C251">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D251">
         <v>0</v>
@@ -3916,41 +3916,41 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>luizcosta_mma</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C252">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D252">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>giulia.fasolato</v>
+        <v>markakasocks</v>
       </c>
       <c r="B253">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C253">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D253">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>michelle_mirele</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C254">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D254">
         <v>0</v>
@@ -3958,13 +3958,13 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>danielfranzesilva</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C255">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D255">
         <v>0</v>
@@ -3972,97 +3972,97 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>ednilsonkaicai</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B256">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C256">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D256">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B257">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C257">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D257">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>dayanaa1511</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C258">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D258">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>vanessamelomma</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B259">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D259">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>leonardopateira</v>
+        <v>manmoska</v>
       </c>
       <c r="B260">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C260">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D260">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>rahikikhalid</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B261">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C261">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D261">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>manumito.oficial</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B262">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C262">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D262">
         <v>0</v>
@@ -4070,13 +4070,13 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>carlosnoelblack</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B263">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C263">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D263">
         <v>0</v>
@@ -4084,13 +4084,13 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>moisespira</v>
       </c>
       <c r="B264">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C264">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D264">
         <v>0</v>
@@ -4098,41 +4098,41 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>lokomemo_protetores</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B265">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C265">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D265">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>coutz11</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B266">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D266">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>orlando_alfa09</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B267">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C267">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D267">
         <v>0</v>
@@ -4140,13 +4140,13 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>vitorshowman</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B268">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C268">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D268">
         <v>0</v>
@@ -4154,13 +4154,13 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>4lissson</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C269">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D269">
         <v>0</v>
@@ -4168,97 +4168,97 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>danilofernandescf</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B270">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C270">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D270">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>bryandazuera</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B271">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C271">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D271">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>ommariotti</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B272">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C272">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D272">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>brodschack_</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B273">
         <v>0</v>
       </c>
       <c r="C273">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D273">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>_vpft</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B274">
         <v>0</v>
       </c>
       <c r="C274">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D274">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>izabeldelfino_</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B275">
         <v>0</v>
       </c>
       <c r="C275">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D275">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>janjaovix</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B276">
         <v>0</v>
       </c>
       <c r="C276">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D276">
         <v>1</v>
@@ -4266,27 +4266,27 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>guerreirammaofc</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B277">
         <v>0</v>
       </c>
       <c r="C277">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D277">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B278">
         <v>0</v>
       </c>
       <c r="C278">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D278">
         <v>0</v>
@@ -4294,13 +4294,13 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>helenaseveribjj</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B279">
         <v>0</v>
       </c>
       <c r="C279">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D279">
         <v>0</v>
@@ -4308,41 +4308,41 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>_kainanlima</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B280">
         <v>0</v>
       </c>
       <c r="C280">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D280">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>jimmy_indioap</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B281">
         <v>0</v>
       </c>
       <c r="C281">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D281">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>omar_alneaimi</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B282">
         <v>0</v>
       </c>
       <c r="C282">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D282">
         <v>0</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>victor_brunopersonal</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B283">
         <v>0</v>
@@ -4359,12 +4359,12 @@
         <v>1</v>
       </c>
       <c r="D283">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>motumbo_team</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4373,12 +4373,12 @@
         <v>1</v>
       </c>
       <c r="D284">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>vanemessina</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4387,18 +4387,18 @@
         <v>1</v>
       </c>
       <c r="D285">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>dadwillians</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B286">
         <v>0</v>
       </c>
       <c r="C286">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D286">
         <v>0</v>
@@ -4406,13 +4406,13 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>thalytabjj</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B287">
         <v>0</v>
       </c>
       <c r="C287">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D287">
         <v>0</v>
@@ -4420,13 +4420,13 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B288">
         <v>0</v>
       </c>
       <c r="C288">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D288">
         <v>0</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>esteticaluharruda</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B289">
         <v>0</v>
@@ -4443,12 +4443,12 @@
         <v>1</v>
       </c>
       <c r="D289">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>chubotaru_lilu</v>
+        <v>coutz11</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4457,18 +4457,18 @@
         <v>1</v>
       </c>
       <c r="D290">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>eusoufernandosaito</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B291">
         <v>0</v>
       </c>
       <c r="C291">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D291">
         <v>0</v>
@@ -4476,13 +4476,13 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>dandraco_</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B292">
         <v>0</v>
       </c>
       <c r="C292">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D292">
         <v>0</v>
@@ -4490,13 +4490,13 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>4lissson</v>
       </c>
       <c r="B293">
         <v>0</v>
       </c>
       <c r="C293">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D293">
         <v>0</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>sejamotivadorofc</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B294">
         <v>0</v>
@@ -4513,12 +4513,12 @@
         <v>1</v>
       </c>
       <c r="D294">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>tpapereira</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4527,12 +4527,12 @@
         <v>1</v>
       </c>
       <c r="D295">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>kfcampeoes</v>
+        <v>ommariotti</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4541,12 +4541,12 @@
         <v>1</v>
       </c>
       <c r="D296">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>herrickmarinho</v>
+        <v>brodschack_</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4555,12 +4555,12 @@
         <v>1</v>
       </c>
       <c r="D297">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>rafaelcmjj</v>
+        <v>_vpft</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4569,12 +4569,12 @@
         <v>1</v>
       </c>
       <c r="D298">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>cristianomarcello</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4583,12 +4583,12 @@
         <v>1</v>
       </c>
       <c r="D299">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>_gabrielpego</v>
+        <v>janjaovix</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4597,12 +4597,12 @@
         <v>1</v>
       </c>
       <c r="D300">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>taylor_71kg</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4611,12 +4611,12 @@
         <v>1</v>
       </c>
       <c r="D301">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>doraasivla</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>pe.mirandas</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>leaoanaalice</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>caioparangole</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>sabrinaalsilva</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>eglaudiomma</v>
+        <v>vanemessina</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>strong_stg_oficial</v>
+        <v>dadwillians</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>ricardotofanello</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>taporondebruno</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>anamatias.m</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>claudio_marchese_7</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>1000ton_n</v>
+        <v>dandraco_</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>paulo.titoo</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>vitorcosta_mma</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>couragemma</v>
+        <v>tpapereira</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>romulerasilva</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>edergama.mma</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>alineanne_</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>julckreis</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>andreza.thais.1</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>benicius_edu</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>michele_mixa</v>
+        <v>doraasivla</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>joaolauar_</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>igorbrasileiro01</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>felipeocalmon</v>
+        <v>caioparangole</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>rejr_mma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>deivssonmanin</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>andrey_m_s_</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>vidaldanin</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>barbaracontadora</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B334">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>natalves5</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B335">
         <v>0</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>boradepodcastoficial</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>audizioandrade</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>isadoragolimpio</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>dudu.acabamentos</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>katlembrenda</v>
+        <v>couragemma</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>aline.amaral21</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>tamysregina</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>guilhermews1994</v>
+        <v>alineanne_</v>
       </c>
       <c r="B344">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>percepcar</v>
+        <v>julckreis</v>
       </c>
       <c r="B345">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>kevin.mota95</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>_marcos_.71</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>douglas_vitor8</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B349">
         <v>0</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>raulcarvalho1010</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B350">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>roginbrito</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B351">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>meirelesmma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B352">
         <v>0</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>dvlucc2k26_</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>armysenju</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>f.ostini</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>fher.nando_</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B356">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>bastazinifilho</v>
+        <v>natalves5</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -5414,28 +5414,574 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
+        <v>marlon_bodybuilding</v>
+      </c>
+      <c r="B359">
+        <v>0</v>
+      </c>
+      <c r="C359">
+        <v>1</v>
+      </c>
+      <c r="D359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>boradepodcastoficial</v>
+      </c>
+      <c r="B360">
+        <v>0</v>
+      </c>
+      <c r="C360">
+        <v>1</v>
+      </c>
+      <c r="D360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>audizioandrade</v>
+      </c>
+      <c r="B361">
+        <v>0</v>
+      </c>
+      <c r="C361">
+        <v>1</v>
+      </c>
+      <c r="D361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>isadoragolimpio</v>
+      </c>
+      <c r="B362">
+        <v>0</v>
+      </c>
+      <c r="C362">
+        <v>1</v>
+      </c>
+      <c r="D362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>dudu.acabamentos</v>
+      </c>
+      <c r="B363">
+        <v>0</v>
+      </c>
+      <c r="C363">
+        <v>1</v>
+      </c>
+      <c r="D363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>katlembrenda</v>
+      </c>
+      <c r="B364">
+        <v>0</v>
+      </c>
+      <c r="C364">
+        <v>1</v>
+      </c>
+      <c r="D364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>aline.amaral21</v>
+      </c>
+      <c r="B365">
+        <v>0</v>
+      </c>
+      <c r="C365">
+        <v>1</v>
+      </c>
+      <c r="D365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>tamysregina</v>
+      </c>
+      <c r="B366">
+        <v>0</v>
+      </c>
+      <c r="C366">
+        <v>1</v>
+      </c>
+      <c r="D366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>guilhermews1994</v>
+      </c>
+      <c r="B367">
+        <v>0</v>
+      </c>
+      <c r="C367">
+        <v>1</v>
+      </c>
+      <c r="D367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>percepcar</v>
+      </c>
+      <c r="B368">
+        <v>0</v>
+      </c>
+      <c r="C368">
+        <v>1</v>
+      </c>
+      <c r="D368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>kevin.mota95</v>
+      </c>
+      <c r="B369">
+        <v>0</v>
+      </c>
+      <c r="C369">
+        <v>1</v>
+      </c>
+      <c r="D369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>_marcos_.71</v>
+      </c>
+      <c r="B370">
+        <v>0</v>
+      </c>
+      <c r="C370">
+        <v>1</v>
+      </c>
+      <c r="D370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>douglas_vitor8</v>
+      </c>
+      <c r="B371">
+        <v>0</v>
+      </c>
+      <c r="C371">
+        <v>1</v>
+      </c>
+      <c r="D371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>gemeaslauraebrenda</v>
+      </c>
+      <c r="B372">
+        <v>0</v>
+      </c>
+      <c r="C372">
+        <v>1</v>
+      </c>
+      <c r="D372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>raulcarvalho1010</v>
+      </c>
+      <c r="B373">
+        <v>0</v>
+      </c>
+      <c r="C373">
+        <v>1</v>
+      </c>
+      <c r="D373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>roginbrito</v>
+      </c>
+      <c r="B374">
+        <v>0</v>
+      </c>
+      <c r="C374">
+        <v>1</v>
+      </c>
+      <c r="D374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>meirelesmma</v>
+      </c>
+      <c r="B375">
+        <v>0</v>
+      </c>
+      <c r="C375">
+        <v>1</v>
+      </c>
+      <c r="D375">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>dvlucc2k26_</v>
+      </c>
+      <c r="B376">
+        <v>0</v>
+      </c>
+      <c r="C376">
+        <v>1</v>
+      </c>
+      <c r="D376">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>armysenju</v>
+      </c>
+      <c r="B377">
+        <v>0</v>
+      </c>
+      <c r="C377">
+        <v>1</v>
+      </c>
+      <c r="D377">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>f.ostini</v>
+      </c>
+      <c r="B378">
+        <v>0</v>
+      </c>
+      <c r="C378">
+        <v>1</v>
+      </c>
+      <c r="D378">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>fher.nando_</v>
+      </c>
+      <c r="B379">
+        <v>0</v>
+      </c>
+      <c r="C379">
+        <v>1</v>
+      </c>
+      <c r="D379">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>cristiannogueira.vtt</v>
+      </c>
+      <c r="B380">
+        <v>0</v>
+      </c>
+      <c r="C380">
+        <v>1</v>
+      </c>
+      <c r="D380">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>bastazinifilho</v>
+      </c>
+      <c r="B381">
+        <v>0</v>
+      </c>
+      <c r="C381">
+        <v>1</v>
+      </c>
+      <c r="D381">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
         <v>pammygaryo</v>
       </c>
-      <c r="B359">
-        <v>0</v>
-      </c>
-      <c r="C359">
-        <v>1</v>
-      </c>
-      <c r="D359">
+      <c r="B382">
+        <v>0</v>
+      </c>
+      <c r="C382">
+        <v>1</v>
+      </c>
+      <c r="D382">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>anselmo.azevedo</v>
+      </c>
+      <c r="B383">
+        <v>0</v>
+      </c>
+      <c r="C383">
+        <v>1</v>
+      </c>
+      <c r="D383">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>marcotulio_matuto</v>
+      </c>
+      <c r="B384">
+        <v>0</v>
+      </c>
+      <c r="C384">
+        <v>1</v>
+      </c>
+      <c r="D384">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>ianrochaf</v>
+      </c>
+      <c r="B385">
+        <v>0</v>
+      </c>
+      <c r="C385">
+        <v>1</v>
+      </c>
+      <c r="D385">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>ale.lagonegro</v>
+      </c>
+      <c r="B386">
+        <v>0</v>
+      </c>
+      <c r="C386">
+        <v>1</v>
+      </c>
+      <c r="D386">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>ganemfelipe</v>
+      </c>
+      <c r="B387">
+        <v>0</v>
+      </c>
+      <c r="C387">
+        <v>1</v>
+      </c>
+      <c r="D387">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>marcusvgsz</v>
+      </c>
+      <c r="B388">
+        <v>0</v>
+      </c>
+      <c r="C388">
+        <v>1</v>
+      </c>
+      <c r="D388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>wanderson.casttro</v>
+      </c>
+      <c r="B389">
+        <v>0</v>
+      </c>
+      <c r="C389">
+        <v>1</v>
+      </c>
+      <c r="D389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>fabio.sampaio.90260</v>
+      </c>
+      <c r="B390">
+        <v>0</v>
+      </c>
+      <c r="C390">
+        <v>1</v>
+      </c>
+      <c r="D390">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>jotapeamancio</v>
+      </c>
+      <c r="B391">
+        <v>0</v>
+      </c>
+      <c r="C391">
+        <v>1</v>
+      </c>
+      <c r="D391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>kaynankruschewsky_ufc</v>
+      </c>
+      <c r="B392">
+        <v>0</v>
+      </c>
+      <c r="C392">
+        <v>1</v>
+      </c>
+      <c r="D392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>vitorpaes_personalfight</v>
+      </c>
+      <c r="B393">
+        <v>0</v>
+      </c>
+      <c r="C393">
+        <v>1</v>
+      </c>
+      <c r="D393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>zeferinomma</v>
+      </c>
+      <c r="B394">
+        <v>0</v>
+      </c>
+      <c r="C394">
+        <v>1</v>
+      </c>
+      <c r="D394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>tavaresguu</v>
+      </c>
+      <c r="B395">
+        <v>0</v>
+      </c>
+      <c r="C395">
+        <v>1</v>
+      </c>
+      <c r="D395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>ildemarmarajo</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+      <c r="C396">
+        <v>1</v>
+      </c>
+      <c r="D396">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>peterson_arrais</v>
+      </c>
+      <c r="B397">
+        <v>0</v>
+      </c>
+      <c r="C397">
+        <v>1</v>
+      </c>
+      <c r="D397">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>danieldias7s</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+      <c r="C398">
+        <v>1</v>
+      </c>
+      <c r="D398">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D359"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D398"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D102"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5456,13 +6002,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>374</v>
+        <v>450</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>362</v>
+        <v>434</v>
       </c>
     </row>
     <row r="3">
@@ -5481,30 +6027,30 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>rm.nicki</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>46</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>rpsantos_mma</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B5">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>23</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6">
@@ -5512,27 +6058,27 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>pablofiorindi</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
@@ -5540,13 +6086,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -5554,13 +6100,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B9">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
@@ -5610,13 +6156,13 @@
         <v>mmmarc20</v>
       </c>
       <c r="B13">
+        <v>9</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>8</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -5635,16 +6181,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ryangandraufc</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -5652,46 +6198,46 @@
         <v>combintel</v>
       </c>
       <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
         <v>5</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16">
-        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>god.motivacao</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B17">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C17">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>irmandadefightteam</v>
+        <v>aline.r15</v>
       </c>
       <c r="B19">
         <v>2</v>
@@ -5705,7 +6251,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>excelentfightcompetition</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B20">
         <v>2</v>
@@ -5719,10 +6265,10 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>_beegomes_</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -5733,10 +6279,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>karen.ottoni</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -5747,7 +6293,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>alfredo_miras</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B23">
         <v>2</v>
@@ -5761,13 +6307,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>marc0s.azv</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -5817,10 +6363,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>z.proddd</v>
+        <v>maxgandra</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -5831,7 +6377,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>maxgandra</v>
+        <v>z.proddd</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -5845,10 +6391,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>livreseseguras</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -5859,10 +6405,10 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ronemayanmorais</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -5873,7 +6419,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>pedrinhosbjj</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -5887,21 +6433,21 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>pedromadeira.s</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -5915,7 +6461,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>kalindrafaria</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -5924,26 +6470,26 @@
         <v>0</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>antonioemanuel.13</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C36">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>enzoferrari680</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -5957,7 +6503,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>gustavomohallem</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -5971,7 +6517,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>atlta.marc0s</v>
+        <v>andreibjj</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -5985,27 +6531,27 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>arturbambam</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B41">
         <v>1</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -6013,13 +6559,13 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>hermaan10_</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -6027,7 +6573,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>danieljsantoss_</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -6041,7 +6587,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>rodrigojansen_</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -6055,7 +6601,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>markakasocks</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -6069,7 +6615,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>hunter.mccrary</v>
+        <v>arturbambam</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -6083,97 +6629,97 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>marcos_tailandess</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>tabajaraharu</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>eliassilverio</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>izabeldelfino_</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>janjaovix</v>
+        <v>markakasocks</v>
       </c>
       <c r="B51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>guerreirammaofc</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>benjafloripabjj</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
         <v>0</v>
@@ -6181,13 +6727,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>f.ostini</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -6195,13 +6741,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>fher.nando_</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -6209,13 +6755,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -6223,13 +6769,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>bastazinifilho</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>0</v>
@@ -6237,13 +6783,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>0</v>
@@ -6251,21 +6797,623 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
+        <v>manmoska</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>0</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>renatoevangelistaa</v>
+      </c>
+      <c r="B60">
+        <v>1</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>cassius.paula</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>ctt.casaestopteam</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>aliferpaulo_</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>moisespira</v>
+      </c>
+      <c r="B64">
+        <v>1</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>rodrigolidiosales</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="str">
+        <v>claudioribeiro_ufc</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>marciocatenacci</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="str">
+        <v>cristiane.c.santana</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="str">
+        <v>ariel_alvees</v>
+      </c>
+      <c r="B69">
+        <v>1</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="str">
+        <v>flahvinhotreinador</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="str">
+        <v>marcos.jordao.bjj</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>selma.oscar12</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>marcos_tailandess</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>2</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>tabajaraharu</v>
+      </c>
+      <c r="B74">
+        <v>0</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>izabeldelfino_</v>
+      </c>
+      <c r="B75">
+        <v>0</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="D75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>janjaovix</v>
+      </c>
+      <c r="B76">
+        <v>0</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>guerreirammaofc</v>
+      </c>
+      <c r="B77">
+        <v>0</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>benjafloripabjj</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>1</v>
+      </c>
+      <c r="D78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>f.ostini</v>
+      </c>
+      <c r="B79">
+        <v>0</v>
+      </c>
+      <c r="C79">
+        <v>1</v>
+      </c>
+      <c r="D79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>fher.nando_</v>
+      </c>
+      <c r="B80">
+        <v>0</v>
+      </c>
+      <c r="C80">
+        <v>1</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>cristiannogueira.vtt</v>
+      </c>
+      <c r="B81">
+        <v>0</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>bastazinifilho</v>
+      </c>
+      <c r="B82">
+        <v>0</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="str">
+        <v>luanlacerda_ufc_61kg</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="str">
         <v>pammygaryo</v>
       </c>
-      <c r="B59">
-        <v>0</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59">
+      <c r="B84">
+        <v>0</v>
+      </c>
+      <c r="C84">
+        <v>1</v>
+      </c>
+      <c r="D84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="str">
+        <v>anselmo.azevedo</v>
+      </c>
+      <c r="B85">
+        <v>0</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="str">
+        <v>marcotulio_matuto</v>
+      </c>
+      <c r="B86">
+        <v>0</v>
+      </c>
+      <c r="C86">
+        <v>1</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="str">
+        <v>ianrochaf</v>
+      </c>
+      <c r="B87">
+        <v>0</v>
+      </c>
+      <c r="C87">
+        <v>1</v>
+      </c>
+      <c r="D87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>ale.lagonegro</v>
+      </c>
+      <c r="B88">
+        <v>0</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="str">
+        <v>ganemfelipe</v>
+      </c>
+      <c r="B89">
+        <v>0</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>flavio.dequeiroz</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>marcusvgsz</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
+        <v>wanderson.casttro</v>
+      </c>
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>fabio.sampaio.90260</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>jotapeamancio</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>kaynankruschewsky_ufc</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>vitorpaes_personalfight</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>zeferinomma</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
+        <v>tavaresguu</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>ildemarmarajo</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>sirleneferreiradiasdias</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>peterson_arrais</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>danieldias7s</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D102"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D398"/>
+  <dimension ref="A1:D399"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -419,13 +419,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>1422</v>
+        <v>1475</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2">
-        <v>1167</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="3">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4">
@@ -447,7 +447,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C4">
         <v>26</v>
@@ -475,13 +475,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B6">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C6">
         <v>7</v>
       </c>
       <c r="D6">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7">
@@ -489,13 +489,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B7">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C7">
         <v>4</v>
       </c>
       <c r="D7">
-        <v>68</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8">
@@ -503,7 +503,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -517,13 +517,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B9">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>82</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -545,13 +545,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B11">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12">
@@ -570,30 +570,30 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>irmandadefightteam</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D13">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ryangandraufc</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B14">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C14">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>39</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -836,30 +836,30 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>tabajaraharu</v>
+        <v>maxgandra</v>
       </c>
       <c r="B32">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C32">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>maxgandra</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B33">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -2082,13 +2082,13 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B121">
         <v>1</v>
       </c>
       <c r="C121">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -2096,27 +2096,27 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>treinaadorrafael</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>benjafloripabjj</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D123">
         <v>0</v>
@@ -2124,13 +2124,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>fernando.mma</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D124">
         <v>0</v>
@@ -2138,13 +2138,13 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D125">
         <v>0</v>
@@ -2152,13 +2152,13 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D126">
         <v>0</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,13 +2180,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>guiiviieira_</v>
+        <v>030sami</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,13 +2362,13 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D141">
         <v>0</v>
@@ -2376,13 +2376,13 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>kalindrafaria</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,35 +2432,35 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>cristianpsicologo</v>
+        <v>andreibjj</v>
       </c>
       <c r="B146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C146">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D146">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C147">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,35 +2502,35 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>antonioemanuel.13</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D151">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C152">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,13 +2544,13 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>tonketjudes</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B154">
         <v>1</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,35 +2852,35 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C176">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D176">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>wlt_miguel</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>jaonevesz</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>flazuera14</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>camii_bonfim</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>wesley_bjjvc</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>sambagabrieloficial</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>peacegrappler</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>_alcantara.bru</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,13 +3580,13 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C228">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D228">
         <v>0</v>
@@ -3594,13 +3594,13 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C229">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D229">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>gustavomohallem</v>
+        <v>turmanmma</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>atlta.marc0s</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B248">
         <v>1</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>arturbambam</v>
       </c>
       <c r="B249">
         <v>1</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>hermaan10_</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B250">
         <v>1</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B251">
         <v>1</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B252">
         <v>1</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B257">
         <v>1</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>natalan_wilgner</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B260">
         <v>1</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B261">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B262">
         <v>1</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B263">
         <v>1</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B264">
         <v>1</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B265">
         <v>1</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B266">
         <v>1</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B268">
         <v>1</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B269">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B270">
         <v>1</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B271">
         <v>1</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,13 +4210,13 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>marinealcausa</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C273">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D273">
         <v>0</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B274">
         <v>0</v>
@@ -4238,63 +4238,63 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B275">
         <v>0</v>
       </c>
       <c r="C275">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D275">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B276">
         <v>0</v>
       </c>
       <c r="C276">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D276">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>giulia.fasolato</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B277">
         <v>0</v>
       </c>
       <c r="C277">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D277">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B278">
         <v>0</v>
       </c>
       <c r="C278">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D278">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B279">
         <v>0</v>
@@ -4308,21 +4308,21 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B280">
         <v>0</v>
       </c>
       <c r="C280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D280">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>dayanaa1511</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B282">
         <v>0</v>
@@ -4345,26 +4345,26 @@
         <v>2</v>
       </c>
       <c r="D282">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>vanessamelomma</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B283">
         <v>0</v>
       </c>
       <c r="C283">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D283">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B285">
         <v>0</v>
@@ -4392,21 +4392,21 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B286">
         <v>0</v>
       </c>
       <c r="C286">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D286">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B288">
         <v>0</v>
@@ -4434,21 +4434,21 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B289">
         <v>0</v>
       </c>
       <c r="C289">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D289">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,21 +4462,21 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B291">
         <v>0</v>
       </c>
       <c r="C291">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D291">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,21 +4504,21 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B294">
         <v>0</v>
       </c>
       <c r="C294">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D294">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B296">
         <v>0</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>izabeldelfino_</v>
+        <v>_vpft</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>janjaovix</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>guerreirammaofc</v>
+        <v>janjaovix</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4625,12 +4625,12 @@
         <v>1</v>
       </c>
       <c r="D302">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>esteticaluharruda</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B334">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B335">
         <v>0</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B344">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B345">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B349">
         <v>0</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B350">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B351">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B352">
         <v>0</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B356">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B359">
         <v>0</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B360">
         <v>0</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B363">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B364">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B365">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B366">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B367">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B368">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B369">
         <v>0</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B370">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B371">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B372">
         <v>0</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B373">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B374">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B375">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>dvlucc2k26_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B376">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>armysenju</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B377">
         <v>0</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>f.ostini</v>
+        <v>armysenju</v>
       </c>
       <c r="B378">
         <v>0</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>fher.nando_</v>
+        <v>f.ostini</v>
       </c>
       <c r="B379">
         <v>0</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B380">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>bastazinifilho</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B381">
         <v>0</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>pammygaryo</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B382">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>anselmo.azevedo</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B383">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>marcotulio_matuto</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B384">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>ianrochaf</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>ale.lagonegro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B386">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>ganemfelipe</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B387">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>marcusvgsz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B388">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>wanderson.casttro</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B389">
         <v>0</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B390">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>jotapeamancio</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B391">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B392">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B393">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>zeferinomma</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B394">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>tavaresguu</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B395">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>ildemarmarajo</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B396">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>peterson_arrais</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B397">
         <v>0</v>
@@ -5960,28 +5960,42 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
+        <v>peterson_arrais</v>
+      </c>
+      <c r="B398">
+        <v>0</v>
+      </c>
+      <c r="C398">
+        <v>1</v>
+      </c>
+      <c r="D398">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
         <v>danieldias7s</v>
       </c>
-      <c r="B398">
-        <v>0</v>
-      </c>
-      <c r="C398">
-        <v>1</v>
-      </c>
-      <c r="D398">
+      <c r="B399">
+        <v>0</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+      <c r="D399">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D398"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D399"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D102"/>
+  <dimension ref="A1:D103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6002,13 +6016,13 @@
         <v>peacegrappler_mma</v>
       </c>
       <c r="B2">
-        <v>450</v>
+        <v>503</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>434</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3">
@@ -6016,13 +6030,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B3">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
@@ -6030,13 +6044,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -6044,13 +6058,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B5">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6">
@@ -6072,7 +6086,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -6086,13 +6100,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>20</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -6100,13 +6114,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B9">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -6114,7 +6128,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B10">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -6167,41 +6181,41 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>cleyton_jesuss</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>marc0s.azv</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B15">
         <v>7</v>
       </c>
       <c r="C15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>combintel</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D16">
         <v>5</v>
@@ -6209,16 +6223,16 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ryangandraufc</v>
+        <v>combintel</v>
       </c>
       <c r="B17">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C17">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -6293,21 +6307,21 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>karen.ottoni</v>
+        <v>maxgandra</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>alfredo_miras</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B24">
         <v>2</v>
@@ -6321,7 +6335,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>badboykillermma</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -6335,7 +6349,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>gra_jpereira</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -6349,7 +6363,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>ninjatheorist</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -6363,16 +6377,16 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>maxgandra</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -6475,7 +6489,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>kalindrafaria</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -6484,12 +6498,12 @@
         <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -6503,7 +6517,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -6517,7 +6531,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -6531,35 +6545,35 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>antonioemanuel.13</v>
+        <v>andreibjj</v>
       </c>
       <c r="B40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C40">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -6573,13 +6587,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>enzoferrari680</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -6587,7 +6601,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>gustavomohallem</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -6601,7 +6615,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>atlta.marc0s</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -6615,7 +6629,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -6629,7 +6643,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>arturbambam</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -6643,7 +6657,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>hermaan10_</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -6657,7 +6671,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -6671,7 +6685,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -6685,7 +6699,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -6699,7 +6713,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -6713,7 +6727,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -6727,7 +6741,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -6741,7 +6755,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -6755,7 +6769,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -6769,7 +6783,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>cjrnavalha</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -6783,7 +6797,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>natalan_wilgner</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -6797,7 +6811,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -6811,7 +6825,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -6825,7 +6839,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -6839,7 +6853,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -6853,7 +6867,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>aliferpaulo_</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -6867,7 +6881,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>moisespira</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -6881,7 +6895,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -6895,7 +6909,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -6909,7 +6923,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -6923,7 +6937,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -6937,7 +6951,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -6951,7 +6965,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -6965,7 +6979,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -6979,7 +6993,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -6993,27 +7007,27 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>marcos_tailandess</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>tabajaraharu</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B74">
         <v>0</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -7021,7 +7035,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>izabeldelfino_</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -7035,7 +7049,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>janjaovix</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -7049,7 +7063,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>guerreirammaofc</v>
+        <v>janjaovix</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -7063,7 +7077,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>benjafloripabjj</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -7072,12 +7086,12 @@
         <v>1</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>f.ostini</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -7091,7 +7105,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>fher.nando_</v>
+        <v>f.ostini</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -7105,7 +7119,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -7119,7 +7133,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>bastazinifilho</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -7133,7 +7147,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -7147,7 +7161,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>pammygaryo</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -7161,7 +7175,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>anselmo.azevedo</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -7175,7 +7189,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>marcotulio_matuto</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -7189,7 +7203,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>ianrochaf</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -7203,7 +7217,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>ale.lagonegro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -7217,7 +7231,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>ganemfelipe</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -7231,7 +7245,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -7245,7 +7259,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>marcusvgsz</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -7259,7 +7273,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>wanderson.casttro</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -7273,7 +7287,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -7287,7 +7301,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>jotapeamancio</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -7301,7 +7315,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -7315,7 +7329,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -7329,7 +7343,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>zeferinomma</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -7343,7 +7357,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>tavaresguu</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -7357,7 +7371,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>ildemarmarajo</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -7371,7 +7385,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -7385,7 +7399,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>peterson_arrais</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -7399,21 +7413,35 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>peterson_arrais</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
         <v>danieldias7s</v>
       </c>
-      <c r="B102">
-        <v>0</v>
-      </c>
-      <c r="C102">
-        <v>1</v>
-      </c>
-      <c r="D102">
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D103"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D399"/>
+  <dimension ref="A1:D408"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="4">
@@ -447,7 +447,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C4">
         <v>26</v>
@@ -475,7 +475,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B6">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C6">
         <v>7</v>
@@ -489,13 +489,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B7">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C7">
         <v>4</v>
       </c>
       <c r="D7">
-        <v>71</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -503,7 +503,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -517,13 +517,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B9">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C9">
         <v>2</v>
       </c>
       <c r="D9">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10">
@@ -545,7 +545,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B11">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -556,108 +556,108 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>anaaj_camargo</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B12">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ryangandraufc</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B13">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C13">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>irmandadefightteam</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B14">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D14">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>mmmarc20</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B15">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ronemayanmorais</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>bellsouza816</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B17">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D17">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>erik_.mma</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B18">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>kaua_limamma</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B19">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -668,231 +668,231 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>combintel</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B20">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>aline.r15</v>
+        <v>combintel</v>
       </c>
       <c r="B21">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C21">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D21">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>god.motivacao</v>
+        <v>aline.r15</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C22">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>cleyton_jesuss</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B23">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C23">
-        <v>4</v>
+        <v>124</v>
       </c>
       <c r="D23">
-        <v>18</v>
+        <v>38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>gra_jpereira</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B24">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D24">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>leandro._bjj</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B25">
         <v>19</v>
       </c>
       <c r="C25">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>alvesmidih</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B26">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D26">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>tiwimma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B27">
         <v>15</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>pedromadeira.s</v>
+        <v>tiwimma</v>
       </c>
       <c r="B28">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>eliassilverio</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B29">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B30">
         <v>11</v>
       </c>
       <c r="C30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>cjrnavalha</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B31">
         <v>11</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>maxgandra</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B32">
         <v>11</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>tabajaraharu</v>
+        <v>maxgandra</v>
       </c>
       <c r="B33">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C33">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>_beegomes_</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B34">
+        <v>6</v>
+      </c>
+      <c r="C34">
+        <v>11</v>
+      </c>
+      <c r="D34">
         <v>8</v>
-      </c>
-      <c r="C34">
-        <v>1</v>
-      </c>
-      <c r="D34">
-        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>marc0s.azv</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C35">
         <v>1</v>
       </c>
       <c r="D35">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>tawanregismma</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B36">
         <v>7</v>
@@ -901,18 +901,18 @@
         <v>1</v>
       </c>
       <c r="D36">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>karen.ottoni</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -920,167 +920,167 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>rrafaelins</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B38">
+        <v>5</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
         <v>4</v>
-      </c>
-      <c r="C38">
-        <v>4</v>
-      </c>
-      <c r="D38">
-        <v>5</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>italothearcher</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C40">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>vndcardoso</v>
+        <v>italothearcher</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>juniordiasmma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B42">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>badboykillermma</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>gdazuera</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>enzoferrari680</v>
+        <v>gdazuera</v>
       </c>
       <c r="B45">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B46">
         <v>6</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>eolucasrosa</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>dagestan0920</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B49">
         <v>5</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -1088,13 +1088,13 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1102,27 +1102,27 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>_.maduoliveira_</v>
+        <v>paxlucta</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D51">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B52">
         <v>3</v>
       </c>
       <c r="C52">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -1130,21 +1130,21 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>glm.barbosa</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>excelentfightcompetition</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B54">
         <v>2</v>
@@ -1158,27 +1158,27 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>marcelogabrielmma</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
       <c r="C56">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D56">
         <v>3</v>
@@ -1186,111 +1186,111 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C57">
+        <v>4</v>
+      </c>
+      <c r="D57">
         <v>3</v>
-      </c>
-      <c r="D57">
-        <v>5</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>gabrielsouzamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B58">
         <v>2</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D58">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B59">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>alfredo_miras</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>marcos_tailandess</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>ravenrodriguez___</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B62">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C62">
+        <v>8</v>
+      </c>
+      <c r="D62">
         <v>3</v>
-      </c>
-      <c r="D62">
-        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>fabinho_falcao_</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -1298,24 +1298,24 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B66">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B67">
         <v>4</v>
@@ -1340,21 +1340,21 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ninjatheorist</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>shawlin13oficial</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B69">
         <v>2</v>
@@ -1363,12 +1363,12 @@
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -1382,7 +1382,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -1396,7 +1396,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B72">
         <v>2</v>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>z.proddd</v>
+        <v>febrancatti</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -1424,13 +1424,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>dogodoyfoto</v>
+        <v>z.proddd</v>
       </c>
       <c r="B74">
         <v>2</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -1438,35 +1438,35 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>reifernandes</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -1480,27 +1480,27 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -1508,21 +1508,21 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1536,91 +1536,91 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>odeivisoncardoso</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B84">
         <v>1</v>
       </c>
       <c r="C84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D84">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>maca.mariotti</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B85">
         <v>1</v>
       </c>
       <c r="C85">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D85">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>adriano.trator</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B86">
         <v>1</v>
       </c>
       <c r="C86">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -1648,21 +1648,21 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -1676,7 +1676,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>livreseseguras</v>
+        <v>ruangzk</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -1690,69 +1690,69 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>washington_cassisno</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B93">
         <v>1</v>
       </c>
       <c r="C93">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D93">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94">
         <v>2</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B97">
         <v>2</v>
       </c>
       <c r="C97">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D97">
         <v>0</v>
@@ -1760,13 +1760,13 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B98">
         <v>2</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D98">
         <v>0</v>
@@ -1774,35 +1774,35 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B100">
         <v>1</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -1825,18 +1825,18 @@
         <v>1</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -1844,13 +1844,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B104">
         <v>1</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -1858,21 +1858,21 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B106">
         <v>2</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B107">
         <v>2</v>
@@ -1900,7 +1900,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -1914,21 +1914,21 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C109">
         <v>0</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1956,7 +1956,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>heltoncm2002</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -1984,35 +1984,35 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>aliferpaulo_</v>
+        <v>raelduraes</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
         <v>0</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>pedrinhosbjj</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,13 +2096,13 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>1</v>
@@ -2110,35 +2110,35 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>treinaadorrafael</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>benjafloripabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>fernando.mma</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,13 +2166,13 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D127">
         <v>0</v>
@@ -2180,13 +2180,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>fagnerosensei</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128">
         <v>0</v>
@@ -2194,13 +2194,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>030sami</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D129">
         <v>0</v>
@@ -2208,13 +2208,13 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>guiiviieira_</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D130">
         <v>0</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>cshigueo</v>
+        <v>030sami</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>emerson_lucaszx</v>
+        <v>cshigueo</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>danni_goncalves12</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>mttsm._</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>andrealvess02</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>gildojiu</v>
+        <v>mttsm._</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>kawannsennast</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>yurimartins1_</v>
+        <v>gildojiu</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>matheusteodoro_1</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,13 +2376,13 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>kael_lyto</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>kalindrafaria</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,13 +2404,13 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>oniszczuk_ko</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,41 +2432,41 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>andreibjj</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>cristianpsicologo</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C147">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D147">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>juanx.pontes</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B148">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -2474,13 +2474,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>select_from_joao</v>
+        <v>andreibjj</v>
       </c>
       <c r="B149">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -2488,21 +2488,21 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>yeslifeacademia</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C150">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D150">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>ojaimerocha</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,21 +2516,21 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>antonioemanuel.13</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C152">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D152">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>gasparjr1983</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,27 +2558,27 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>tonketjudes</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C155">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>_eliasffx</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B156">
         <v>1</v>
       </c>
       <c r="C156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D156">
         <v>0</v>
@@ -2586,13 +2586,13 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>pdfiv</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B157">
         <v>1</v>
       </c>
       <c r="C157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>mariaraimundad940</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>gabesantos.13</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>euvitormirandaa</v>
+        <v>pdfiv</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>thompsonborralho</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>frankikolimabjj</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>alerrandrojj</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>anahangelica</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>minotaurinho</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>lara.rpr</v>
+        <v>anahangelica</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>codasqueves</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>yan_touro.7766</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>carolinne.xwp</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>davicorbella</v>
+        <v>codasqueves</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>artemio_bjj</v>
+        <v>davicorbella</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>katiaecarreraf</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>geraldocnetomma</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,21 +2866,21 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>pedro_pavin_</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C177">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D177">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>xavyeroficial</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>maryanagandra</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,21 +2908,21 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>eliandropires</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>charlesanthony2466</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>draanapaulaponceano</v>
+        <v>eliandropires</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>saj_photo_miami</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>alternativaremocoes</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>benivalentinn</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>navarro_9430</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>_puroosso88</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>_rayysp</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>cami.terra_</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>gabicardoson</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>martta.mariah</v>
+        <v>_rayysp</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>wlt_miguel</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>jaonevesz</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>pietroshz</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>___neller</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>_bety_marcal</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>guilhermeefelix__</v>
+        <v>pietroshz</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>pativinisf</v>
+        <v>___neller</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>judadany</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>andre_alcausa</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>_fernunes</v>
+        <v>pativinisf</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>aloirmarcal</v>
+        <v>judadany</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>gilberto_7606</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>_fernunes</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>flazuera14</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>camii_bonfim</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>danlouiz.jj</v>
+        <v>flazuera14</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>gabriel_trevelin</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>y.arthur_01</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>muricunha</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>victorhenriquebjj</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>_lsanchess_</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>__bielgg</v>
+        <v>muricunha</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>mr__rlk01</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>vitor_buck</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>fran.ruys</v>
+        <v>__bielgg</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>wesley_bjjvc</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>sambagabrieloficial</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>peacegrappler</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>_alcantara.bru</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>cesar.boanerges</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>alexandreconsentino</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,13 +3594,13 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>rafaela_duaartee</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C229">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D229">
         <v>0</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>andre.legendre.10</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C231">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D231">
         <v>0</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>phillipe.harry</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>andrejetx</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>leandro_motiv4</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>olga.oliveira013</v>
+        <v>andrejetx</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>leosacraa</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>gutocriativo</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>igorfso_</v>
+        <v>leosacraa</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>lay_roqs</v>
+        <v>igorfso_</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>bigjota.artist</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>mth_fernandes031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>turmanmma</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>gustavomohallem</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>atlta.marc0s</v>
+        <v>turmanmma</v>
       </c>
       <c r="B248">
         <v>1</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>arturbambam</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B249">
         <v>1</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B250">
         <v>1</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>hermaan10_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B251">
         <v>1</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B252">
         <v>1</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B257">
         <v>1</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>natalan_wilgner</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B260">
         <v>1</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B261">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B262">
         <v>1</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B263">
         <v>1</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B264">
         <v>1</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B265">
         <v>1</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B266">
         <v>1</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B268">
         <v>1</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B269">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B270">
         <v>1</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B271">
         <v>1</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B273">
         <v>1</v>
@@ -4224,13 +4224,13 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>marinealcausa</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C274">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D274">
         <v>0</v>
@@ -4238,13 +4238,13 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>emersonriosmma</v>
+        <v>magnoddias</v>
       </c>
       <c r="B275">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C275">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D275">
         <v>0</v>
@@ -4252,63 +4252,63 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>luizcosta_mma</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B276">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C276">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D276">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B277">
         <v>0</v>
       </c>
       <c r="C277">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D277">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>giulia.fasolato</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B278">
         <v>0</v>
       </c>
       <c r="C278">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D278">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>michelle_mirele</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B279">
         <v>0</v>
       </c>
       <c r="C279">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D279">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>danielfranzesilva</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B280">
         <v>0</v>
@@ -4317,12 +4317,12 @@
         <v>3</v>
       </c>
       <c r="D280">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>ednilsonkaicai</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B281">
         <v>0</v>
@@ -4331,32 +4331,32 @@
         <v>2</v>
       </c>
       <c r="D281">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>dayanaa1511</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B282">
         <v>0</v>
       </c>
       <c r="C282">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D282">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B283">
         <v>0</v>
       </c>
       <c r="C283">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D283">
         <v>0</v>
@@ -4364,13 +4364,13 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>vanessamelomma</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B284">
         <v>0</v>
       </c>
       <c r="C284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D284">
         <v>1</v>
@@ -4378,13 +4378,13 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>leonardopateira</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B285">
         <v>0</v>
       </c>
       <c r="C285">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D285">
         <v>1</v>
@@ -4392,13 +4392,13 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>rahikikhalid</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B286">
         <v>0</v>
       </c>
       <c r="C286">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D286">
         <v>1</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>manumito.oficial</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B287">
         <v>0</v>
@@ -4420,35 +4420,35 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>carlosnoelblack</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B288">
         <v>0</v>
       </c>
       <c r="C288">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D288">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B289">
         <v>0</v>
       </c>
       <c r="C289">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D289">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>lokomemo_protetores</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -4462,21 +4462,21 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>coutz11</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B291">
         <v>0</v>
       </c>
       <c r="C291">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D291">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>orlando_alfa09</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>vitorshowman</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4504,21 +4504,21 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>4lissson</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B294">
         <v>0</v>
       </c>
       <c r="C294">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D294">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>danilofernandescf</v>
+        <v>coutz11</v>
       </c>
       <c r="B295">
         <v>0</v>
@@ -4532,49 +4532,49 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>bryandazuera</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B296">
         <v>0</v>
       </c>
       <c r="C296">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D296">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>ommariotti</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B297">
         <v>0</v>
       </c>
       <c r="C297">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D297">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>brodschack_</v>
+        <v>4lissson</v>
       </c>
       <c r="B298">
         <v>0</v>
       </c>
       <c r="C298">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D298">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>_vpft</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>izabeldelfino_</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>janjaovix</v>
+        <v>ommariotti</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>guerreirammaofc</v>
+        <v>brodschack_</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_vpft</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4639,12 +4639,12 @@
         <v>1</v>
       </c>
       <c r="D303">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>helenaseveribjj</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4653,12 +4653,12 @@
         <v>1</v>
       </c>
       <c r="D304">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>_kainanlima</v>
+        <v>janjaovix</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4667,12 +4667,12 @@
         <v>1</v>
       </c>
       <c r="D305">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>jimmy_indioap</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4681,12 +4681,12 @@
         <v>1</v>
       </c>
       <c r="D306">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>omar_alneaimi</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>victor_brunopersonal</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>motumbo_team</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>vanemessina</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>dadwillians</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>thalytabjj</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>esteticaluharruda</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>chubotaru_lilu</v>
+        <v>vanemessina</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>eusoufernandosaito</v>
+        <v>dadwillians</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,7 +4812,7 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>dandraco_</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>sejamotivadorofc</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>tpapereira</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>kfcampeoes</v>
+        <v>dandraco_</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>herrickmarinho</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>rafaelcmjj</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>cristianomarcello</v>
+        <v>tpapereira</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>_gabrielpego</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>taylor_71kg</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>doraasivla</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>pe.mirandas</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>leaoanaalice</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>caioparangole</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>sabrinaalsilva</v>
+        <v>doraasivla</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>eglaudiomma</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>strong_stg_oficial</v>
+        <v>caioparangole</v>
       </c>
       <c r="B334">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>ricardotofanello</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B335">
         <v>0</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>taporondebruno</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>anamatias.m</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>claudio_marchese_7</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>1000ton_n</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>paulo.titoo</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>vitorcosta_mma</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>couragemma</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>romulerasilva</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>edergama.mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B344">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>alineanne_</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B345">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>julckreis</v>
+        <v>couragemma</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>andreza.thais.1</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>benicius_edu</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>alineanne_</v>
       </c>
       <c r="B349">
         <v>0</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>michele_mixa</v>
+        <v>julckreis</v>
       </c>
       <c r="B350">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>joaolauar_</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B351">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>igorbrasileiro01</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B352">
         <v>0</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>felipeocalmon</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>rejr_mma</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>deivssonmanin</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>andrey_m_s_</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B356">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>vidaldanin</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>barbaracontadora</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>natalves5</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B359">
         <v>0</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B360">
         <v>0</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>boradepodcastoficial</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>audizioandrade</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>isadoragolimpio</v>
+        <v>natalves5</v>
       </c>
       <c r="B363">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>dudu.acabamentos</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B364">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>katlembrenda</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B365">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>aline.amaral21</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B366">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>tamysregina</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B367">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>guilhermews1994</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B368">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>percepcar</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B369">
         <v>0</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>kevin.mota95</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B370">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>_marcos_.71</v>
+        <v>tamysregina</v>
       </c>
       <c r="B371">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>douglas_vitor8</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B372">
         <v>0</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>percepcar</v>
       </c>
       <c r="B373">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>raulcarvalho1010</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B374">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>roginbrito</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B375">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>meirelesmma</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B376">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>dvlucc2k26_</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B377">
         <v>0</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>armysenju</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B378">
         <v>0</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>f.ostini</v>
+        <v>roginbrito</v>
       </c>
       <c r="B379">
         <v>0</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>fher.nando_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B380">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B381">
         <v>0</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>bastazinifilho</v>
+        <v>armysenju</v>
       </c>
       <c r="B382">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>pammygaryo</v>
+        <v>f.ostini</v>
       </c>
       <c r="B383">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>anselmo.azevedo</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B384">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>marcotulio_matuto</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>ianrochaf</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B386">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>ale.lagonegro</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B387">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>ganemfelipe</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B388">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>marcusvgsz</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B389">
         <v>0</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>wanderson.casttro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B390">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B391">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>jotapeamancio</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B392">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B393">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B394">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>zeferinomma</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B395">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>tavaresguu</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B396">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>ildemarmarajo</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B397">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>peterson_arrais</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B398">
         <v>0</v>
@@ -5974,28 +5974,154 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
+        <v>zeferinomma</v>
+      </c>
+      <c r="B399">
+        <v>0</v>
+      </c>
+      <c r="C399">
+        <v>1</v>
+      </c>
+      <c r="D399">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>tavaresguu</v>
+      </c>
+      <c r="B400">
+        <v>0</v>
+      </c>
+      <c r="C400">
+        <v>1</v>
+      </c>
+      <c r="D400">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>ildemarmarajo</v>
+      </c>
+      <c r="B401">
+        <v>0</v>
+      </c>
+      <c r="C401">
+        <v>1</v>
+      </c>
+      <c r="D401">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>peterson_arrais</v>
+      </c>
+      <c r="B402">
+        <v>0</v>
+      </c>
+      <c r="C402">
+        <v>1</v>
+      </c>
+      <c r="D402">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
         <v>danieldias7s</v>
       </c>
-      <c r="B399">
-        <v>0</v>
-      </c>
-      <c r="C399">
-        <v>1</v>
-      </c>
-      <c r="D399">
+      <c r="B403">
+        <v>0</v>
+      </c>
+      <c r="C403">
+        <v>1</v>
+      </c>
+      <c r="D403">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>ohanna.anselmo</v>
+      </c>
+      <c r="B404">
+        <v>0</v>
+      </c>
+      <c r="C404">
+        <v>1</v>
+      </c>
+      <c r="D404">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>brun_oguerreiro</v>
+      </c>
+      <c r="B405">
+        <v>0</v>
+      </c>
+      <c r="C405">
+        <v>1</v>
+      </c>
+      <c r="D405">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>helman_mma70</v>
+      </c>
+      <c r="B406">
+        <v>0</v>
+      </c>
+      <c r="C406">
+        <v>1</v>
+      </c>
+      <c r="D406">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>macio.almeida_89</v>
+      </c>
+      <c r="B407">
+        <v>0</v>
+      </c>
+      <c r="C407">
+        <v>1</v>
+      </c>
+      <c r="D407">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>lyviaestherbjj</v>
+      </c>
+      <c r="B408">
+        <v>0</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+      <c r="D408">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D399"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D408"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D103"/>
+  <dimension ref="A1:D113"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6030,7 +6156,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B3">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -6044,7 +6170,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -6058,27 +6184,27 @@
         <v>rm.nicki</v>
       </c>
       <c r="B5">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B6">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
@@ -6086,7 +6212,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -6097,139 +6223,139 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>pedr00jj</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B8">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>23</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>quemuel_ottoni</v>
+        <v>pedr00jj</v>
       </c>
       <c r="B9">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>luis_pequeno_mma</v>
+        <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>pg_grappling</v>
+        <v>luis_pequeno_mma</v>
       </c>
       <c r="B11">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>anaaj_camargo</v>
+        <v>pg_grappling</v>
       </c>
       <c r="B12">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>mmmarc20</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B13">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
         <v>9</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>8</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ryangandraufc</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C14">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>cleyton_jesuss</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C15">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D15">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>marc0s.azv</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B16">
         <v>7</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>combintel</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -6237,49 +6363,49 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>god.motivacao</v>
+        <v>combintel</v>
       </c>
       <c r="B18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C18">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>aline.r15</v>
+        <v>maxgandra</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>irmandadefightteam</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D20">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>excelentfightcompetition</v>
+        <v>aline.r15</v>
       </c>
       <c r="B21">
         <v>2</v>
@@ -6293,10 +6419,10 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>_beegomes_</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B22">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -6307,24 +6433,24 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>maxgandra</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>karen.ottoni</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -6335,7 +6461,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>alfredo_miras</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B25">
         <v>2</v>
@@ -6349,7 +6475,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>badboykillermma</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -6363,7 +6489,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>gra_jpereira</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B27">
         <v>2</v>
@@ -6377,7 +6503,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ninjatheorist</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B28">
         <v>2</v>
@@ -6391,7 +6517,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>z.proddd</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -6400,15 +6526,15 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ronemayanmorais</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -6419,7 +6545,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>pedromadeira.s</v>
+        <v>z.proddd</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -6433,10 +6559,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>livreseseguras</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B32">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -6447,35 +6573,35 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>eliassilverio</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B33">
         <v>1</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>pedrinhosbjj</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B34">
         <v>1</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -6489,7 +6615,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -6503,7 +6629,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>kalindrafaria</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -6512,12 +6638,12 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -6526,12 +6652,12 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>oniszczuk_ko</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -6545,41 +6671,41 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>andreibjj</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>antonioemanuel.13</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C41">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>gasparjr1983</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B42">
         <v>1</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -6587,13 +6713,13 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>andreibjj</v>
       </c>
       <c r="B43">
         <v>1</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -6601,27 +6727,27 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>enzoferrari680</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>gustavomohallem</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -6629,13 +6755,13 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>atlta.marc0s</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -6643,7 +6769,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>arturbambam</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -6657,7 +6783,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -6671,7 +6797,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>hermaan10_</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -6685,7 +6811,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>danieljsantoss_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -6699,7 +6825,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>rodrigojansen_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -6713,7 +6839,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>markakasocks</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -6727,7 +6853,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>hunter.mccrary</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -6741,7 +6867,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>omarcotomaz</v>
+        <v>markakasocks</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -6755,7 +6881,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>alphavillesup</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -6769,7 +6895,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ricieritonan</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -6783,7 +6909,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>lucasampaio</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -6797,7 +6923,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>cjrnavalha</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -6811,7 +6937,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>natalan_wilgner</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -6825,7 +6951,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>manmoska</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -6839,7 +6965,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>renatoevangelistaa</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -6853,7 +6979,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>cassius.paula</v>
+        <v>manmoska</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -6867,7 +6993,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -6881,7 +7007,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>aliferpaulo_</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -6895,7 +7021,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -6909,7 +7035,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>rodrigolidiosales</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -6923,7 +7049,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>moisespira</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -6937,7 +7063,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>marciocatenacci</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -6951,7 +7077,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>cristiane.c.santana</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -6965,7 +7091,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ariel_alvees</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -6979,7 +7105,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>flahvinhotreinador</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -6993,7 +7119,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -7007,7 +7133,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>selma.oscar12</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -7021,69 +7147,69 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>marcos_tailandess</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>tabajaraharu</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>izabeldelfino_</v>
+        <v>magnoddias</v>
       </c>
       <c r="B76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>janjaovix</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>guerreirammaofc</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B78">
         <v>0</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -7091,21 +7217,21 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>benjafloripabjj</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B79">
         <v>0</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>f.ostini</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -7114,12 +7240,12 @@
         <v>1</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>fher.nando_</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -7128,12 +7254,12 @@
         <v>1</v>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>janjaovix</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -7142,12 +7268,12 @@
         <v>1</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>bastazinifilho</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -7156,12 +7282,12 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -7175,7 +7301,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>pammygaryo</v>
+        <v>f.ostini</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -7189,7 +7315,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>anselmo.azevedo</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -7203,7 +7329,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>marcotulio_matuto</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -7217,7 +7343,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>ianrochaf</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -7231,7 +7357,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>ale.lagonegro</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -7245,7 +7371,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>ganemfelipe</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -7259,7 +7385,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -7273,7 +7399,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>marcusvgsz</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -7287,7 +7413,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>wanderson.casttro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -7301,7 +7427,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -7315,7 +7441,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>jotapeamancio</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -7329,7 +7455,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -7343,7 +7469,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -7357,7 +7483,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>zeferinomma</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -7371,7 +7497,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>tavaresguu</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -7385,7 +7511,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>ildemarmarajo</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -7399,7 +7525,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -7413,7 +7539,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>peterson_arrais</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -7427,21 +7553,161 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
+        <v>zeferinomma</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>tavaresguu</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>ildemarmarajo</v>
+      </c>
+      <c r="B105">
+        <v>0</v>
+      </c>
+      <c r="C105">
+        <v>1</v>
+      </c>
+      <c r="D105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>sirleneferreiradiasdias</v>
+      </c>
+      <c r="B106">
+        <v>0</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>peterson_arrais</v>
+      </c>
+      <c r="B107">
+        <v>0</v>
+      </c>
+      <c r="C107">
+        <v>1</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
         <v>danieldias7s</v>
       </c>
-      <c r="B103">
-        <v>0</v>
-      </c>
-      <c r="C103">
-        <v>1</v>
-      </c>
-      <c r="D103">
+      <c r="B108">
+        <v>0</v>
+      </c>
+      <c r="C108">
+        <v>1</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>ohanna.anselmo</v>
+      </c>
+      <c r="B109">
+        <v>0</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>brun_oguerreiro</v>
+      </c>
+      <c r="B110">
+        <v>0</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+      <c r="D110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>helman_mma70</v>
+      </c>
+      <c r="B111">
+        <v>0</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>macio.almeida_89</v>
+      </c>
+      <c r="B112">
+        <v>0</v>
+      </c>
+      <c r="C112">
+        <v>1</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>lyviaestherbjj</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="D113">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D103"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D113"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D408"/>
+  <dimension ref="A1:D433"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
       <c r="D3">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="4">
@@ -447,125 +447,125 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B4">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C4">
         <v>26</v>
       </c>
       <c r="D4">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B5">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>77</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>pablofiorindi</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>188</v>
+        <v>227</v>
       </c>
       <c r="C6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D6">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>pedr00jj</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>167</v>
+        <v>198</v>
       </c>
       <c r="C7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>rpsantos_mma</v>
+        <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C8">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>rm.nicki</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B9">
-        <v>101</v>
+        <v>197</v>
       </c>
       <c r="C9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>92</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>pg_grappling</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B10">
+        <v>107</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
         <v>96</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>hugo7jj</v>
+        <v>pg_grappling</v>
       </c>
       <c r="B11">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>50</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>peacegrappler</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B12">
-        <v>42</v>
+        <v>101</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>41</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -590,7 +590,7 @@
         <v>42</v>
       </c>
       <c r="C14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D14">
         <v>42</v>
@@ -696,30 +696,30 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B22">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C22">
-        <v>6</v>
+        <v>132</v>
       </c>
       <c r="D22">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>god.motivacao</v>
+        <v>aline.r15</v>
       </c>
       <c r="B23">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="C23">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="D23">
-        <v>38</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -794,30 +794,30 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>pedromadeira.s</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B29">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>eliassilverio</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B30">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -836,72 +836,72 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>cjrnavalha</v>
+        <v>maxgandra</v>
       </c>
       <c r="B32">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>maxgandra</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B33">
         <v>12</v>
       </c>
       <c r="C33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>tabajaraharu</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B34">
+        <v>11</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
         <v>6</v>
-      </c>
-      <c r="C34">
-        <v>11</v>
-      </c>
-      <c r="D34">
-        <v>8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>_beegomes_</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B35">
+        <v>6</v>
+      </c>
+      <c r="C35">
+        <v>11</v>
+      </c>
+      <c r="D35">
         <v>8</v>
-      </c>
-      <c r="C35">
-        <v>1</v>
-      </c>
-      <c r="D35">
-        <v>6</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>marc0s.azv</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -1074,27 +1074,27 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>eolucasrosa</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>dagestan0920</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B50">
         <v>5</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -1102,13 +1102,13 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C51">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -1116,27 +1116,27 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>_.maduoliveira_</v>
+        <v>paxlucta</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D52">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D53">
         <v>3</v>
@@ -1144,21 +1144,21 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>glm.barbosa</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>excelentfightcompetition</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B55">
         <v>2</v>
@@ -1172,27 +1172,27 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>marcelogabrielmma</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>_oliveira09_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B57">
         <v>3</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D57">
         <v>3</v>
@@ -1200,72 +1200,72 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C58">
+        <v>4</v>
+      </c>
+      <c r="D58">
         <v>3</v>
-      </c>
-      <c r="D58">
-        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>gabrielsouzamma</v>
+        <v>edebetim_</v>
       </c>
       <c r="B59">
         <v>2</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>alfredo_miras</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>marcos_tailandess</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -1326,13 +1326,13 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>lipe.ftt</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B67">
         <v>4</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -1340,7 +1340,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B68">
         <v>4</v>
@@ -1354,21 +1354,21 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ninjatheorist</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>shawlin13oficial</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B70">
         <v>2</v>
@@ -1377,40 +1377,40 @@
         <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>eduardorodrigrs</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>febrancatti</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>z.proddd</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B74">
         <v>2</v>
@@ -1438,13 +1438,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>dogodoyfoto</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B75">
         <v>2</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -1452,21 +1452,21 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>reifernandes</v>
+        <v>febrancatti</v>
       </c>
       <c r="B76">
         <v>2</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>daniel_dias_214</v>
+        <v>z.proddd</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -1480,13 +1480,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -1494,35 +1494,35 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>alexsandra_kairos</v>
+        <v>reifernandes</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>f.luan_11</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>vitorpetrino</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1536,27 +1536,27 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>jcchagas_</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B82">
         <v>2</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>anderson.logan.35</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B83">
         <v>3</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83">
         <v>0</v>
@@ -1564,80 +1564,80 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>marifferreirac</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>odeivisoncardoso</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>maca.mariotti</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>adriano.trator</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C87">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>s__simone__</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>kaua_limaofc</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C89">
         <v>0</v>
@@ -1648,41 +1648,41 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>clouddhidden</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>lucascardosol__</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B91">
         <v>1</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>ruangzk</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -1690,41 +1690,41 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>livreseseguras</v>
+        <v>s__simone__</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>washington_cassisno</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>ismaeldaniell</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B95">
         <v>2</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D95">
         <v>0</v>
@@ -1732,77 +1732,77 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>douglasipvr_mma</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>tassiogiloficial</v>
+        <v>ruangzk</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>vnciuss__df</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>jhee_dias</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>albertoleandromoco</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100">
         <v>2</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>pauloserrati</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -1816,55 +1816,55 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>fredoctmma</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>diegopaivajj</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>fabaotipster</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B105">
         <v>1</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -1872,69 +1872,69 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>joegam3r</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>mimuniz.bjj</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>orafao1</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D108">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>fabi.godooy</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>leobahiamma</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -1942,77 +1942,77 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>joegam3r</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111">
         <v>0</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
         <v>0</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>heltoncm2002</v>
+        <v>orafao1</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
         <v>0</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>raelduraes</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>aliferpaulo_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115">
         <v>0</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>mineirinho_jj</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,35 +2040,35 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>graalino</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118">
         <v>0</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>lopesbrunao</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119">
         <v>0</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>pedrinhosbjj</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>araujojonaspenhade</v>
+        <v>raelduraes</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,21 +2096,21 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C122">
         <v>0</v>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>jesabelmelo9</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,13 +2124,13 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B124">
         <v>1</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -2138,91 +2138,91 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>treinaadorrafael</v>
+        <v>graalino</v>
       </c>
       <c r="B125">
         <v>1</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>benjafloripabjj</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B126">
         <v>1</v>
       </c>
       <c r="C126">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>fernando.mma</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B127">
         <v>1</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B128">
         <v>1</v>
       </c>
       <c r="C128">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B129">
         <v>1</v>
       </c>
       <c r="C129">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>fagnerosensei</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B130">
         <v>1</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>030sami</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2231,15 +2231,15 @@
         <v>0</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>guiiviieira_</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -2250,27 +2250,27 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>cshigueo</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D134">
         <v>0</v>
@@ -2278,13 +2278,13 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>emerson_lucaszx</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B135">
         <v>1</v>
       </c>
       <c r="C135">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -2292,13 +2292,13 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>danni_goncalves12</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B136">
         <v>1</v>
       </c>
       <c r="C136">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -2306,13 +2306,13 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>mttsm._</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D137">
         <v>0</v>
@@ -2320,13 +2320,13 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>andrealvess02</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D138">
         <v>0</v>
@@ -2334,13 +2334,13 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>gildojiu</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D139">
         <v>0</v>
@@ -2348,13 +2348,13 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>kawannsennast</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B140">
         <v>1</v>
       </c>
       <c r="C140">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D140">
         <v>0</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>yurimartins1_</v>
+        <v>030sami</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>matheusteodoro_1</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>cshigueo</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,13 +2404,13 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>kael_lyto</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>kalindrafaria</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,21 +2432,21 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D146">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>mttsm._</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>oniszczuk_ko</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>andreibjj</v>
+        <v>gildojiu</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,27 +2488,27 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>cristianpsicologo</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B150">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C150">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D150">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>juanx.pontes</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B151">
         <v>1</v>
       </c>
       <c r="C151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -2516,13 +2516,13 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>select_from_joao</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B152">
         <v>1</v>
       </c>
       <c r="C152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -2530,13 +2530,13 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>yeslifeacademia</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B153">
         <v>1</v>
       </c>
       <c r="C153">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -2544,13 +2544,13 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>ojaimerocha</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B154">
         <v>1</v>
       </c>
       <c r="C154">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -2558,21 +2558,21 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>antonioemanuel.13</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C155">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D155">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>gasparjr1983</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2581,18 +2581,18 @@
         <v>1</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B157">
         <v>1</v>
       </c>
       <c r="C157">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D157">
         <v>0</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>tonketjudes</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>_eliasffx</v>
+        <v>andreibjj</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>pdfiv</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,27 +2642,27 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>mariaraimundad940</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D161">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>gabesantos.13</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B162">
         <v>1</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D162">
         <v>0</v>
@@ -2670,13 +2670,13 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>euvitormirandaa</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B163">
         <v>1</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -2684,13 +2684,13 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>thompsonborralho</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B164">
         <v>1</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -2698,13 +2698,13 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>frankikolimabjj</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B165">
         <v>1</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -2712,27 +2712,27 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>alerrandrojj</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>anahangelica</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B167">
         <v>1</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -2740,13 +2740,13 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B168">
         <v>1</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>minotaurinho</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>lara.rpr</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>codasqueves</v>
+        <v>pdfiv</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>yan_touro.7766</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>carolinne.xwp</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>davicorbella</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>artemio_bjj</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>katiaecarreraf</v>
+        <v>anahangelica</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>geraldocnetomma</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,21 +2908,21 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>pedro_pavin_</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C180">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D180">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>xavyeroficial</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>maryanagandra</v>
+        <v>codasqueves</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>eliandropires</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>charlesanthony2466</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>davicorbella</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>draanapaulaponceano</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>saj_photo_miami</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>alternativaremocoes</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>benivalentinn</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,21 +3062,21 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>navarro_9430</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>_puroosso88</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>_rayysp</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>cami.terra_</v>
+        <v>eliandropires</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>gabicardoson</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>martta.mariah</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>wlt_miguel</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>jaonevesz</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>pietroshz</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>___neller</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>_bety_marcal</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>guilhermeefelix__</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>pativinisf</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>judadany</v>
+        <v>_rayysp</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>andre_alcausa</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>_fernunes</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>aloirmarcal</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>gilberto_7606</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>pietroshz</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>flazuera14</v>
+        <v>___neller</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>camii_bonfim</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>danlouiz.jj</v>
+        <v>pativinisf</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>gabriel_trevelin</v>
+        <v>judadany</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>y.arthur_01</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>muricunha</v>
+        <v>_fernunes</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>victorhenriquebjj</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>_lsanchess_</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>__bielgg</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>mr__rlk01</v>
+        <v>flazuera14</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>vitor_buck</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>fran.ruys</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>wesley_bjjvc</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>sambagabrieloficial</v>
+        <v>muricunha</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>_alcantara.bru</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>cesar.boanerges</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>__bielgg</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>alexandreconsentino</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,13 +3622,13 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>rafaela_duaartee</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C231">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D231">
         <v>0</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>andre.legendre.10</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>phillipe.harry</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>andrejetx</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>leandro_motiv4</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>olga.oliveira013</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>leosacraa</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,13 +3748,13 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>gutocriativo</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C240">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D240">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>igorfso_</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>lay_roqs</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>bigjota.artist</v>
+        <v>andrejetx</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>mth_fernandes031</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>turmanmma</v>
+        <v>leosacraa</v>
       </c>
       <c r="B248">
         <v>1</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>gustavomohallem</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B249">
         <v>1</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>atlta.marc0s</v>
+        <v>igorfso_</v>
       </c>
       <c r="B250">
         <v>1</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>arturbambam</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B251">
         <v>1</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>hermaan10_</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B252">
         <v>1</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>danieljsantoss_</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>rodrigojansen_</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>markakasocks</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>hunter.mccrary</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>omarcotomaz</v>
+        <v>turmanmma</v>
       </c>
       <c r="B257">
         <v>1</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>alphavillesup</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>ricieritonan</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>lucasampaio</v>
+        <v>arturbambam</v>
       </c>
       <c r="B260">
         <v>1</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>natalan_wilgner</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B261">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>manmoska</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B262">
         <v>1</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>renatoevangelistaa</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B263">
         <v>1</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>cassius.paula</v>
+        <v>markakasocks</v>
       </c>
       <c r="B264">
         <v>1</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B265">
         <v>1</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>moisespira</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B266">
         <v>1</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>rodrigolidiosales</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B268">
         <v>1</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>marciocatenacci</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B269">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>cristiane.c.santana</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B270">
         <v>1</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>ariel_alvees</v>
+        <v>manmoska</v>
       </c>
       <c r="B271">
         <v>1</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>flahvinhotreinador</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B273">
         <v>1</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>selma.oscar12</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>magnoddias</v>
+        <v>moisespira</v>
       </c>
       <c r="B275">
         <v>1</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>romulobelarmino</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B276">
         <v>1</v>
@@ -4266,13 +4266,13 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>marinealcausa</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B277">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C277">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D277">
         <v>0</v>
@@ -4280,13 +4280,13 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>emersonriosmma</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B278">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C278">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D278">
         <v>0</v>
@@ -4294,55 +4294,55 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>luizcosta_mma</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B279">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C279">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D279">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B280">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C280">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D280">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>giulia.fasolato</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C281">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D281">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>michelle_mirele</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B282">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C282">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D282">
         <v>0</v>
@@ -4350,13 +4350,13 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>danielfranzesilva</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B283">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C283">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D283">
         <v>0</v>
@@ -4364,55 +4364,55 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>ednilsonkaicai</v>
+        <v>magnoddias</v>
       </c>
       <c r="B284">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C284">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D284">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>dayanaa1511</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C285">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D285">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>guerreirammaofc</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B286">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C286">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D286">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C287">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D287">
         <v>0</v>
@@ -4420,55 +4420,55 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>vanessamelomma</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B288">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C288">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D288">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>leonardopateira</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B289">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C289">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D289">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>rahikikhalid</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B290">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C290">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D290">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>manumito.oficial</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B291">
         <v>0</v>
       </c>
       <c r="C291">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D291">
         <v>0</v>
@@ -4476,13 +4476,13 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>carlosnoelblack</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B292">
         <v>0</v>
       </c>
       <c r="C292">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D292">
         <v>0</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -4499,18 +4499,18 @@
         <v>2</v>
       </c>
       <c r="D293">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>lokomemo_protetores</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B294">
         <v>0</v>
       </c>
       <c r="C294">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D294">
         <v>1</v>
@@ -4518,27 +4518,27 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>coutz11</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B295">
         <v>0</v>
       </c>
       <c r="C295">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D295">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>orlando_alfa09</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B296">
         <v>0</v>
       </c>
       <c r="C296">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D296">
         <v>0</v>
@@ -4546,13 +4546,13 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>vitorshowman</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B297">
         <v>0</v>
       </c>
       <c r="C297">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D297">
         <v>0</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>4lissson</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -4569,18 +4569,18 @@
         <v>2</v>
       </c>
       <c r="D298">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>danilofernandescf</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B299">
         <v>0</v>
       </c>
       <c r="C299">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D299">
         <v>1</v>
@@ -4588,13 +4588,13 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>bryandazuera</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B300">
         <v>0</v>
       </c>
       <c r="C300">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D300">
         <v>1</v>
@@ -4602,21 +4602,21 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>ommariotti</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B301">
         <v>0</v>
       </c>
       <c r="C301">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D301">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>brodschack_</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B302">
         <v>0</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>_vpft</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B303">
         <v>0</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>izabeldelfino_</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B304">
         <v>0</v>
@@ -4658,41 +4658,41 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>janjaovix</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B305">
         <v>0</v>
       </c>
       <c r="C305">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D305">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B306">
         <v>0</v>
       </c>
       <c r="C306">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D306">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B307">
         <v>0</v>
       </c>
       <c r="C307">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>helenaseveribjj</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4709,12 +4709,12 @@
         <v>1</v>
       </c>
       <c r="D308">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>_kainanlima</v>
+        <v>coutz11</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4723,18 +4723,18 @@
         <v>1</v>
       </c>
       <c r="D309">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>jimmy_indioap</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B310">
         <v>0</v>
       </c>
       <c r="C310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D310">
         <v>0</v>
@@ -4742,13 +4742,13 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>omar_alneaimi</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B311">
         <v>0</v>
       </c>
       <c r="C311">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D311">
         <v>0</v>
@@ -4756,13 +4756,13 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>victor_brunopersonal</v>
+        <v>4lissson</v>
       </c>
       <c r="B312">
         <v>0</v>
       </c>
       <c r="C312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>motumbo_team</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4779,12 +4779,12 @@
         <v>1</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>vanemessina</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4793,12 +4793,12 @@
         <v>1</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>dadwillians</v>
+        <v>ommariotti</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4807,12 +4807,12 @@
         <v>1</v>
       </c>
       <c r="D315">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>thalytabjj</v>
+        <v>brodschack_</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4821,12 +4821,12 @@
         <v>1</v>
       </c>
       <c r="D316">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>esteticaluharruda</v>
+        <v>_vpft</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4835,12 +4835,12 @@
         <v>1</v>
       </c>
       <c r="D317">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>chubotaru_lilu</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4849,12 +4849,12 @@
         <v>1</v>
       </c>
       <c r="D318">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>eusoufernandosaito</v>
+        <v>janjaovix</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4863,12 +4863,12 @@
         <v>1</v>
       </c>
       <c r="D319">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>dandraco_</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4877,12 +4877,12 @@
         <v>1</v>
       </c>
       <c r="D320">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4891,12 +4891,12 @@
         <v>1</v>
       </c>
       <c r="D321">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>sejamotivadorofc</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>tpapereira</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>kfcampeoes</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>herrickmarinho</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>rafaelcmjj</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>cristianomarcello</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>_gabrielpego</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>taylor_71kg</v>
+        <v>vanemessina</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>dadwillians</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>doraasivla</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>pe.mirandas</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>leaoanaalice</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>caioparangole</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B334">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>sabrinaalsilva</v>
+        <v>dandraco_</v>
       </c>
       <c r="B335">
         <v>0</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>eglaudiomma</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>strong_stg_oficial</v>
+        <v>tpapereira</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>ricardotofanello</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>taporondebruno</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>anamatias.m</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>claudio_marchese_7</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>1000ton_n</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>paulo.titoo</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B344">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>vitorcosta_mma</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B345">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>couragemma</v>
+        <v>doraasivla</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>romulerasilva</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>edergama.mma</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>alineanne_</v>
+        <v>caioparangole</v>
       </c>
       <c r="B349">
         <v>0</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>julckreis</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B350">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>andreza.thais.1</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B351">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>benicius_edu</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B352">
         <v>0</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>michele_mixa</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>joaolauar_</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>igorbrasileiro01</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B356">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>felipeocalmon</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>rejr_mma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>deivssonmanin</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B359">
         <v>0</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>andrey_m_s_</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B360">
         <v>0</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>vidaldanin</v>
+        <v>couragemma</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>barbaracontadora</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>natalves5</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B363">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>alineanne_</v>
       </c>
       <c r="B364">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>boradepodcastoficial</v>
+        <v>julckreis</v>
       </c>
       <c r="B365">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>audizioandrade</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B366">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>isadoragolimpio</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B367">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>dudu.acabamentos</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B368">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>katlembrenda</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B369">
         <v>0</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>aline.amaral21</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B370">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>tamysregina</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B371">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>guilhermews1994</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B372">
         <v>0</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>percepcar</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B373">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>kevin.mota95</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B374">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>_marcos_.71</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B375">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>douglas_vitor8</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B376">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B377">
         <v>0</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>raulcarvalho1010</v>
+        <v>natalves5</v>
       </c>
       <c r="B378">
         <v>0</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>roginbrito</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B379">
         <v>0</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>meirelesmma</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B380">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>dvlucc2k26_</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B381">
         <v>0</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>armysenju</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B382">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>f.ostini</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B383">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>fher.nando_</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B384">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>bastazinifilho</v>
+        <v>tamysregina</v>
       </c>
       <c r="B386">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>pammygaryo</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B387">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>anselmo.azevedo</v>
+        <v>percepcar</v>
       </c>
       <c r="B388">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>marcotulio_matuto</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B389">
         <v>0</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>ianrochaf</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B390">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>ale.lagonegro</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B391">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>ganemfelipe</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B392">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>marcusvgsz</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B393">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>wanderson.casttro</v>
+        <v>roginbrito</v>
       </c>
       <c r="B394">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B395">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>jotapeamancio</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B396">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>armysenju</v>
       </c>
       <c r="B397">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>f.ostini</v>
       </c>
       <c r="B398">
         <v>0</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>zeferinomma</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B399">
         <v>0</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>tavaresguu</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B400">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>ildemarmarajo</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B401">
         <v>0</v>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>peterson_arrais</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B402">
         <v>0</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>danieldias7s</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B403">
         <v>0</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>ohanna.anselmo</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B404">
         <v>0</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B405">
         <v>0</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>helman_mma70</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B406">
         <v>0</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>macio.almeida_89</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B407">
         <v>0</v>
@@ -6100,28 +6100,378 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
+        <v>marcusvgsz</v>
+      </c>
+      <c r="B408">
+        <v>0</v>
+      </c>
+      <c r="C408">
+        <v>1</v>
+      </c>
+      <c r="D408">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>wanderson.casttro</v>
+      </c>
+      <c r="B409">
+        <v>0</v>
+      </c>
+      <c r="C409">
+        <v>1</v>
+      </c>
+      <c r="D409">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>fabio.sampaio.90260</v>
+      </c>
+      <c r="B410">
+        <v>0</v>
+      </c>
+      <c r="C410">
+        <v>1</v>
+      </c>
+      <c r="D410">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>jotapeamancio</v>
+      </c>
+      <c r="B411">
+        <v>0</v>
+      </c>
+      <c r="C411">
+        <v>1</v>
+      </c>
+      <c r="D411">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>kaynankruschewsky_ufc</v>
+      </c>
+      <c r="B412">
+        <v>0</v>
+      </c>
+      <c r="C412">
+        <v>1</v>
+      </c>
+      <c r="D412">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>vitorpaes_personalfight</v>
+      </c>
+      <c r="B413">
+        <v>0</v>
+      </c>
+      <c r="C413">
+        <v>1</v>
+      </c>
+      <c r="D413">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>zeferinomma</v>
+      </c>
+      <c r="B414">
+        <v>0</v>
+      </c>
+      <c r="C414">
+        <v>1</v>
+      </c>
+      <c r="D414">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>tavaresguu</v>
+      </c>
+      <c r="B415">
+        <v>0</v>
+      </c>
+      <c r="C415">
+        <v>1</v>
+      </c>
+      <c r="D415">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>ildemarmarajo</v>
+      </c>
+      <c r="B416">
+        <v>0</v>
+      </c>
+      <c r="C416">
+        <v>1</v>
+      </c>
+      <c r="D416">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>peterson_arrais</v>
+      </c>
+      <c r="B417">
+        <v>0</v>
+      </c>
+      <c r="C417">
+        <v>1</v>
+      </c>
+      <c r="D417">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>danieldias7s</v>
+      </c>
+      <c r="B418">
+        <v>0</v>
+      </c>
+      <c r="C418">
+        <v>1</v>
+      </c>
+      <c r="D418">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>ohanna.anselmo</v>
+      </c>
+      <c r="B419">
+        <v>0</v>
+      </c>
+      <c r="C419">
+        <v>1</v>
+      </c>
+      <c r="D419">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>brun_oguerreiro</v>
+      </c>
+      <c r="B420">
+        <v>0</v>
+      </c>
+      <c r="C420">
+        <v>1</v>
+      </c>
+      <c r="D420">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>helman_mma70</v>
+      </c>
+      <c r="B421">
+        <v>0</v>
+      </c>
+      <c r="C421">
+        <v>1</v>
+      </c>
+      <c r="D421">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>macio.almeida_89</v>
+      </c>
+      <c r="B422">
+        <v>0</v>
+      </c>
+      <c r="C422">
+        <v>1</v>
+      </c>
+      <c r="D422">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
         <v>lyviaestherbjj</v>
       </c>
-      <c r="B408">
-        <v>0</v>
-      </c>
-      <c r="C408">
-        <v>1</v>
-      </c>
-      <c r="D408">
+      <c r="B423">
+        <v>0</v>
+      </c>
+      <c r="C423">
+        <v>1</v>
+      </c>
+      <c r="D423">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>wendel_bjj14</v>
+      </c>
+      <c r="B424">
+        <v>0</v>
+      </c>
+      <c r="C424">
+        <v>1</v>
+      </c>
+      <c r="D424">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>karine_killer_ufc</v>
+      </c>
+      <c r="B425">
+        <v>0</v>
+      </c>
+      <c r="C425">
+        <v>1</v>
+      </c>
+      <c r="D425">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>andressa_bjj_</v>
+      </c>
+      <c r="B426">
+        <v>0</v>
+      </c>
+      <c r="C426">
+        <v>1</v>
+      </c>
+      <c r="D426">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>dreamartpro</v>
+      </c>
+      <c r="B427">
+        <v>0</v>
+      </c>
+      <c r="C427">
+        <v>1</v>
+      </c>
+      <c r="D427">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>makelele_bjj</v>
+      </c>
+      <c r="B428">
+        <v>0</v>
+      </c>
+      <c r="C428">
+        <v>1</v>
+      </c>
+      <c r="D428">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>fdanieljj</v>
+      </c>
+      <c r="B429">
+        <v>0</v>
+      </c>
+      <c r="C429">
+        <v>1</v>
+      </c>
+      <c r="D429">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>jeferson_tijolo1</v>
+      </c>
+      <c r="B430">
+        <v>0</v>
+      </c>
+      <c r="C430">
+        <v>1</v>
+      </c>
+      <c r="D430">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>caioleonjj</v>
+      </c>
+      <c r="B431">
+        <v>0</v>
+      </c>
+      <c r="C431">
+        <v>1</v>
+      </c>
+      <c r="D431">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>kevinlopes_bjj</v>
+      </c>
+      <c r="B432">
+        <v>0</v>
+      </c>
+      <c r="C432">
+        <v>1</v>
+      </c>
+      <c r="D432">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>malene_elleen</v>
+      </c>
+      <c r="B433">
+        <v>0</v>
+      </c>
+      <c r="C433">
+        <v>1</v>
+      </c>
+      <c r="D433">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D408"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D433"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D113"/>
+  <dimension ref="A1:D140"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6153,58 +6503,58 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>hugo7jj</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>pablofiorindi</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B4">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>rm.nicki</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B5">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>56</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>peacegrappler</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B6">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>41</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -6212,7 +6562,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -6226,7 +6576,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B8">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -6240,13 +6590,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B9">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10">
@@ -6254,13 +6604,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C10">
         <v>4</v>
       </c>
       <c r="D10">
-        <v>28</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11">
@@ -6268,13 +6618,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B11">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -6282,13 +6632,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B12">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -6321,44 +6671,44 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ryangandraufc</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B15">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C15">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>cleyton_jesuss</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C16">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>marc0s.azv</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B17">
         <v>7</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
@@ -6377,30 +6727,30 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>maxgandra</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D19">
-        <v>1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>god.motivacao</v>
+        <v>maxgandra</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -6489,35 +6839,35 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>badboykillermma</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>gra_jpereira</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ninjatheorist</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B29">
         <v>2</v>
@@ -6531,21 +6881,21 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>pedromadeira.s</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>z.proddd</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -6554,15 +6904,15 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ronemayanmorais</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -6573,38 +6923,38 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>livreseseguras</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B33">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>eliassilverio</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B34">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>pedrinhosbjj</v>
+        <v>z.proddd</v>
       </c>
       <c r="B35">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -6615,24 +6965,24 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>araujojonaspenhade</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B37">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -6643,21 +6993,21 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>jesabelmelo9</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>kalindrafaria</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -6666,26 +7016,26 @@
         <v>0</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B40">
         <v>1</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -6694,12 +7044,12 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>oniszczuk_ko</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -6708,12 +7058,12 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>andreibjj</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -6722,46 +7072,46 @@
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>antonioemanuel.13</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B44">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>gasparjr1983</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -6769,13 +7119,13 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>enzoferrari680</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -6783,7 +7133,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>gustavomohallem</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -6797,21 +7147,21 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>atlta.marc0s</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>arturbambam</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -6825,7 +7175,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>hermaan10_</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -6839,7 +7189,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>danieljsantoss_</v>
+        <v>andreibjj</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -6853,7 +7203,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>rodrigojansen_</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -6867,27 +7217,27 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>markakasocks</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>hunter.mccrary</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B55">
         <v>1</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -6895,13 +7245,13 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>omarcotomaz</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -6909,7 +7259,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>alphavillesup</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -6923,7 +7273,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ricieritonan</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -6937,7 +7287,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>lucasampaio</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -6951,7 +7301,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>cjrnavalha</v>
+        <v>arturbambam</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -6965,7 +7315,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>natalan_wilgner</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -6979,7 +7329,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>manmoska</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -6993,7 +7343,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>renatoevangelistaa</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -7007,7 +7357,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>cassius.paula</v>
+        <v>markakasocks</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -7021,7 +7371,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -7035,7 +7385,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>aliferpaulo_</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -7049,7 +7399,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>moisespira</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -7063,7 +7413,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>rodrigolidiosales</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -7077,7 +7427,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -7091,7 +7441,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>marciocatenacci</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -7105,7 +7455,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>cristiane.c.santana</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -7119,7 +7469,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ariel_alvees</v>
+        <v>manmoska</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -7133,7 +7483,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>flahvinhotreinador</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -7147,7 +7497,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -7161,7 +7511,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>selma.oscar12</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -7175,7 +7525,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>magnoddias</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -7189,7 +7539,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>romulobelarmino</v>
+        <v>moisespira</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -7203,97 +7553,97 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>marcos_tailandess</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>guerreirammaofc</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>tabajaraharu</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>izabeldelfino_</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>janjaovix</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>benjafloripabjj</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84">
         <v>0</v>
@@ -7301,13 +7651,13 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>f.ostini</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D85">
         <v>0</v>
@@ -7315,13 +7665,13 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>fher.nando_</v>
+        <v>magnoddias</v>
       </c>
       <c r="B86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86">
         <v>0</v>
@@ -7329,13 +7679,13 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -7343,13 +7693,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>bastazinifilho</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -7357,13 +7707,13 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -7371,13 +7721,13 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>pammygaryo</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -7385,13 +7735,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>anselmo.azevedo</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -7399,13 +7749,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>marcotulio_matuto</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -7413,13 +7763,13 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>ianrochaf</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>0</v>
@@ -7427,13 +7777,13 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>ale.lagonegro</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94">
         <v>0</v>
@@ -7441,21 +7791,21 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>ganemfelipe</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B95">
         <v>0</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -7464,12 +7814,12 @@
         <v>1</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>marcusvgsz</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -7478,12 +7828,12 @@
         <v>1</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>wanderson.casttro</v>
+        <v>janjaovix</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -7492,12 +7842,12 @@
         <v>1</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B99">
         <v>0</v>
@@ -7506,12 +7856,12 @@
         <v>1</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>jotapeamancio</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B100">
         <v>0</v>
@@ -7520,12 +7870,12 @@
         <v>1</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B101">
         <v>0</v>
@@ -7539,7 +7889,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>f.ostini</v>
       </c>
       <c r="B102">
         <v>0</v>
@@ -7553,7 +7903,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>zeferinomma</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B103">
         <v>0</v>
@@ -7567,7 +7917,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>tavaresguu</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -7581,7 +7931,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ildemarmarajo</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -7595,7 +7945,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -7609,7 +7959,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>peterson_arrais</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B107">
         <v>0</v>
@@ -7623,7 +7973,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>danieldias7s</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B108">
         <v>0</v>
@@ -7637,7 +7987,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>ohanna.anselmo</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B109">
         <v>0</v>
@@ -7651,7 +8001,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B110">
         <v>0</v>
@@ -7665,7 +8015,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>helman_mma70</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B111">
         <v>0</v>
@@ -7679,7 +8029,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>macio.almeida_89</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -7693,21 +8043,399 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
+        <v>flavio.dequeiroz</v>
+      </c>
+      <c r="B113">
+        <v>0</v>
+      </c>
+      <c r="C113">
+        <v>1</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>marcusvgsz</v>
+      </c>
+      <c r="B114">
+        <v>0</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="D114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>wanderson.casttro</v>
+      </c>
+      <c r="B115">
+        <v>0</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>fabio.sampaio.90260</v>
+      </c>
+      <c r="B116">
+        <v>0</v>
+      </c>
+      <c r="C116">
+        <v>1</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>jotapeamancio</v>
+      </c>
+      <c r="B117">
+        <v>0</v>
+      </c>
+      <c r="C117">
+        <v>1</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>kaynankruschewsky_ufc</v>
+      </c>
+      <c r="B118">
+        <v>0</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>vitorpaes_personalfight</v>
+      </c>
+      <c r="B119">
+        <v>0</v>
+      </c>
+      <c r="C119">
+        <v>1</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>zeferinomma</v>
+      </c>
+      <c r="B120">
+        <v>0</v>
+      </c>
+      <c r="C120">
+        <v>1</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>tavaresguu</v>
+      </c>
+      <c r="B121">
+        <v>0</v>
+      </c>
+      <c r="C121">
+        <v>1</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>ildemarmarajo</v>
+      </c>
+      <c r="B122">
+        <v>0</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>sirleneferreiradiasdias</v>
+      </c>
+      <c r="B123">
+        <v>0</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>peterson_arrais</v>
+      </c>
+      <c r="B124">
+        <v>0</v>
+      </c>
+      <c r="C124">
+        <v>1</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>danieldias7s</v>
+      </c>
+      <c r="B125">
+        <v>0</v>
+      </c>
+      <c r="C125">
+        <v>1</v>
+      </c>
+      <c r="D125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>ohanna.anselmo</v>
+      </c>
+      <c r="B126">
+        <v>0</v>
+      </c>
+      <c r="C126">
+        <v>1</v>
+      </c>
+      <c r="D126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>brun_oguerreiro</v>
+      </c>
+      <c r="B127">
+        <v>0</v>
+      </c>
+      <c r="C127">
+        <v>1</v>
+      </c>
+      <c r="D127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>helman_mma70</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="D128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>macio.almeida_89</v>
+      </c>
+      <c r="B129">
+        <v>0</v>
+      </c>
+      <c r="C129">
+        <v>1</v>
+      </c>
+      <c r="D129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
         <v>lyviaestherbjj</v>
       </c>
-      <c r="B113">
-        <v>0</v>
-      </c>
-      <c r="C113">
-        <v>1</v>
-      </c>
-      <c r="D113">
+      <c r="B130">
+        <v>0</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+      <c r="D130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>wendel_bjj14</v>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="D131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>karine_killer_ufc</v>
+      </c>
+      <c r="B132">
+        <v>0</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+      <c r="D132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>andressa_bjj_</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+      <c r="D133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>dreamartpro</v>
+      </c>
+      <c r="B134">
+        <v>0</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+      <c r="D134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>makelele_bjj</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+      <c r="D135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>fdanieljj</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+      <c r="D136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>jeferson_tijolo1</v>
+      </c>
+      <c r="B137">
+        <v>0</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>caioleonjj</v>
+      </c>
+      <c r="B138">
+        <v>0</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+      <c r="D138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>kevinlopes_bjj</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+      <c r="D139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>malene_elleen</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D113"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D140"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D433"/>
+  <dimension ref="A1:D446"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,41 +433,41 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="C3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>luis_pequeno_mma</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B4">
-        <v>335</v>
+        <v>259</v>
       </c>
       <c r="C4">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>43</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>peacegrappler</v>
+        <v>luis_pequeno_mma</v>
       </c>
       <c r="B5">
-        <v>182</v>
+        <v>344</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D5">
-        <v>181</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -475,13 +475,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="C6">
         <v>9</v>
       </c>
       <c r="D6">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7">
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="C7">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -503,13 +503,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="9">
@@ -517,13 +517,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B9">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -531,13 +531,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -545,13 +545,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B11">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12">
@@ -559,7 +559,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B12">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -587,13 +587,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
@@ -601,7 +601,7 @@
         <v>irmandadefightteam</v>
       </c>
       <c r="B15">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -615,13 +615,13 @@
         <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -671,7 +671,7 @@
         <v>kaua_limamma</v>
       </c>
       <c r="B20">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -685,41 +685,41 @@
         <v>combintel</v>
       </c>
       <c r="B21">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21">
         <v>1</v>
       </c>
       <c r="D21">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>god.motivacao</v>
+        <v>aline.r15</v>
       </c>
       <c r="B22">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C22">
-        <v>132</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>42</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B23">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="C23">
-        <v>6</v>
+        <v>136</v>
       </c>
       <c r="D23">
-        <v>7</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24">
@@ -741,13 +741,13 @@
         <v>gra_jpereira</v>
       </c>
       <c r="B25">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C25">
         <v>2</v>
       </c>
       <c r="D25">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
@@ -769,13 +769,13 @@
         <v>alvesmidih</v>
       </c>
       <c r="B27">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -808,13 +808,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>pedromadeira.s</v>
+        <v>maxgandra</v>
       </c>
       <c r="B30">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D30">
         <v>6</v>
@@ -822,30 +822,30 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B31">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C31">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>maxgandra</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B32">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -881,13 +881,13 @@
         <v>tabajaraharu</v>
       </c>
       <c r="B35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35">
         <v>11</v>
       </c>
       <c r="D35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36">
@@ -906,13 +906,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>tawanregismma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B37">
         <v>7</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -920,13 +920,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>karen.ottoni</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B38">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -934,52 +934,52 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>rrafaelins</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B39">
+        <v>5</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
         <v>4</v>
-      </c>
-      <c r="C39">
-        <v>4</v>
-      </c>
-      <c r="D39">
-        <v>5</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B40">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>italothearcher</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C41">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>vndcardoso</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -990,58 +990,58 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>juniordiasmma</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B43">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>badboykillermma</v>
+        <v>italothearcher</v>
       </c>
       <c r="B44">
         <v>4</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D44">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>gdazuera</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>enzoferrari680</v>
+        <v>gdazuera</v>
       </c>
       <c r="B46">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47">
@@ -1060,69 +1060,69 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B48">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>marcos_tailandess</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C49">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>eolucasrosa</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>dagestan0920</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>paxlucta</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C52">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -1130,69 +1130,69 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>_.maduoliveira_</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>paxlucta</v>
       </c>
       <c r="B54">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>glm.barbosa</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>excelentfightcompetition</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D56">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>marcelogabrielmma</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B57">
         <v>3</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D57">
         <v>3</v>
@@ -1206,10 +1206,10 @@
         <v>3</v>
       </c>
       <c r="C58">
+        <v>5</v>
+      </c>
+      <c r="D58">
         <v>4</v>
-      </c>
-      <c r="D58">
-        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1220,21 +1220,21 @@
         <v>2</v>
       </c>
       <c r="C59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>gabrielsouzamma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -1242,27 +1242,27 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>salost.ofc</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>alfredo_miras</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -1270,13 +1270,13 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>ravenrodriguez___</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C63">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -1284,27 +1284,27 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>fabinho_falcao_</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B64">
         <v>2</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -1312,27 +1312,27 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B67">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -1340,13 +1340,13 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>lipe.ftt</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B68">
         <v>4</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B69">
         <v>4</v>
@@ -1368,77 +1368,77 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ninjatheorist</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>_pizzariabambina_</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B72">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>shawlin13oficial</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>eduardorodrigrs</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B74">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B75">
         <v>2</v>
@@ -1447,12 +1447,12 @@
         <v>0</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>febrancatti</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -1461,12 +1461,12 @@
         <v>0</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>z.proddd</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -1480,13 +1480,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>dogodoyfoto</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B78">
         <v>2</v>
       </c>
       <c r="C78">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -1494,21 +1494,21 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>reifernandes</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B79">
         <v>2</v>
       </c>
       <c r="C79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>daniel_dias_214</v>
+        <v>febrancatti</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>z.proddd</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1536,83 +1536,83 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>alexsandra_kairos</v>
+        <v>reifernandes</v>
       </c>
       <c r="B82">
         <v>2</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>multiplicaaba</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>f.luan_11</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>vitorpetrino</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>jcchagas_</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B86">
         <v>2</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>anderson.logan.35</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B87">
         <v>3</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -1620,69 +1620,69 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>marifferreirac</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>meol.socialmidia</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>odeivisoncardoso</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>maca.mariotti</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B91">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C91">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>adriano.trator</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B92">
         <v>1</v>
       </c>
       <c r="C92">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>s__simone__</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -1704,111 +1704,111 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>kaua_limaofc</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C94">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>clouddhidden</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>lucascardosol__</v>
+        <v>s__simone__</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>ruangzk</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97">
         <v>0</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>livreseseguras</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>washington_cassisno</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B99">
         <v>1</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>ismaeldaniell</v>
+        <v>ruangzk</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>douglasipvr_mma</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D101">
         <v>2</v>
@@ -1816,13 +1816,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>tassiogiloficial</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B102">
         <v>2</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -1830,21 +1830,21 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>vnciuss__df</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>jhee_dias</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B104">
         <v>2</v>
@@ -1858,49 +1858,49 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>albertoleandromoco</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>pauloserrati</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B107">
         <v>1</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>fredoctmma</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -1909,26 +1909,26 @@
         <v>1</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>diegopaivajj</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>fabaotipster</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,35 +1942,35 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>joegam3r</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B111">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>mimuniz.bjj</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>orafao1</v>
+        <v>joegam3r</v>
       </c>
       <c r="B113">
         <v>2</v>
@@ -1984,7 +1984,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>fabi.godooy</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B114">
         <v>2</v>
@@ -1998,35 +1998,35 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>leobahiamma</v>
+        <v>orafao1</v>
       </c>
       <c r="B115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115">
         <v>0</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116">
         <v>0</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -2040,63 +2040,63 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>wlt_miguel</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C118">
         <v>0</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B119">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C119">
         <v>0</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>heltoncm2002</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C120">
         <v>0</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>raelduraes</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121">
         <v>0</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>aliferpaulo_</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B122">
         <v>2</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>mineirinho_jj</v>
+        <v>raelduraes</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,21 +2138,21 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>graalino</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125">
         <v>0</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>lopesbrunao</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>pedrinhosbjj</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>araujojonaspenhade</v>
+        <v>graalino</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>jesabelmelo9</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>marcocanatelli</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,27 +2236,27 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>pvd_._dudis</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C132">
         <v>0</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B133">
         <v>1</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -2264,27 +2264,27 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>treinaadorrafael</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B134">
         <v>1</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>benjafloripabjj</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D135">
         <v>0</v>
@@ -2292,13 +2292,13 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>fernando.mma</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D136">
         <v>0</v>
@@ -2306,83 +2306,83 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>sr.valter</v>
       </c>
       <c r="B137">
         <v>1</v>
       </c>
       <c r="C137">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>estevaotoledo</v>
+        <v>devessonjj</v>
       </c>
       <c r="B138">
         <v>1</v>
       </c>
       <c r="C138">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B139">
         <v>1</v>
       </c>
       <c r="C139">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>fagnerosensei</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B140">
         <v>1</v>
       </c>
       <c r="C140">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>030sami</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>guiiviieira_</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D142">
         <v>0</v>
@@ -2390,13 +2390,13 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>cshigueo</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -2404,13 +2404,13 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -2418,13 +2418,13 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>emerson_lucaszx</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -2432,13 +2432,13 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>danni_goncalves12</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -2446,13 +2446,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>mttsm._</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -2460,13 +2460,13 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>andrealvess02</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B148">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>gildojiu</v>
+        <v>030sami</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>kawannsennast</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>yurimartins1_</v>
+        <v>cshigueo</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>matheusteodoro_1</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,13 +2544,13 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>kael_lyto</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B154">
         <v>1</v>
       </c>
       <c r="C154">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>kalindrafaria</v>
+        <v>mttsm._</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,21 +2572,21 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B156">
         <v>1</v>
       </c>
       <c r="C156">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D156">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>gildojiu</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>oniszczuk_ko</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>andreibjj</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>chuck_tlp</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,27 +2642,27 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>cristianpsicologo</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C161">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D161">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>juanx.pontes</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B162">
         <v>1</v>
       </c>
       <c r="C162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D162">
         <v>0</v>
@@ -2670,13 +2670,13 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>select_from_joao</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B163">
         <v>1</v>
       </c>
       <c r="C163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>yeslifeacademia</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2693,18 +2693,18 @@
         <v>1</v>
       </c>
       <c r="D164">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>ojaimerocha</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B165">
         <v>1</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -2712,27 +2712,27 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>antonioemanuel.13</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C166">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D166">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>gasparjr1983</v>
+        <v>andreibjj</v>
       </c>
       <c r="B167">
         <v>1</v>
       </c>
       <c r="C167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -2740,13 +2740,13 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B168">
         <v>1</v>
       </c>
       <c r="C168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -2754,27 +2754,27 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>tonketjudes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>_eliasffx</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B170">
         <v>1</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D170">
         <v>0</v>
@@ -2782,13 +2782,13 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>pdfiv</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B171">
         <v>1</v>
       </c>
       <c r="C171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D171">
         <v>0</v>
@@ -2796,13 +2796,13 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>mariaraimundad940</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B172">
         <v>1</v>
       </c>
       <c r="C172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D172">
         <v>0</v>
@@ -2810,13 +2810,13 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>gabesantos.13</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B173">
         <v>1</v>
       </c>
       <c r="C173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D173">
         <v>0</v>
@@ -2824,27 +2824,27 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>euvitormirandaa</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C174">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>thompsonborralho</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B175">
         <v>1</v>
       </c>
       <c r="C175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D175">
         <v>0</v>
@@ -2852,13 +2852,13 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>frankikolimabjj</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B176">
         <v>1</v>
       </c>
       <c r="C176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -2866,13 +2866,13 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>alerrandrojj</v>
+        <v>magnoddias</v>
       </c>
       <c r="B177">
         <v>1</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>anahangelica</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>minotaurinho</v>
+        <v>pdfiv</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>lara.rpr</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>codasqueves</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>yan_touro.7766</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>carolinne.xwp</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>davicorbella</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>anahangelica</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>artemio_bjj</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>katiaecarreraf</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>geraldocnetomma</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,21 +3062,21 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>pedro_pavin_</v>
+        <v>codasqueves</v>
       </c>
       <c r="B191">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C191">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D191">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>xavyeroficial</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>maryanagandra</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>eliandropires</v>
+        <v>davicorbella</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>charlesanthony2466</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>draanapaulaponceano</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>saj_photo_miami</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>alternativaremocoes</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,21 +3188,21 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>benivalentinn</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C200">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D200">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>navarro_9430</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>_puroosso88</v>
+        <v>eliandropires</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>_rayysp</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>cami.terra_</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>gabicardoson</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>martta.mariah</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>jaonevesz</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>pietroshz</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>___neller</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>_bety_marcal</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>pativinisf</v>
+        <v>_rayysp</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>judadany</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>andre_alcausa</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>_fernunes</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>aloirmarcal</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>gilberto_7606</v>
+        <v>pietroshz</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>___neller</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>flazuera14</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>camii_bonfim</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>danlouiz.jj</v>
+        <v>pativinisf</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>gabriel_trevelin</v>
+        <v>judadany</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>y.arthur_01</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>muricunha</v>
+        <v>_fernunes</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>victorhenriquebjj</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>_lsanchess_</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>__bielgg</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>mr__rlk01</v>
+        <v>flazuera14</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>vitor_buck</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>fran.ruys</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>wesley_bjjvc</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>sambagabrieloficial</v>
+        <v>muricunha</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>_alcantara.bru</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>cesar.boanerges</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>__bielgg</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>alexandreconsentino</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,13 +3748,13 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>rafaela_duaartee</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C240">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D240">
         <v>0</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>andre.legendre.10</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>phillipe.harry</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>andrejetx</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>leandro_motiv4</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>olga.oliveira013</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -3860,13 +3860,13 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>leosacraa</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B248">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C248">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D248">
         <v>0</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>gutocriativo</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B249">
         <v>1</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>igorfso_</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B250">
         <v>1</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B251">
         <v>1</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>lay_roqs</v>
+        <v>andrejetx</v>
       </c>
       <c r="B252">
         <v>1</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>bigjota.artist</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>mth_fernandes031</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>leosacraa</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>turmanmma</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B257">
         <v>1</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>gustavomohallem</v>
+        <v>igorfso_</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>atlta.marc0s</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>arturbambam</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B260">
         <v>1</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>hermaan10_</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B261">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>danieljsantoss_</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B262">
         <v>1</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>rodrigojansen_</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B263">
         <v>1</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>markakasocks</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B264">
         <v>1</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>hunter.mccrary</v>
+        <v>turmanmma</v>
       </c>
       <c r="B265">
         <v>1</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>omarcotomaz</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B266">
         <v>1</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>alphavillesup</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>ricieritonan</v>
+        <v>arturbambam</v>
       </c>
       <c r="B268">
         <v>1</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>lucasampaio</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B269">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>natalan_wilgner</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B270">
         <v>1</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>manmoska</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B271">
         <v>1</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>renatoevangelistaa</v>
+        <v>markakasocks</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>cassius.paula</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B273">
         <v>1</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>moisespira</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B275">
         <v>1</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>rodrigolidiosales</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B276">
         <v>1</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B277">
         <v>1</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>marciocatenacci</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B278">
         <v>1</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>cristiane.c.santana</v>
+        <v>manmoska</v>
       </c>
       <c r="B279">
         <v>1</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>ariel_alvees</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B280">
         <v>1</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>flahvinhotreinador</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B281">
         <v>1</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B282">
         <v>1</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>selma.oscar12</v>
+        <v>moisespira</v>
       </c>
       <c r="B283">
         <v>1</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>magnoddias</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B284">
         <v>1</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>romulobelarmino</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B285">
         <v>1</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>fernandamourabjj</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B286">
         <v>1</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>larissamartinsbjj</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B287">
         <v>1</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B288">
         <v>1</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>leitefelippez</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B289">
         <v>1</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>israelbahiensebraz</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -4462,13 +4462,13 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>marinealcausa</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B291">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C291">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D291">
         <v>0</v>
@@ -4476,13 +4476,13 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>emersonriosmma</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B292">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C292">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D292">
         <v>0</v>
@@ -4490,55 +4490,55 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>luizcosta_mma</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B293">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C293">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D293">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B294">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C294">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D294">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>giulia.fasolato</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B295">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C295">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D295">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>michelle_mirele</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B296">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C296">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D296">
         <v>0</v>
@@ -4546,13 +4546,13 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>danielfranzesilva</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B297">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C297">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D297">
         <v>0</v>
@@ -4560,49 +4560,49 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>ednilsonkaicai</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B298">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C298">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D298">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>dayanaa1511</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B299">
         <v>0</v>
       </c>
       <c r="C299">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D299">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>guerreirammaofc</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B300">
         <v>0</v>
       </c>
       <c r="C300">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D300">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B301">
         <v>0</v>
@@ -4611,18 +4611,18 @@
         <v>2</v>
       </c>
       <c r="D301">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>vanessamelomma</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B302">
         <v>0</v>
       </c>
       <c r="C302">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D302">
         <v>1</v>
@@ -4630,41 +4630,41 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>leonardopateira</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B303">
         <v>0</v>
       </c>
       <c r="C303">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D303">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>rahikikhalid</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B304">
         <v>0</v>
       </c>
       <c r="C304">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D304">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>manumito.oficial</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B305">
         <v>0</v>
       </c>
       <c r="C305">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D305">
         <v>0</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>carlosnoelblack</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B306">
         <v>0</v>
@@ -4681,12 +4681,12 @@
         <v>2</v>
       </c>
       <c r="D306">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4695,18 +4695,18 @@
         <v>2</v>
       </c>
       <c r="D307">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>lokomemo_protetores</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B308">
         <v>0</v>
       </c>
       <c r="C308">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D308">
         <v>1</v>
@@ -4714,105 +4714,105 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>coutz11</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B309">
         <v>0</v>
       </c>
       <c r="C309">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D309">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>orlando_alfa09</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B310">
         <v>0</v>
       </c>
       <c r="C310">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D310">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>vitorshowman</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B311">
         <v>0</v>
       </c>
       <c r="C311">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D311">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>4lissson</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B312">
         <v>0</v>
       </c>
       <c r="C312">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D312">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>danilofernandescf</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B313">
         <v>0</v>
       </c>
       <c r="C313">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D313">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>bryandazuera</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B314">
         <v>0</v>
       </c>
       <c r="C314">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D314">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>ommariotti</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B315">
         <v>0</v>
       </c>
       <c r="C315">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D315">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>brodschack_</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,7 +4826,7 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>_vpft</v>
+        <v>coutz11</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,49 +4840,49 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>izabeldelfino_</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B318">
         <v>0</v>
       </c>
       <c r="C318">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D318">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>janjaovix</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B319">
         <v>0</v>
       </c>
       <c r="C319">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D319">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>4lissson</v>
       </c>
       <c r="B320">
         <v>0</v>
       </c>
       <c r="C320">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D320">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>edsonbahienseb</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4905,12 +4905,12 @@
         <v>1</v>
       </c>
       <c r="D322">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>helenaseveribjj</v>
+        <v>ommariotti</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4919,12 +4919,12 @@
         <v>1</v>
       </c>
       <c r="D323">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>_kainanlima</v>
+        <v>brodschack_</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4933,12 +4933,12 @@
         <v>1</v>
       </c>
       <c r="D324">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>jimmy_indioap</v>
+        <v>_vpft</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4947,12 +4947,12 @@
         <v>1</v>
       </c>
       <c r="D325">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>omar_alneaimi</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4961,12 +4961,12 @@
         <v>1</v>
       </c>
       <c r="D326">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>victor_brunopersonal</v>
+        <v>janjaovix</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4975,12 +4975,12 @@
         <v>1</v>
       </c>
       <c r="D327">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>motumbo_team</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4989,12 +4989,12 @@
         <v>1</v>
       </c>
       <c r="D328">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>vanemessina</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5003,12 +5003,12 @@
         <v>1</v>
       </c>
       <c r="D329">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>dadwillians</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5017,12 +5017,12 @@
         <v>1</v>
       </c>
       <c r="D330">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>thalytabjj</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5031,12 +5031,12 @@
         <v>1</v>
       </c>
       <c r="D331">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>esteticaluharruda</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>chubotaru_lilu</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>eusoufernandosaito</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B334">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>dandraco_</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B335">
         <v>0</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>sejamotivadorofc</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>tpapereira</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>kfcampeoes</v>
+        <v>vanemessina</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>herrickmarinho</v>
+        <v>dadwillians</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>rafaelcmjj</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>cristianomarcello</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>_gabrielpego</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>taylor_71kg</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B344">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>dandraco_</v>
       </c>
       <c r="B345">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>doraasivla</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>pe.mirandas</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>leaoanaalice</v>
+        <v>tpapereira</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>caioparangole</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B349">
         <v>0</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>sabrinaalsilva</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B350">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B351">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>eglaudiomma</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B352">
         <v>0</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>strong_stg_oficial</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>ricardotofanello</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>taporondebruno</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>anamatias.m</v>
+        <v>doraasivla</v>
       </c>
       <c r="B356">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>claudio_marchese_7</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>1000ton_n</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>paulo.titoo</v>
+        <v>caioparangole</v>
       </c>
       <c r="B359">
         <v>0</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>vitorcosta_mma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B360">
         <v>0</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>couragemma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>romulerasilva</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>edergama.mma</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B363">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>alineanne_</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B364">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>julckreis</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B365">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>andreza.thais.1</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B366">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>benicius_edu</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B367">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B368">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>michele_mixa</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B369">
         <v>0</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>joaolauar_</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B370">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>igorbrasileiro01</v>
+        <v>couragemma</v>
       </c>
       <c r="B371">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>felipeocalmon</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B372">
         <v>0</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>rejr_mma</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B373">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>deivssonmanin</v>
+        <v>alineanne_</v>
       </c>
       <c r="B374">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>andrey_m_s_</v>
+        <v>julckreis</v>
       </c>
       <c r="B375">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>vidaldanin</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B376">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>barbaracontadora</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B377">
         <v>0</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>natalves5</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B378">
         <v>0</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B379">
         <v>0</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>boradepodcastoficial</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B380">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>audizioandrade</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B381">
         <v>0</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>isadoragolimpio</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B382">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>dudu.acabamentos</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B383">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>katlembrenda</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B384">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>aline.amaral21</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>tamysregina</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B386">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>guilhermews1994</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B387">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>percepcar</v>
+        <v>natalves5</v>
       </c>
       <c r="B388">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>kevin.mota95</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B389">
         <v>0</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>_marcos_.71</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B390">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>douglas_vitor8</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B391">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B392">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>raulcarvalho1010</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B393">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>roginbrito</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B394">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>meirelesmma</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B395">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>dvlucc2k26_</v>
+        <v>tamysregina</v>
       </c>
       <c r="B396">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>armysenju</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B397">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>f.ostini</v>
+        <v>percepcar</v>
       </c>
       <c r="B398">
         <v>0</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>fher.nando_</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B399">
         <v>0</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B400">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>bastazinifilho</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B401">
         <v>0</v>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>pammygaryo</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B402">
         <v>0</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>anselmo.azevedo</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B403">
         <v>0</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>marcotulio_matuto</v>
+        <v>roginbrito</v>
       </c>
       <c r="B404">
         <v>0</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>ianrochaf</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B405">
         <v>0</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>ale.lagonegro</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B406">
         <v>0</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>ganemfelipe</v>
+        <v>armysenju</v>
       </c>
       <c r="B407">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>marcusvgsz</v>
+        <v>f.ostini</v>
       </c>
       <c r="B408">
         <v>0</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>wanderson.casttro</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B409">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B410">
         <v>0</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>jotapeamancio</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B411">
         <v>0</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B412">
         <v>0</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B413">
         <v>0</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>zeferinomma</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B414">
         <v>0</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>tavaresguu</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B415">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>ildemarmarajo</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B416">
         <v>0</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>peterson_arrais</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B417">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>danieldias7s</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B418">
         <v>0</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>ohanna.anselmo</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B419">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>brun_oguerreiro</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B420">
         <v>0</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>helman_mma70</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B421">
         <v>0</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>macio.almeida_89</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B422">
         <v>0</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>lyviaestherbjj</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B423">
         <v>0</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>wendel_bjj14</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B424">
         <v>0</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>karine_killer_ufc</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B425">
         <v>0</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>andressa_bjj_</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B426">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>dreamartpro</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B427">
         <v>0</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>makelele_bjj</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B428">
         <v>0</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>fdanieljj</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B429">
         <v>0</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B430">
         <v>0</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>caioleonjj</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B431">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B432">
         <v>0</v>
@@ -6450,28 +6450,210 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
+        <v>lyviaestherbjj</v>
+      </c>
+      <c r="B433">
+        <v>0</v>
+      </c>
+      <c r="C433">
+        <v>1</v>
+      </c>
+      <c r="D433">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>wendel_bjj14</v>
+      </c>
+      <c r="B434">
+        <v>0</v>
+      </c>
+      <c r="C434">
+        <v>1</v>
+      </c>
+      <c r="D434">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>karine_killer_ufc</v>
+      </c>
+      <c r="B435">
+        <v>0</v>
+      </c>
+      <c r="C435">
+        <v>1</v>
+      </c>
+      <c r="D435">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>andressa_bjj_</v>
+      </c>
+      <c r="B436">
+        <v>0</v>
+      </c>
+      <c r="C436">
+        <v>1</v>
+      </c>
+      <c r="D436">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>dreamartpro</v>
+      </c>
+      <c r="B437">
+        <v>0</v>
+      </c>
+      <c r="C437">
+        <v>1</v>
+      </c>
+      <c r="D437">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>makelele_bjj</v>
+      </c>
+      <c r="B438">
+        <v>0</v>
+      </c>
+      <c r="C438">
+        <v>1</v>
+      </c>
+      <c r="D438">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>fdanieljj</v>
+      </c>
+      <c r="B439">
+        <v>0</v>
+      </c>
+      <c r="C439">
+        <v>1</v>
+      </c>
+      <c r="D439">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>jeferson_tijolo1</v>
+      </c>
+      <c r="B440">
+        <v>0</v>
+      </c>
+      <c r="C440">
+        <v>1</v>
+      </c>
+      <c r="D440">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>caioleonjj</v>
+      </c>
+      <c r="B441">
+        <v>0</v>
+      </c>
+      <c r="C441">
+        <v>1</v>
+      </c>
+      <c r="D441">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>kevinlopes_bjj</v>
+      </c>
+      <c r="B442">
+        <v>0</v>
+      </c>
+      <c r="C442">
+        <v>1</v>
+      </c>
+      <c r="D442">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="str">
         <v>malene_elleen</v>
       </c>
-      <c r="B433">
-        <v>0</v>
-      </c>
-      <c r="C433">
-        <v>1</v>
-      </c>
-      <c r="D433">
+      <c r="B443">
+        <v>0</v>
+      </c>
+      <c r="C443">
+        <v>1</v>
+      </c>
+      <c r="D443">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>leonardoo_paixao</v>
+      </c>
+      <c r="B444">
+        <v>0</v>
+      </c>
+      <c r="C444">
+        <v>1</v>
+      </c>
+      <c r="D444">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
+        <v>josita_bjj</v>
+      </c>
+      <c r="B445">
+        <v>0</v>
+      </c>
+      <c r="C445">
+        <v>1</v>
+      </c>
+      <c r="D445">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>roxostrike</v>
+      </c>
+      <c r="B446">
+        <v>0</v>
+      </c>
+      <c r="C446">
+        <v>1</v>
+      </c>
+      <c r="D446">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D433"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D446"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D140"/>
+  <dimension ref="A1:D163"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6506,13 +6688,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>181</v>
+        <v>258</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>181</v>
+        <v>257</v>
       </c>
     </row>
     <row r="4">
@@ -6520,7 +6702,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B4">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -6534,13 +6716,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B5">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
@@ -6548,13 +6730,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B6">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7">
@@ -6562,13 +6744,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -6576,13 +6758,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B8">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -6590,13 +6772,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B9">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -6604,13 +6786,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -6618,13 +6800,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B11">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -6632,21 +6814,21 @@
         <v>pg_grappling</v>
       </c>
       <c r="B12">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>anaaj_camargo</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -6657,128 +6839,128 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>mmmarc20</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B14">
+        <v>12</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
         <v>9</v>
-      </c>
-      <c r="C14">
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>marc0s.azv</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B15">
+        <v>8</v>
+      </c>
+      <c r="C15">
         <v>12</v>
       </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
       <c r="D15">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ryangandraufc</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B16">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C16">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D16">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>cleyton_jesuss</v>
+        <v>combintel</v>
       </c>
       <c r="B17">
         <v>7</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>combintel</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>god.motivacao</v>
+        <v>maxgandra</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C19">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D19">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>maxgandra</v>
+        <v>aline.r15</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D21">
-        <v>2</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>irmandadefightteam</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -6786,10 +6968,10 @@
         <v>excelentfightcompetition</v>
       </c>
       <c r="B23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
         <v>2</v>
@@ -6797,7 +6979,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>_beegomes_</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B24">
         <v>3</v>
@@ -6811,24 +6993,24 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>karen.ottoni</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B25">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>alfredo_miras</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -6839,63 +7021,63 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>eliassilverio</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>badboykillermma</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>gra_jpereira</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ninjatheorist</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -6909,69 +7091,69 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>pedromadeira.s</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B32">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>_pizzariabambina_</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>z.proddd</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>multiplicaaba</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B36">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -6979,7 +7161,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>ronemayanmorais</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B37">
         <v>2</v>
@@ -6988,71 +7170,71 @@
         <v>0</v>
       </c>
       <c r="D37">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>meol.socialmidia</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>livreseseguras</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>marcos_tailandess</v>
+        <v>z.proddd</v>
       </c>
       <c r="B40">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C40">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>pedrinhosbjj</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>araujojonaspenhade</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B42">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -7063,63 +7245,63 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>jesabelmelo9</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B44">
         <v>1</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>marcocanatelli</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>pvd_._dudis</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>estevaotoledo</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -7128,15 +7310,15 @@
         <v>1</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>kalindrafaria</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -7147,13 +7329,13 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -7161,7 +7343,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -7170,12 +7352,12 @@
         <v>0</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>oniszczuk_ko</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -7184,12 +7366,12 @@
         <v>0</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>andreibjj</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -7198,12 +7380,12 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>chuck_tlp</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -7212,32 +7394,32 @@
         <v>0</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>antonioemanuel.13</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>gasparjr1983</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>
@@ -7245,21 +7427,21 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>sr.valter</v>
       </c>
       <c r="B56">
         <v>1</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>enzoferrari680</v>
+        <v>devessonjj</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -7268,12 +7450,12 @@
         <v>0</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>gustavomohallem</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -7282,12 +7464,12 @@
         <v>0</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>atlta.marc0s</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -7296,18 +7478,18 @@
         <v>0</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>arturbambam</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D60">
         <v>0</v>
@@ -7315,7 +7497,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>hermaan10_</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -7329,21 +7511,21 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>danieljsantoss_</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>rodrigojansen_</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -7357,7 +7539,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>markakasocks</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -7371,7 +7553,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>hunter.mccrary</v>
+        <v>andreibjj</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -7385,7 +7567,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>omarcotomaz</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -7399,27 +7581,27 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>alphavillesup</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ricieritonan</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -7427,13 +7609,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>lucasampaio</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -7441,13 +7623,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>cjrnavalha</v>
+        <v>magnoddias</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -7455,7 +7637,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>natalan_wilgner</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -7469,7 +7651,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>manmoska</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -7483,7 +7665,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>renatoevangelistaa</v>
+        <v>arturbambam</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -7497,7 +7679,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>cassius.paula</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -7511,7 +7693,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -7525,7 +7707,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>aliferpaulo_</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -7539,7 +7721,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>moisespira</v>
+        <v>markakasocks</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -7553,7 +7735,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>rodrigolidiosales</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -7567,7 +7749,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -7581,7 +7763,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>marciocatenacci</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -7595,7 +7777,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>cristiane.c.santana</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -7609,7 +7791,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ariel_alvees</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -7623,7 +7805,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>flahvinhotreinador</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -7637,7 +7819,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -7651,7 +7833,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>selma.oscar12</v>
+        <v>manmoska</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -7665,7 +7847,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>magnoddias</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -7679,7 +7861,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>romulobelarmino</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -7693,7 +7875,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -7707,7 +7889,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>fernandamourabjj</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -7721,7 +7903,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>larissamartinsbjj</v>
+        <v>moisespira</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -7735,7 +7917,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -7749,7 +7931,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>leitefelippez</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -7763,7 +7945,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>israelbahiensebraz</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -7777,7 +7959,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>wlt_miguel</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -7791,97 +7973,97 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>guerreirammaofc</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>tabajaraharu</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>izabeldelfino_</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>janjaovix</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>edsonbahienseb</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>benjafloripabjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D101">
         <v>0</v>
@@ -7889,13 +8071,13 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>f.ostini</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -7903,13 +8085,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>fher.nando_</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -7917,13 +8099,13 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D104">
         <v>0</v>
@@ -7931,13 +8113,13 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>bastazinifilho</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -7945,13 +8127,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -7959,13 +8141,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>pammygaryo</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -7973,13 +8155,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>anselmo.azevedo</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -7987,13 +8169,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>marcotulio_matuto</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -8001,13 +8183,13 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ianrochaf</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D110">
         <v>0</v>
@@ -8015,21 +8197,21 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ale.lagonegro</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B111">
         <v>0</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ganemfelipe</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B112">
         <v>0</v>
@@ -8038,12 +8220,12 @@
         <v>1</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>janjaovix</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -8052,12 +8234,12 @@
         <v>1</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>marcusvgsz</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -8066,12 +8248,12 @@
         <v>1</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>wanderson.casttro</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -8080,12 +8262,12 @@
         <v>1</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -8094,12 +8276,12 @@
         <v>1</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>jotapeamancio</v>
+        <v>edebetim_</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -8108,12 +8290,12 @@
         <v>1</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -8122,12 +8304,12 @@
         <v>1</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -8136,12 +8318,12 @@
         <v>1</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>zeferinomma</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -8150,12 +8332,12 @@
         <v>1</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>tavaresguu</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -8169,7 +8351,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>ildemarmarajo</v>
+        <v>f.ostini</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -8183,7 +8365,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -8197,7 +8379,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>peterson_arrais</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -8211,7 +8393,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>danieldias7s</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -8225,7 +8407,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>ohanna.anselmo</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -8239,7 +8421,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>brun_oguerreiro</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -8253,7 +8435,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>helman_mma70</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -8267,7 +8449,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>macio.almeida_89</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -8281,7 +8463,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>lyviaestherbjj</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -8295,7 +8477,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>wendel_bjj14</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -8309,7 +8491,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>karine_killer_ufc</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -8323,7 +8505,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>andressa_bjj_</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -8337,7 +8519,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>dreamartpro</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -8351,7 +8533,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>makelele_bjj</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -8365,7 +8547,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>fdanieljj</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -8379,7 +8561,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -8393,7 +8575,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>caioleonjj</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -8407,7 +8589,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -8421,21 +8603,343 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
+        <v>zeferinomma</v>
+      </c>
+      <c r="B140">
+        <v>0</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="D140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>tavaresguu</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+      <c r="D141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>ildemarmarajo</v>
+      </c>
+      <c r="B142">
+        <v>0</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+      <c r="D142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>sirleneferreiradiasdias</v>
+      </c>
+      <c r="B143">
+        <v>0</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="D143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>peterson_arrais</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+      <c r="D144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>danieldias7s</v>
+      </c>
+      <c r="B145">
+        <v>0</v>
+      </c>
+      <c r="C145">
+        <v>1</v>
+      </c>
+      <c r="D145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>ohanna.anselmo</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="D146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>brun_oguerreiro</v>
+      </c>
+      <c r="B147">
+        <v>0</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="D147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>helman_mma70</v>
+      </c>
+      <c r="B148">
+        <v>0</v>
+      </c>
+      <c r="C148">
+        <v>1</v>
+      </c>
+      <c r="D148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>macio.almeida_89</v>
+      </c>
+      <c r="B149">
+        <v>0</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+      <c r="D149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>lyviaestherbjj</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+      <c r="D150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>wendel_bjj14</v>
+      </c>
+      <c r="B151">
+        <v>0</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+      <c r="D151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>karine_killer_ufc</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="D152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>andressa_bjj_</v>
+      </c>
+      <c r="B153">
+        <v>0</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+      <c r="D153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>dreamartpro</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+      <c r="D154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>makelele_bjj</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="D155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>fdanieljj</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+      <c r="D156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>jeferson_tijolo1</v>
+      </c>
+      <c r="B157">
+        <v>0</v>
+      </c>
+      <c r="C157">
+        <v>1</v>
+      </c>
+      <c r="D157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>caioleonjj</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="D158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>kevinlopes_bjj</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+      <c r="C159">
+        <v>1</v>
+      </c>
+      <c r="D159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
         <v>malene_elleen</v>
       </c>
-      <c r="B140">
-        <v>0</v>
-      </c>
-      <c r="C140">
-        <v>1</v>
-      </c>
-      <c r="D140">
+      <c r="B160">
+        <v>0</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+      <c r="D160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>leonardoo_paixao</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+      <c r="D161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>josita_bjj</v>
+      </c>
+      <c r="B162">
+        <v>0</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+      <c r="D162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>roxostrike</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+      <c r="D163">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D140"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D163"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D446"/>
+  <dimension ref="A1:D447"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,13 +433,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B3">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="C3">
         <v>11</v>
       </c>
       <c r="D3">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B4">
-        <v>259</v>
+        <v>308</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>257</v>
+        <v>302</v>
       </c>
     </row>
     <row r="5">
@@ -475,13 +475,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="C6">
         <v>9</v>
       </c>
       <c r="D6">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7">
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="C7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="8">
@@ -503,7 +503,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -531,41 +531,41 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>pg_grappling</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B11">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>44</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>hugo7jj</v>
+        <v>pg_grappling</v>
       </c>
       <c r="B12">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -590,10 +590,10 @@
         <v>44</v>
       </c>
       <c r="C14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D14">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -1704,49 +1704,49 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>odeivisoncardoso</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C94">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>adriano.trator</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B95">
         <v>1</v>
       </c>
       <c r="C95">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B97">
         <v>2</v>
@@ -1760,7 +1760,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -1774,21 +1774,21 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99">
         <v>0</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -1802,69 +1802,69 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B101">
         <v>1</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C102">
         <v>2</v>
       </c>
       <c r="D102">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D103">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B105">
         <v>2</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D105">
         <v>0</v>
@@ -1872,13 +1872,13 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B106">
         <v>2</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -1886,35 +1886,35 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B107">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B108">
         <v>1</v>
       </c>
       <c r="C108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D108">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -1928,7 +1928,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1937,18 +1937,18 @@
         <v>1</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D111">
         <v>1</v>
@@ -1956,13 +1956,13 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -1970,21 +1970,21 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B114">
         <v>2</v>
@@ -1998,7 +1998,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B115">
         <v>2</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B116">
         <v>2</v>
@@ -2026,21 +2026,21 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
         <v>0</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,21 +2068,21 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>wlt_miguel</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C120">
         <v>0</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B121">
         <v>2</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>wesley_bjjvc</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B122">
         <v>2</v>
@@ -2110,21 +2110,21 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>heltoncm2002</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C123">
         <v>0</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -2138,35 +2138,35 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>aliferpaulo_</v>
+        <v>raelduraes</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C125">
         <v>0</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126">
         <v>0</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,7 +2180,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>pedrinhosbjj</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>jesabelmelo9</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>marcocanatelli</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,21 +2278,21 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>pvd_._dudis</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C135">
         <v>0</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B136">
         <v>2</v>
@@ -2306,21 +2306,21 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>sr.valter</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137">
         <v>0</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>devessonjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>tatianeaguiarp</v>
+        <v>devessonjj</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>pitbullandrade</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,13 +2362,13 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B141">
         <v>1</v>
       </c>
       <c r="C141">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D141">
         <v>1</v>
@@ -2376,27 +2376,27 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>treinaadorrafael</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>benjafloripabjj</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D143">
         <v>0</v>
@@ -2404,13 +2404,13 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>fernando.mma</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -2418,13 +2418,13 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -2432,13 +2432,13 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>estevaotoledo</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -2446,13 +2446,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -2460,7 +2460,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -2474,13 +2474,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B149">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>guiiviieira_</v>
+        <v>030sami</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B162">
         <v>1</v>
       </c>
       <c r="C162">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D162">
         <v>0</v>
@@ -2670,13 +2670,13 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>kalindrafaria</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B163">
         <v>1</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -2684,35 +2684,35 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B164">
         <v>1</v>
       </c>
       <c r="C164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B165">
         <v>1</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D165">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>chuck_tlp</v>
+        <v>andreibjj</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,35 +2754,35 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>cristianpsicologo</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C169">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D169">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C170">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,35 +2824,35 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>antonioemanuel.13</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C174">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D174">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C175">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>magnoddias</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,13 +2880,13 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>tonketjudes</v>
+        <v>magnoddias</v>
       </c>
       <c r="B178">
         <v>1</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,35 +3188,35 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C200">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D200">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B201">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C201">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D201">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>jaonevesz</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>camii_bonfim</v>
+        <v>flazuera14</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>sambagabrieloficial</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>_alcantara.bru</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -3860,13 +3860,13 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C248">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D248">
         <v>0</v>
@@ -3874,13 +3874,13 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C249">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D249">
         <v>0</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B250">
         <v>1</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B251">
         <v>1</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B252">
         <v>1</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B257">
         <v>1</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B260">
         <v>1</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B261">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B262">
         <v>1</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B263">
         <v>1</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B264">
         <v>1</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B265">
         <v>1</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>gustavomohallem</v>
+        <v>turmanmma</v>
       </c>
       <c r="B266">
         <v>1</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>atlta.marc0s</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B268">
         <v>1</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>hermaan10_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B269">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B270">
         <v>1</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B271">
         <v>1</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B273">
         <v>1</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B275">
         <v>1</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B276">
         <v>1</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B277">
         <v>1</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>natalan_wilgner</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B278">
         <v>1</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B279">
         <v>1</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B280">
         <v>1</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B281">
         <v>1</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B282">
         <v>1</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B283">
         <v>1</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B284">
         <v>1</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B285">
         <v>1</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B286">
         <v>1</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B287">
         <v>1</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B288">
         <v>1</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B289">
         <v>1</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B291">
         <v>1</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B292">
         <v>1</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>fernandamourabjj</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B293">
         <v>1</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B294">
         <v>1</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B295">
         <v>1</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B296">
         <v>1</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B297">
         <v>1</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>joselia_1980</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B298">
         <v>1</v>
@@ -4574,13 +4574,13 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>marinealcausa</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B299">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C299">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D299">
         <v>0</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B300">
         <v>0</v>
@@ -4602,63 +4602,63 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B301">
         <v>0</v>
       </c>
       <c r="C301">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D301">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B302">
         <v>0</v>
       </c>
       <c r="C302">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D302">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>giulia.fasolato</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B303">
         <v>0</v>
       </c>
       <c r="C303">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D303">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B304">
         <v>0</v>
       </c>
       <c r="C304">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D304">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B305">
         <v>0</v>
@@ -4672,21 +4672,21 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B306">
         <v>0</v>
       </c>
       <c r="C306">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D306">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>dayanaa1511</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B307">
         <v>0</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>guerreirammaofc</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B308">
         <v>0</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B309">
         <v>0</v>
@@ -4723,26 +4723,26 @@
         <v>2</v>
       </c>
       <c r="D309">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>vanessamelomma</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B310">
         <v>0</v>
       </c>
       <c r="C310">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D310">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,21 +4770,21 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B313">
         <v>0</v>
       </c>
       <c r="C313">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D313">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,7 +4798,7 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,21 +4812,21 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B316">
         <v>0</v>
       </c>
       <c r="C316">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D316">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,21 +4840,21 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B318">
         <v>0</v>
       </c>
       <c r="C318">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D318">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,21 +4882,21 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B321">
         <v>0</v>
       </c>
       <c r="C321">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D321">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>izabeldelfino_</v>
+        <v>_vpft</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,7 +4966,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>janjaovix</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>janjaovix</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,7 +5008,7 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>peacegrappler_archive</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5045,12 +5045,12 @@
         <v>1</v>
       </c>
       <c r="D332">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B334">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B335">
         <v>0</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>esteticaluharruda</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B344">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B345">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B349">
         <v>0</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B350">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B351">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B352">
         <v>0</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B356">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B359">
         <v>0</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B360">
         <v>0</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B363">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B364">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B365">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B366">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B367">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B368">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B369">
         <v>0</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B370">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B371">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B372">
         <v>0</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B373">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B374">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B375">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B376">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B377">
         <v>0</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B378">
         <v>0</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B379">
         <v>0</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B380">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B381">
         <v>0</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B382">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B383">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B384">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B386">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B387">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B388">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B389">
         <v>0</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B390">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B391">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B392">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B393">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B394">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B395">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B396">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B397">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B398">
         <v>0</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B399">
         <v>0</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B400">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B401">
         <v>0</v>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B402">
         <v>0</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B403">
         <v>0</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B404">
         <v>0</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B405">
         <v>0</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>dvlucc2k26_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B406">
         <v>0</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>armysenju</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B407">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>f.ostini</v>
+        <v>armysenju</v>
       </c>
       <c r="B408">
         <v>0</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>fher.nando_</v>
+        <v>f.ostini</v>
       </c>
       <c r="B409">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B410">
         <v>0</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>bastazinifilho</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B411">
         <v>0</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>pammygaryo</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B412">
         <v>0</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>anselmo.azevedo</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B413">
         <v>0</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>marcotulio_matuto</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B414">
         <v>0</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>ianrochaf</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B415">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>ale.lagonegro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B416">
         <v>0</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>ganemfelipe</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B417">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>marcusvgsz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B418">
         <v>0</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>wanderson.casttro</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B419">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B420">
         <v>0</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>jotapeamancio</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B421">
         <v>0</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B422">
         <v>0</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B423">
         <v>0</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>zeferinomma</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B424">
         <v>0</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>tavaresguu</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B425">
         <v>0</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>ildemarmarajo</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B426">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>peterson_arrais</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B427">
         <v>0</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>danieldias7s</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B428">
         <v>0</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>ohanna.anselmo</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B429">
         <v>0</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B430">
         <v>0</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>helman_mma70</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B431">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>macio.almeida_89</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B432">
         <v>0</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>lyviaestherbjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B433">
         <v>0</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>wendel_bjj14</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B434">
         <v>0</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>karine_killer_ufc</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B435">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>andressa_bjj_</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B436">
         <v>0</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>dreamartpro</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B437">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>makelele_bjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B438">
         <v>0</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>fdanieljj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B439">
         <v>0</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B440">
         <v>0</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>caioleonjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B441">
         <v>0</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B442">
         <v>0</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>malene_elleen</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B443">
         <v>0</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>leonardoo_paixao</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B444">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>josita_bjj</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B445">
         <v>0</v>
@@ -6632,28 +6632,42 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
+        <v>josita_bjj</v>
+      </c>
+      <c r="B446">
+        <v>0</v>
+      </c>
+      <c r="C446">
+        <v>1</v>
+      </c>
+      <c r="D446">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="str">
         <v>roxostrike</v>
       </c>
-      <c r="B446">
-        <v>0</v>
-      </c>
-      <c r="C446">
-        <v>1</v>
-      </c>
-      <c r="D446">
+      <c r="B447">
+        <v>0</v>
+      </c>
+      <c r="C447">
+        <v>1</v>
+      </c>
+      <c r="D447">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D446"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D447"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D163"/>
+  <dimension ref="A1:D164"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6688,13 +6702,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>258</v>
+        <v>307</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>257</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4">
@@ -6702,13 +6716,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B4">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>50</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5">
@@ -6716,13 +6730,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6">
@@ -6730,41 +6744,41 @@
         <v>rm.nicki</v>
       </c>
       <c r="B6">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>rpsantos_mma</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B7">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -6772,7 +6786,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B9">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -6786,13 +6800,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -6859,10 +6873,10 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -7259,27 +7273,27 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>marcos_tailandess</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>tabajaraharu</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B45">
         <v>1</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -7287,7 +7301,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ravenrodriguez___</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -7301,7 +7315,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>dogodoyfoto</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -7315,35 +7329,35 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>enzoferrari680</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>pedrinhosbjj</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -7357,7 +7371,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -7371,7 +7385,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>jesabelmelo9</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -7385,7 +7399,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>marcocanatelli</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -7399,21 +7413,21 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>pvd_._dudis</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B55">
         <v>2</v>
@@ -7427,21 +7441,21 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>sr.valter</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>devessonjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -7455,7 +7469,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>tatianeaguiarp</v>
+        <v>devessonjj</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -7469,7 +7483,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>pitbullandrade</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -7483,27 +7497,27 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>estevaotoledo</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B60">
         <v>1</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>kalindrafaria</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D61">
         <v>0</v>
@@ -7511,35 +7525,35 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B62">
         <v>1</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -7553,7 +7567,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -7567,7 +7581,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>chuck_tlp</v>
+        <v>andreibjj</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -7581,35 +7595,35 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>antonioemanuel.13</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C67">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -7623,7 +7637,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>magnoddias</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -7637,13 +7651,13 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>gustavomohallem</v>
+        <v>magnoddias</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71">
         <v>0</v>
@@ -7651,7 +7665,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>atlta.marc0s</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -7665,7 +7679,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -7679,7 +7693,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>hermaan10_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -7693,7 +7707,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -7707,7 +7721,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -7721,7 +7735,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -7735,7 +7749,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -7749,7 +7763,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -7763,7 +7777,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -7777,7 +7791,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -7791,7 +7805,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -7805,7 +7819,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>cjrnavalha</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -7819,7 +7833,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>natalan_wilgner</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -7833,7 +7847,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -7847,7 +7861,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -7861,7 +7875,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -7875,7 +7889,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -7889,7 +7903,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>aliferpaulo_</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -7903,7 +7917,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>moisespira</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -7917,7 +7931,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -7931,7 +7945,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -7945,7 +7959,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -7959,7 +7973,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -7973,7 +7987,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -7987,7 +8001,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -8001,7 +8015,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -8015,7 +8029,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -8029,7 +8043,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -8043,7 +8057,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -8057,7 +8071,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>fernandamourabjj</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -8071,7 +8085,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -8085,7 +8099,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -8099,7 +8113,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -8113,7 +8127,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -8127,7 +8141,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>wlt_miguel</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -8141,7 +8155,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>wesley_bjjvc</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -8155,7 +8169,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>juniordiasmma</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -8169,7 +8183,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>joselia_1980</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -8183,7 +8197,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>kaua_limamma</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -8197,27 +8211,27 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>guerreirammaofc</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>izabeldelfino_</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B112">
         <v>0</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -8225,7 +8239,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>janjaovix</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B113">
         <v>0</v>
@@ -8239,7 +8253,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>janjaovix</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -8253,7 +8267,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -8267,7 +8281,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -8281,7 +8295,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>edebetim_</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -8295,7 +8309,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>maca.mariotti</v>
+        <v>edebetim_</v>
       </c>
       <c r="B118">
         <v>0</v>
@@ -8309,7 +8323,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>peacegrappler_archive</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B119">
         <v>0</v>
@@ -8323,7 +8337,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>_oliveira09_</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -8337,7 +8351,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>benjafloripabjj</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B121">
         <v>0</v>
@@ -8346,12 +8360,12 @@
         <v>1</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>f.ostini</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -8365,7 +8379,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>fher.nando_</v>
+        <v>f.ostini</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -8379,7 +8393,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -8393,7 +8407,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>bastazinifilho</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -8407,7 +8421,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -8421,7 +8435,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>pammygaryo</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -8435,7 +8449,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>anselmo.azevedo</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -8449,7 +8463,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>marcotulio_matuto</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -8463,7 +8477,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>ianrochaf</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -8477,7 +8491,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>ale.lagonegro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -8491,7 +8505,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>ganemfelipe</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -8505,7 +8519,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -8519,7 +8533,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>marcusvgsz</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -8533,7 +8547,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>wanderson.casttro</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -8547,7 +8561,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -8561,7 +8575,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>jotapeamancio</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -8575,7 +8589,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -8589,7 +8603,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -8603,7 +8617,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>zeferinomma</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -8617,7 +8631,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>tavaresguu</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -8631,7 +8645,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ildemarmarajo</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -8645,7 +8659,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -8659,7 +8673,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>peterson_arrais</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -8673,7 +8687,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>danieldias7s</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -8687,7 +8701,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>ohanna.anselmo</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -8701,7 +8715,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -8715,7 +8729,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>helman_mma70</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -8729,7 +8743,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>macio.almeida_89</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -8743,7 +8757,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>lyviaestherbjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -8757,7 +8771,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>wendel_bjj14</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -8771,7 +8785,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>karine_killer_ufc</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -8785,7 +8799,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>andressa_bjj_</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -8799,7 +8813,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>dreamartpro</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -8813,7 +8827,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>makelele_bjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -8827,7 +8841,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>fdanieljj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -8841,7 +8855,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -8855,7 +8869,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>caioleonjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -8869,7 +8883,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -8883,7 +8897,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>malene_elleen</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -8897,7 +8911,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>leonardoo_paixao</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -8911,7 +8925,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>josita_bjj</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -8925,21 +8939,35 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
+        <v>josita_bjj</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+      <c r="D163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
         <v>roxostrike</v>
       </c>
-      <c r="B163">
-        <v>0</v>
-      </c>
-      <c r="C163">
-        <v>1</v>
-      </c>
-      <c r="D163">
+      <c r="B164">
+        <v>0</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="D164">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D163"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D164"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -430,30 +430,30 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>quemuel_ottoni</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="C3">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>peacegrappler</v>
+        <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>308</v>
+        <v>355</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5">
@@ -475,7 +475,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="C6">
         <v>9</v>
@@ -489,13 +489,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="C7">
         <v>8</v>
       </c>
       <c r="D7">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -503,13 +503,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -517,13 +517,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B9">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -545,7 +545,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B11">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -590,7 +590,7 @@
         <v>44</v>
       </c>
       <c r="C14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14">
         <v>46</v>
@@ -780,44 +780,44 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>tiwimma</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B28">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C28">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>eliassilverio</v>
+        <v>maxgandra</v>
       </c>
       <c r="B29">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D29">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>maxgandra</v>
+        <v>tiwimma</v>
       </c>
       <c r="B30">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D30">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
@@ -853,7 +853,7 @@
         <v>marc0s.azv</v>
       </c>
       <c r="B33">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C33">
         <v>1</v>
@@ -1284,10 +1284,10 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>alfredo_miras</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -1298,66 +1298,66 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>fabinho_falcao_</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>ailinperezufc</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>mah__vergueiro</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B68">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C68">
         <v>1</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B69">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -1368,13 +1368,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>fau_gfs</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B70">
         <v>4</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70">
         <v>0</v>
@@ -1382,49 +1382,49 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ninjatheorist</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B71">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>livreseseguras</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>_pizzariabambina_</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B74">
         <v>4</v>
@@ -1438,21 +1438,21 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>artewebpersonalizados</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>tatibscardoso</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B76">
         <v>2</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>shawlin13oficial</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B77">
         <v>2</v>
@@ -1475,12 +1475,12 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>z.proddd</v>
+        <v>febrancatti</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1536,35 +1536,35 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>reifernandes</v>
+        <v>z.proddd</v>
       </c>
       <c r="B82">
         <v>2</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -1578,41 +1578,41 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>maca.mariotti</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>alexsandra_kairos</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>multiplicaaba</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D87">
         <v>0</v>
@@ -1620,13 +1620,13 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>f.luan_11</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B88">
         <v>3</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
         <v>0</v>
@@ -1634,21 +1634,21 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -1662,58 +1662,58 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>meol.socialmidia</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>kauepraciano</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B94">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
@@ -6702,83 +6702,83 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>307</v>
+        <v>344</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>hugo7jj</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>pablofiorindi</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>47</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>rm.nicki</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B6">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B7">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>rpsantos_mma</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B8">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9">
@@ -6786,13 +6786,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B9">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -6800,13 +6800,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -6873,7 +6873,7 @@
         <v>8</v>
       </c>
       <c r="C15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15">
         <v>17</v>
@@ -6884,7 +6884,7 @@
         <v>marc0s.azv</v>
       </c>
       <c r="B16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -6926,7 +6926,7 @@
         <v>maxgandra</v>
       </c>
       <c r="B19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19">
         <v>1</v>
@@ -7021,24 +7021,24 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>_beegomes_</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B26">
         <v>3</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>karen.ottoni</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B27">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -7049,10 +7049,10 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>alfredo_miras</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B28">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -7063,35 +7063,35 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>eliassilverio</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B29">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B30">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>badboykillermma</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -7105,41 +7105,41 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ninjatheorist</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>pedromadeira.s</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>livreseseguras</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -7147,21 +7147,21 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B35">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>_pizzariabambina_</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B36">
         <v>4</v>
@@ -7175,21 +7175,21 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>vndcardoso</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B37">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>artewebpersonalizados</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B38">
         <v>2</v>
@@ -7203,7 +7203,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>tatibscardoso</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B39">
         <v>2</v>
@@ -7217,7 +7217,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>z.proddd</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B40">
         <v>2</v>
@@ -7226,63 +7226,63 @@
         <v>0</v>
       </c>
       <c r="D40">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>multiplicaaba</v>
+        <v>z.proddd</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ronemayanmorais</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>meol.socialmidia</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>kauepraciano</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">

--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4">
@@ -587,7 +587,7 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C14">
         <v>41</v>
@@ -780,30 +780,30 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>eliassilverio</v>
+        <v>maxgandra</v>
       </c>
       <c r="B28">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C28">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D28">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>maxgandra</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B29">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C29">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30">
@@ -6702,13 +6702,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="4">
@@ -6839,24 +6839,24 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>mmmarc20</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>anaaj_camargo</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -6867,16 +6867,16 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>ryangandraufc</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C15">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -6926,7 +6926,7 @@
         <v>maxgandra</v>
       </c>
       <c r="B19">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19">
         <v>1</v>

--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>346</v>
+        <v>365</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
@@ -447,7 +447,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C4">
         <v>11</v>
@@ -475,13 +475,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -489,10 +489,10 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>90</v>
@@ -545,13 +545,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B11">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12">
@@ -590,7 +590,7 @@
         <v>45</v>
       </c>
       <c r="C14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14">
         <v>46</v>
@@ -685,7 +685,7 @@
         <v>combintel</v>
       </c>
       <c r="B21">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1102,41 +1102,41 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>marcos_tailandess</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B51">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C51">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>eolucasrosa</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B52">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C52">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>dagestan0920</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B53">
         <v>5</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -1144,13 +1144,13 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B54">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C54">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -1158,27 +1158,27 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>_.maduoliveira_</v>
+        <v>paxlucta</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D55">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>dogodoyfoto</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B56">
         <v>3</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>3</v>
@@ -1186,13 +1186,13 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B57">
         <v>3</v>
       </c>
       <c r="C57">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D57">
         <v>3</v>
@@ -1200,105 +1200,105 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>_oliveira09_</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B58">
         <v>3</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D58">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59">
+        <v>5</v>
+      </c>
+      <c r="D59">
         <v>4</v>
-      </c>
-      <c r="D59">
-        <v>6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>glm.barbosa</v>
+        <v>edebetim_</v>
       </c>
       <c r="B60">
         <v>2</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D60">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>gabrielsouzamma</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>ninjatheorist</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>kauepraciano</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B65">
         <v>3</v>
@@ -6702,13 +6702,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>345</v>
+        <v>364</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>307</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4">
@@ -6716,10 +6716,10 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D4">
         <v>52</v>
@@ -6730,55 +6730,55 @@
         <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>rpsantos_mma</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>rm.nicki</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>80</v>
+        <v>115</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>68</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B8">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>41</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
@@ -6800,7 +6800,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -6845,7 +6845,7 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>17</v>
@@ -6898,7 +6898,7 @@
         <v>combintel</v>
       </c>
       <c r="B17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -6993,10 +6993,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>irmandadefightteam</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B24">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -7007,7 +7007,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>alvesmidih</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B25">
         <v>3</v>
@@ -7016,18 +7016,18 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>eliassilverio</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B26">
         <v>3</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -7035,21 +7035,21 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>_beegomes_</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B27">
         <v>3</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>ninjatheorist</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B28">
         <v>3</v>
@@ -7063,7 +7063,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>kauepraciano</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B29">
         <v>3</v>

--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>365</v>
+        <v>402</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>314</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B5">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C5">
         <v>26</v>
@@ -489,7 +489,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C7">
         <v>9</v>
@@ -503,13 +503,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
@@ -517,13 +517,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B9">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C9">
         <v>4</v>
       </c>
       <c r="D9">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10">
@@ -531,13 +531,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11">
@@ -545,7 +545,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B11">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -587,7 +587,7 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C14">
         <v>42</v>
@@ -668,30 +668,30 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>kaua_limamma</v>
+        <v>combintel</v>
       </c>
       <c r="B20">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>combintel</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B21">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -786,7 +786,7 @@
         <v>18</v>
       </c>
       <c r="C28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D28">
         <v>6</v>
@@ -1018,69 +1018,69 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>badboykillermma</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>gdazuera</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C46">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>gdazuera</v>
       </c>
       <c r="B47">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D47">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>excelentfightcompetition</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ravenrodriguez___</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C49">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -1088,69 +1088,69 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B50">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>kauepraciano</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>marcos_tailandess</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B52">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C52">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>eolucasrosa</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B53">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>dagestan0920</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B54">
         <v>5</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -1158,13 +1158,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C55">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -1172,27 +1172,27 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>_.maduoliveira_</v>
+        <v>paxlucta</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D56">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>dogodoyfoto</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B57">
         <v>3</v>
       </c>
       <c r="C57">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>3</v>
@@ -1200,13 +1200,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B58">
         <v>3</v>
       </c>
       <c r="C58">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D58">
         <v>3</v>
@@ -1214,100 +1214,100 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>_oliveira09_</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B59">
         <v>3</v>
       </c>
       <c r="C59">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D59">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60">
+        <v>5</v>
+      </c>
+      <c r="D60">
         <v>4</v>
-      </c>
-      <c r="D60">
-        <v>6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>glm.barbosa</v>
+        <v>edebetim_</v>
       </c>
       <c r="B61">
         <v>2</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D61">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>gabrielsouzamma</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C63">
         <v>1</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B64">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ninjatheorist</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B65">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -6702,13 +6702,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>364</v>
+        <v>401</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>314</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4">
@@ -6716,7 +6716,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -6730,7 +6730,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -6741,30 +6741,30 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B6">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>rpsantos_mma</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B7">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -6772,13 +6772,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B8">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -6786,13 +6786,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B9">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -6800,13 +6800,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11">
@@ -6814,7 +6814,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B11">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -6842,7 +6842,7 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13">
         <v>15</v>
@@ -6898,7 +6898,7 @@
         <v>combintel</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -6929,7 +6929,7 @@
         <v>11</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -6979,27 +6979,27 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>excelentfightcompetition</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>kauepraciano</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -7007,10 +7007,10 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>irmandadefightteam</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B25">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>alvesmidih</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B26">
         <v>3</v>
@@ -7030,18 +7030,18 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>eliassilverio</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B27">
         <v>3</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -7049,21 +7049,21 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>_beegomes_</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>ninjatheorist</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B29">
         <v>3</v>

--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>402</v>
+        <v>440</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>348</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B5">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C5">
         <v>26</v>
@@ -472,30 +472,30 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B6">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>pablofiorindi</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B7">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="C7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8">
@@ -503,13 +503,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -545,13 +545,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B11">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12">
@@ -559,7 +559,7 @@
         <v>pg_grappling</v>
       </c>
       <c r="B12">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -587,13 +587,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C14">
         <v>42</v>
       </c>
       <c r="D14">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -615,7 +615,7 @@
         <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -640,44 +640,44 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>bellsouza816</v>
+        <v>combintel</v>
       </c>
       <c r="B18">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>erik_.mma</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B19">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>combintel</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B20">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -716,10 +716,10 @@
         <v>9</v>
       </c>
       <c r="C23">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D23">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24">
@@ -1718,49 +1718,49 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>odeivisoncardoso</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C95">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>adriano.trator</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B96">
         <v>1</v>
       </c>
       <c r="C96">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>s__simone__</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B98">
         <v>2</v>
@@ -1774,7 +1774,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B99">
         <v>2</v>
@@ -1788,21 +1788,21 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100">
         <v>0</v>
       </c>
       <c r="D100">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -1816,69 +1816,69 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B102">
         <v>1</v>
       </c>
       <c r="C102">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D102">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>ismaeldaniell</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C103">
         <v>2</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D104">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B106">
         <v>2</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D106">
         <v>0</v>
@@ -1886,13 +1886,13 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -1900,35 +1900,35 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D108">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B109">
         <v>1</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D109">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -1942,7 +1942,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>fredoctmma</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1951,18 +1951,18 @@
         <v>1</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B112">
         <v>1</v>
       </c>
       <c r="C112">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -1970,13 +1970,13 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -1984,21 +1984,21 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B115">
         <v>2</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B116">
         <v>2</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B117">
         <v>2</v>
@@ -2040,21 +2040,21 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C118">
         <v>0</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,21 +2082,21 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>wlt_miguel</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C121">
         <v>0</v>
       </c>
       <c r="D121">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B122">
         <v>2</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>wesley_bjjvc</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B123">
         <v>2</v>
@@ -2124,21 +2124,21 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>heltoncm2002</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
         <v>0</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -2152,35 +2152,35 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>aliferpaulo_</v>
+        <v>raelduraes</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C126">
         <v>0</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127">
         <v>0</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,7 +2194,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>pedrinhosbjj</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>jesabelmelo9</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>marcocanatelli</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,21 +2292,21 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>pvd_._dudis</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B136">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C136">
         <v>0</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B137">
         <v>2</v>
@@ -2320,21 +2320,21 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>sr.valter</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B138">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C138">
         <v>0</v>
       </c>
       <c r="D138">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>devessonjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>tatianeaguiarp</v>
+        <v>devessonjj</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>pitbullandrade</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -6702,13 +6702,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>401</v>
+        <v>439</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>348</v>
+        <v>385</v>
       </c>
     </row>
     <row r="4">
@@ -6716,13 +6716,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
@@ -6730,41 +6730,41 @@
         <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>rpsantos_mma</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -6772,7 +6772,7 @@
         <v>rm.nicki</v>
       </c>
       <c r="B8">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -6786,13 +6786,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B9">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10">
@@ -6800,13 +6800,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -6814,7 +6814,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B11">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         <v>pg_grappling</v>
       </c>
       <c r="B12">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -6842,13 +6842,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>15</v>
       </c>
       <c r="D13">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
@@ -6856,7 +6856,7 @@
         <v>mmmarc20</v>
       </c>
       <c r="B14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -6881,30 +6881,30 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>marc0s.azv</v>
+        <v>combintel</v>
       </c>
       <c r="B16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>combintel</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B17">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18">
@@ -6957,10 +6957,10 @@
         <v>2</v>
       </c>
       <c r="C21">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22">
@@ -7287,27 +7287,27 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>marcos_tailandess</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B45">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>tabajaraharu</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ravenrodriguez___</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -7329,7 +7329,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>dogodoyfoto</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -7343,35 +7343,35 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>enzoferrari680</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>pedrinhosbjj</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -7385,7 +7385,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -7399,7 +7399,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>jesabelmelo9</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -7413,7 +7413,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>marcocanatelli</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -7427,21 +7427,21 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>pvd_._dudis</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B56">
         <v>2</v>
@@ -7455,21 +7455,21 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>sr.valter</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>devessonjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>tatianeaguiarp</v>
+        <v>devessonjj</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -7497,7 +7497,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>pitbullandrade</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B60">
         <v>1</v>

--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D447"/>
+  <dimension ref="A1:D462"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>440</v>
+        <v>493</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>385</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B5">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C5">
         <v>26</v>
@@ -472,30 +472,30 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>pablofiorindi</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C6">
         <v>10</v>
       </c>
       <c r="D6">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B7">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8">
@@ -503,7 +503,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -517,7 +517,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B9">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -531,13 +531,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11">
@@ -545,7 +545,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B11">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -587,13 +587,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B14">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D14">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15">
@@ -1214,178 +1214,178 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C59">
         <v>7</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>_oliveira09_</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B60">
         <v>3</v>
       </c>
       <c r="C60">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D60">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C61">
+        <v>5</v>
+      </c>
+      <c r="D61">
         <v>4</v>
-      </c>
-      <c r="D61">
-        <v>6</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>glm.barbosa</v>
+        <v>edebetim_</v>
       </c>
       <c r="B62">
         <v>2</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>gabrielsouzamma</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64">
         <v>1</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B65">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>alfredo_miras</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>fabinho_falcao_</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C67">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ailinperezufc</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B68">
         <v>2</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>mah__vergueiro</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B70">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C70">
         <v>1</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>lipe.ftt</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B71">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -1396,13 +1396,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>fau_gfs</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B72">
         <v>4</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -1410,21 +1410,21 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>livreseseguras</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B73">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B74">
         <v>4</v>
@@ -1438,49 +1438,49 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>_pizzariabambina_</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B75">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>artewebpersonalizados</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>tatibscardoso</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B77">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>shawlin13oficial</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B78">
         <v>2</v>
@@ -1489,12 +1489,12 @@
         <v>0</v>
       </c>
       <c r="D78">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>eduardorodrigrs</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -1503,12 +1503,12 @@
         <v>0</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>febrancatti</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>z.proddd</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -1550,21 +1550,21 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>reifernandes</v>
+        <v>febrancatti</v>
       </c>
       <c r="B83">
         <v>2</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>daniel_dias_214</v>
+        <v>z.proddd</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -1578,69 +1578,69 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>reifernandes</v>
       </c>
       <c r="B85">
         <v>2</v>
       </c>
       <c r="C85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>maca.mariotti</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>multiplicaaba</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B88">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>f.luan_11</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D89">
         <v>0</v>
@@ -1648,55 +1648,55 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>vitorpetrino</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>jcchagas_</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>anderson.logan.35</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>marifferreirac</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -1704,7 +1704,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>meol.socialmidia</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B94">
         <v>3</v>
@@ -1718,13 +1718,13 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>pitbullandrade</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -1732,30 +1732,30 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>odeivisoncardoso</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>adriano.trator</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B97">
         <v>1</v>
       </c>
       <c r="C97">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
@@ -1956,27 +1956,27 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>fredoctmma</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B113">
         <v>1</v>
       </c>
       <c r="C113">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -1984,13 +1984,13 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -1998,21 +1998,21 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B116">
         <v>2</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B117">
         <v>2</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B118">
         <v>2</v>
@@ -2054,21 +2054,21 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C119">
         <v>0</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,21 +2096,21 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>wlt_miguel</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B122">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C122">
         <v>0</v>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B123">
         <v>2</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>wesley_bjjvc</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B124">
         <v>2</v>
@@ -2138,21 +2138,21 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>heltoncm2002</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B125">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C125">
         <v>0</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -2166,35 +2166,35 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>aliferpaulo_</v>
+        <v>raelduraes</v>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C127">
         <v>0</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128">
         <v>0</v>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B129">
         <v>1</v>
@@ -2208,7 +2208,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>pedrinhosbjj</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>jesabelmelo9</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>marcocanatelli</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,21 +2306,21 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>pvd_._dudis</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B137">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C137">
         <v>0</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B138">
         <v>2</v>
@@ -2334,21 +2334,21 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>sr.valter</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B139">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C139">
         <v>0</v>
       </c>
       <c r="D139">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>devessonjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>tatianeaguiarp</v>
+        <v>devessonjj</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,13 +2376,13 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B142">
         <v>1</v>
       </c>
       <c r="C142">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -2390,27 +2390,27 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>treinaadorrafael</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>benjafloripabjj</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D144">
         <v>0</v>
@@ -2418,13 +2418,13 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>fernando.mma</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -2432,13 +2432,13 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -2446,13 +2446,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>estevaotoledo</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -2460,13 +2460,13 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B148">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -2474,7 +2474,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -2488,13 +2488,13 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B150">
         <v>1</v>
       </c>
       <c r="C150">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>guiiviieira_</v>
+        <v>030sami</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,13 +2670,13 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B163">
         <v>1</v>
       </c>
       <c r="C163">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -2684,13 +2684,13 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>kalindrafaria</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B164">
         <v>1</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -2698,35 +2698,35 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B165">
         <v>1</v>
       </c>
       <c r="C165">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D165">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B166">
         <v>1</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D166">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,7 +2740,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>chuck_tlp</v>
+        <v>andreibjj</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,35 +2768,35 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>cristianpsicologo</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C170">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D170">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B171">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C171">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,35 +2838,35 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>antonioemanuel.13</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C175">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D175">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C176">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>magnoddias</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,13 +2894,13 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>tonketjudes</v>
+        <v>magnoddias</v>
       </c>
       <c r="B179">
         <v>1</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,35 +3202,35 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C201">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D201">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B202">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C202">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>jaonevesz</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>camii_bonfim</v>
+        <v>flazuera14</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>sambagabrieloficial</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>_alcantara.bru</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B248">
         <v>1</v>
@@ -3874,13 +3874,13 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B249">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C249">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D249">
         <v>0</v>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B250">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C250">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D250">
         <v>0</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B251">
         <v>1</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B252">
         <v>1</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B257">
         <v>1</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B260">
         <v>1</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B261">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B262">
         <v>1</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B263">
         <v>1</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B264">
         <v>1</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B265">
         <v>1</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B266">
         <v>1</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>gustavomohallem</v>
+        <v>turmanmma</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>atlta.marc0s</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B268">
         <v>1</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B269">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>hermaan10_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B270">
         <v>1</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B271">
         <v>1</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B273">
         <v>1</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B275">
         <v>1</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B276">
         <v>1</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B277">
         <v>1</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B278">
         <v>1</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>natalan_wilgner</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B279">
         <v>1</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B280">
         <v>1</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B281">
         <v>1</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B282">
         <v>1</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B283">
         <v>1</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B284">
         <v>1</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B285">
         <v>1</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B286">
         <v>1</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B287">
         <v>1</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B288">
         <v>1</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B289">
         <v>1</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B291">
         <v>1</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B292">
         <v>1</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B293">
         <v>1</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>fernandamourabjj</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B294">
         <v>1</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B295">
         <v>1</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B296">
         <v>1</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B297">
         <v>1</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B298">
         <v>1</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>joselia_1980</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B299">
         <v>1</v>
@@ -4588,13 +4588,13 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>marinealcausa</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B300">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C300">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D300">
         <v>0</v>
@@ -4602,13 +4602,13 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>emersonriosmma</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B301">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C301">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D301">
         <v>0</v>
@@ -4616,55 +4616,55 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>luizcosta_mma</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B302">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C302">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D302">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B303">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C303">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D303">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>giulia.fasolato</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B304">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C304">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D304">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>michelle_mirele</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B305">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C305">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D305">
         <v>0</v>
@@ -4672,13 +4672,13 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>danielfranzesilva</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B306">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C306">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D306">
         <v>0</v>
@@ -4686,55 +4686,55 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>ednilsonkaicai</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B307">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C307">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D307">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>dayanaa1511</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B308">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C308">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D308">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>guerreirammaofc</v>
+        <v>santos39roger</v>
       </c>
       <c r="B309">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C309">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D309">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B310">
         <v>0</v>
       </c>
       <c r="C310">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D310">
         <v>0</v>
@@ -4742,41 +4742,41 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>vanessamelomma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B311">
         <v>0</v>
       </c>
       <c r="C311">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D311">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>leonardopateira</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B312">
         <v>0</v>
       </c>
       <c r="C312">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D312">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>rahikikhalid</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B313">
         <v>0</v>
       </c>
       <c r="C313">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D313">
         <v>1</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>manumito.oficial</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4793,18 +4793,18 @@
         <v>2</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>carlosnoelblack</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B315">
         <v>0</v>
       </c>
       <c r="C315">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D315">
         <v>0</v>
@@ -4812,13 +4812,13 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B316">
         <v>0</v>
       </c>
       <c r="C316">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D316">
         <v>0</v>
@@ -4826,13 +4826,13 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>lokomemo_protetores</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B317">
         <v>0</v>
       </c>
       <c r="C317">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D317">
         <v>1</v>
@@ -4840,13 +4840,13 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>coutz11</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B318">
         <v>0</v>
       </c>
       <c r="C318">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D318">
         <v>1</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>orlando_alfa09</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4863,12 +4863,12 @@
         <v>2</v>
       </c>
       <c r="D319">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>vitorshowman</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,21 +4882,21 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>4lissson</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B321">
         <v>0</v>
       </c>
       <c r="C321">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D321">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>danilofernandescf</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>bryandazuera</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,49 +4924,49 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>ommariotti</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B324">
         <v>0</v>
       </c>
       <c r="C324">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D324">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>brodschack_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B325">
         <v>0</v>
       </c>
       <c r="C325">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D325">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>_vpft</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B326">
         <v>0</v>
       </c>
       <c r="C326">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D326">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>izabeldelfino_</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>janjaovix</v>
+        <v>coutz11</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,49 +4994,49 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B329">
         <v>0</v>
       </c>
       <c r="C329">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D329">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>edsonbahienseb</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B330">
         <v>0</v>
       </c>
       <c r="C330">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D330">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>4lissson</v>
       </c>
       <c r="B331">
         <v>0</v>
       </c>
       <c r="C331">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D331">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>peacegrappler_archive</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5050,7 +5050,7 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5059,12 +5059,12 @@
         <v>1</v>
       </c>
       <c r="D333">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>helenaseveribjj</v>
+        <v>ommariotti</v>
       </c>
       <c r="B334">
         <v>0</v>
@@ -5073,12 +5073,12 @@
         <v>1</v>
       </c>
       <c r="D334">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>_kainanlima</v>
+        <v>brodschack_</v>
       </c>
       <c r="B335">
         <v>0</v>
@@ -5087,12 +5087,12 @@
         <v>1</v>
       </c>
       <c r="D335">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>jimmy_indioap</v>
+        <v>_vpft</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5101,12 +5101,12 @@
         <v>1</v>
       </c>
       <c r="D336">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>omar_alneaimi</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5115,12 +5115,12 @@
         <v>1</v>
       </c>
       <c r="D337">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>victor_brunopersonal</v>
+        <v>janjaovix</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5129,12 +5129,12 @@
         <v>1</v>
       </c>
       <c r="D338">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>motumbo_team</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5143,12 +5143,12 @@
         <v>1</v>
       </c>
       <c r="D339">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>vanemessina</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5157,12 +5157,12 @@
         <v>1</v>
       </c>
       <c r="D340">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>dadwillians</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5171,12 +5171,12 @@
         <v>1</v>
       </c>
       <c r="D341">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>thalytabjj</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5185,12 +5185,12 @@
         <v>1</v>
       </c>
       <c r="D342">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>esteticaluharruda</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>chubotaru_lilu</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B344">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>eusoufernandosaito</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B345">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>dandraco_</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>sejamotivadorofc</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>tpapereira</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B349">
         <v>0</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>kfcampeoes</v>
+        <v>vanemessina</v>
       </c>
       <c r="B350">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>herrickmarinho</v>
+        <v>dadwillians</v>
       </c>
       <c r="B351">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>rafaelcmjj</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B352">
         <v>0</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>cristianomarcello</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>_gabrielpego</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>taylor_71kg</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>dandraco_</v>
       </c>
       <c r="B356">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>doraasivla</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>pe.mirandas</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>leaoanaalice</v>
+        <v>tpapereira</v>
       </c>
       <c r="B359">
         <v>0</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>caioparangole</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B360">
         <v>0</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>sabrinaalsilva</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>eglaudiomma</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B363">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>strong_stg_oficial</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B364">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>ricardotofanello</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B365">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>taporondebruno</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B366">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>anamatias.m</v>
+        <v>doraasivla</v>
       </c>
       <c r="B367">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>claudio_marchese_7</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B368">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>1000ton_n</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B369">
         <v>0</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>paulo.titoo</v>
+        <v>caioparangole</v>
       </c>
       <c r="B370">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>vitorcosta_mma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B371">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>couragemma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B372">
         <v>0</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>romulerasilva</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B373">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>edergama.mma</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B374">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>alineanne_</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B375">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>julckreis</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B376">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>andreza.thais.1</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B377">
         <v>0</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>benicius_edu</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B378">
         <v>0</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B379">
         <v>0</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>michele_mixa</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B380">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>joaolauar_</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B381">
         <v>0</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>igorbrasileiro01</v>
+        <v>couragemma</v>
       </c>
       <c r="B382">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>felipeocalmon</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B383">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>rejr_mma</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B384">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>deivssonmanin</v>
+        <v>alineanne_</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>andrey_m_s_</v>
+        <v>julckreis</v>
       </c>
       <c r="B386">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>vidaldanin</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B387">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>barbaracontadora</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B388">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>natalves5</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B389">
         <v>0</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B390">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>boradepodcastoficial</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B391">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>audizioandrade</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B392">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>isadoragolimpio</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B393">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>dudu.acabamentos</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B394">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>katlembrenda</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B395">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>aline.amaral21</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B396">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>tamysregina</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B397">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>guilhermews1994</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B398">
         <v>0</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>percepcar</v>
+        <v>natalves5</v>
       </c>
       <c r="B399">
         <v>0</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>kevin.mota95</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B400">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>_marcos_.71</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B401">
         <v>0</v>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>douglas_vitor8</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B402">
         <v>0</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B403">
         <v>0</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>raulcarvalho1010</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B404">
         <v>0</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>roginbrito</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B405">
         <v>0</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>meirelesmma</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B406">
         <v>0</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>dvlucc2k26_</v>
+        <v>tamysregina</v>
       </c>
       <c r="B407">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>armysenju</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B408">
         <v>0</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>f.ostini</v>
+        <v>percepcar</v>
       </c>
       <c r="B409">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>fher.nando_</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B410">
         <v>0</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B411">
         <v>0</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>bastazinifilho</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B412">
         <v>0</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>pammygaryo</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B413">
         <v>0</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>anselmo.azevedo</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B414">
         <v>0</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>marcotulio_matuto</v>
+        <v>roginbrito</v>
       </c>
       <c r="B415">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>ianrochaf</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B416">
         <v>0</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>ale.lagonegro</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B417">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>ganemfelipe</v>
+        <v>armysenju</v>
       </c>
       <c r="B418">
         <v>0</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>marcusvgsz</v>
+        <v>f.ostini</v>
       </c>
       <c r="B419">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>wanderson.casttro</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B420">
         <v>0</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B421">
         <v>0</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>jotapeamancio</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B422">
         <v>0</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B423">
         <v>0</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B424">
         <v>0</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>zeferinomma</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B425">
         <v>0</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>tavaresguu</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B426">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>ildemarmarajo</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B427">
         <v>0</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>peterson_arrais</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B428">
         <v>0</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>danieldias7s</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B429">
         <v>0</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>ohanna.anselmo</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B430">
         <v>0</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>brun_oguerreiro</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B431">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>helman_mma70</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B432">
         <v>0</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>macio.almeida_89</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B433">
         <v>0</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>lyviaestherbjj</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B434">
         <v>0</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>wendel_bjj14</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B435">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>karine_killer_ufc</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B436">
         <v>0</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>andressa_bjj_</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B437">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>dreamartpro</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B438">
         <v>0</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>makelele_bjj</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B439">
         <v>0</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>fdanieljj</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B440">
         <v>0</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B441">
         <v>0</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>caioleonjj</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B442">
         <v>0</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B443">
         <v>0</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>malene_elleen</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B444">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>leonardoo_paixao</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B445">
         <v>0</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>josita_bjj</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B446">
         <v>0</v>
@@ -6646,28 +6646,238 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
+        <v>andressa_bjj_</v>
+      </c>
+      <c r="B447">
+        <v>0</v>
+      </c>
+      <c r="C447">
+        <v>1</v>
+      </c>
+      <c r="D447">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>dreamartpro</v>
+      </c>
+      <c r="B448">
+        <v>0</v>
+      </c>
+      <c r="C448">
+        <v>1</v>
+      </c>
+      <c r="D448">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
+        <v>makelele_bjj</v>
+      </c>
+      <c r="B449">
+        <v>0</v>
+      </c>
+      <c r="C449">
+        <v>1</v>
+      </c>
+      <c r="D449">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>fdanieljj</v>
+      </c>
+      <c r="B450">
+        <v>0</v>
+      </c>
+      <c r="C450">
+        <v>1</v>
+      </c>
+      <c r="D450">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>jeferson_tijolo1</v>
+      </c>
+      <c r="B451">
+        <v>0</v>
+      </c>
+      <c r="C451">
+        <v>1</v>
+      </c>
+      <c r="D451">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>caioleonjj</v>
+      </c>
+      <c r="B452">
+        <v>0</v>
+      </c>
+      <c r="C452">
+        <v>1</v>
+      </c>
+      <c r="D452">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>kevinlopes_bjj</v>
+      </c>
+      <c r="B453">
+        <v>0</v>
+      </c>
+      <c r="C453">
+        <v>1</v>
+      </c>
+      <c r="D453">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>malene_elleen</v>
+      </c>
+      <c r="B454">
+        <v>0</v>
+      </c>
+      <c r="C454">
+        <v>1</v>
+      </c>
+      <c r="D454">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>leonardoo_paixao</v>
+      </c>
+      <c r="B455">
+        <v>0</v>
+      </c>
+      <c r="C455">
+        <v>1</v>
+      </c>
+      <c r="D455">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="str">
+        <v>josita_bjj</v>
+      </c>
+      <c r="B456">
+        <v>0</v>
+      </c>
+      <c r="C456">
+        <v>1</v>
+      </c>
+      <c r="D456">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="str">
         <v>roxostrike</v>
       </c>
-      <c r="B447">
-        <v>0</v>
-      </c>
-      <c r="C447">
-        <v>1</v>
-      </c>
-      <c r="D447">
+      <c r="B457">
+        <v>0</v>
+      </c>
+      <c r="C457">
+        <v>1</v>
+      </c>
+      <c r="D457">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="str">
+        <v>ruanmiqueias</v>
+      </c>
+      <c r="B458">
+        <v>0</v>
+      </c>
+      <c r="C458">
+        <v>1</v>
+      </c>
+      <c r="D458">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="str">
+        <v>babimaciel1</v>
+      </c>
+      <c r="B459">
+        <v>0</v>
+      </c>
+      <c r="C459">
+        <v>1</v>
+      </c>
+      <c r="D459">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="str">
+        <v>manoel.brum</v>
+      </c>
+      <c r="B460">
+        <v>0</v>
+      </c>
+      <c r="C460">
+        <v>1</v>
+      </c>
+      <c r="D460">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="str">
+        <v>horadopower</v>
+      </c>
+      <c r="B461">
+        <v>0</v>
+      </c>
+      <c r="C461">
+        <v>1</v>
+      </c>
+      <c r="D461">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="str">
+        <v>lyvia_genuina</v>
+      </c>
+      <c r="B462">
+        <v>0</v>
+      </c>
+      <c r="C462">
+        <v>1</v>
+      </c>
+      <c r="D462">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D447"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D462"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D164"/>
+  <dimension ref="A1:D180"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6702,13 +6912,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>439</v>
+        <v>492</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>385</v>
+        <v>438</v>
       </c>
     </row>
     <row r="4">
@@ -6716,10 +6926,10 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>58</v>
@@ -6730,7 +6940,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -6744,13 +6954,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -6758,7 +6968,7 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C7">
         <v>2</v>
@@ -6772,13 +6982,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B8">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="9">
@@ -6786,7 +6996,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B9">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -6800,13 +7010,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -6814,7 +7024,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B11">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -6842,13 +7052,13 @@
         <v>ryangandraufc</v>
       </c>
       <c r="B13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -7077,10 +7287,10 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>karen.ottoni</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -7091,7 +7301,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>alfredo_miras</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B31">
         <v>2</v>
@@ -7105,55 +7315,55 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B32">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>badboykillermma</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>pedromadeira.s</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B34">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>livreseseguras</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -7161,21 +7371,21 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>_pizzariabambina_</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B37">
         <v>4</v>
@@ -7189,21 +7399,21 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>vndcardoso</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>artewebpersonalizados</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B39">
         <v>2</v>
@@ -7217,7 +7427,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>tatibscardoso</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B40">
         <v>2</v>
@@ -7231,7 +7441,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>z.proddd</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B41">
         <v>2</v>
@@ -7240,88 +7450,88 @@
         <v>0</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>multiplicaaba</v>
+        <v>z.proddd</v>
       </c>
       <c r="B42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>ronemayanmorais</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D43">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>meol.socialmidia</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>pitbullandrade</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>marcos_tailandess</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B46">
         <v>1</v>
       </c>
       <c r="C46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>tabajaraharu</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B47">
         <v>1</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47">
         <v>2</v>
@@ -7329,7 +7539,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ravenrodriguez___</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -7343,7 +7553,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>dogodoyfoto</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -7357,49 +7567,49 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>enzoferrari680</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>pedrinhosbjj</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>araujojonaspenhade</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -7413,7 +7623,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>jesabelmelo9</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -7427,7 +7637,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>marcocanatelli</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -7441,63 +7651,63 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>pvd_._dudis</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>boia_capoeira</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>sr.valter</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>devessonjj</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B59">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>tatianeaguiarp</v>
+        <v>sr.valter</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -7511,21 +7721,21 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>estevaotoledo</v>
+        <v>devessonjj</v>
       </c>
       <c r="B61">
         <v>1</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>kalindrafaria</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -7534,12 +7744,12 @@
         <v>0</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -7548,12 +7758,12 @@
         <v>1</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -7567,21 +7777,21 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>oniszczuk_ko</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>andreibjj</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -7595,7 +7805,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>chuck_tlp</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -7609,27 +7819,27 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>antonioemanuel.13</v>
+        <v>andreibjj</v>
       </c>
       <c r="B68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C68">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>gasparjr1983</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -7637,21 +7847,21 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>magnoddias</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -7665,13 +7875,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>gustavomohallem</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B72">
         <v>1</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -7679,13 +7889,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>atlta.marc0s</v>
+        <v>magnoddias</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -7693,7 +7903,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>arturbambam</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -7707,7 +7917,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>hermaan10_</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -7721,7 +7931,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>danieljsantoss_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -7735,7 +7945,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>rodrigojansen_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -7749,7 +7959,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>markakasocks</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -7763,7 +7973,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>hunter.mccrary</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -7777,7 +7987,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>omarcotomaz</v>
+        <v>markakasocks</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -7791,7 +8001,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>alphavillesup</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -7805,7 +8015,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>ricieritonan</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -7819,7 +8029,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>lucasampaio</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -7833,7 +8043,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>cjrnavalha</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -7847,7 +8057,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>natalan_wilgner</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -7861,7 +8071,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>manmoska</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -7875,7 +8085,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>renatoevangelistaa</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -7889,7 +8099,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>cassius.paula</v>
+        <v>manmoska</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -7903,7 +8113,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -7917,7 +8127,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>aliferpaulo_</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -7931,7 +8141,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -7945,7 +8155,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>rodrigolidiosales</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -7959,7 +8169,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>moisespira</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -7973,7 +8183,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>marciocatenacci</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -7987,7 +8197,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>cristiane.c.santana</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -8001,7 +8211,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>ariel_alvees</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -8015,7 +8225,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>flahvinhotreinador</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -8029,7 +8239,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -8043,7 +8253,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>selma.oscar12</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -8057,7 +8267,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>romulobelarmino</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -8071,7 +8281,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -8085,7 +8295,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>fernandamourabjj</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -8099,7 +8309,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>larissamartinsbjj</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -8113,7 +8323,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -8127,7 +8337,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>leitefelippez</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -8141,7 +8351,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>israelbahiensebraz</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -8155,7 +8365,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>wlt_miguel</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -8169,7 +8379,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>wesley_bjjvc</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -8183,7 +8393,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>juniordiasmma</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -8197,7 +8407,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>joselia_1980</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -8211,7 +8421,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>kaua_limamma</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -8225,153 +8435,153 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>guerreirammaofc</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>izabeldelfino_</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>janjaovix</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B114">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>edsonbahienseb</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>edebetim_</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>maca.mariotti</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B119">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>peacegrappler_archive</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B120">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>_oliveira09_</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>benjafloripabjj</v>
+        <v>santos39roger</v>
       </c>
       <c r="B122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -8379,21 +8589,21 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>f.ostini</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B123">
         <v>0</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>fher.nando_</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B124">
         <v>0</v>
@@ -8402,12 +8612,12 @@
         <v>1</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>janjaovix</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -8416,12 +8626,12 @@
         <v>1</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>bastazinifilho</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -8430,12 +8640,12 @@
         <v>1</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -8444,12 +8654,12 @@
         <v>1</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>pammygaryo</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -8458,12 +8668,12 @@
         <v>1</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>anselmo.azevedo</v>
+        <v>edebetim_</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -8472,12 +8682,12 @@
         <v>1</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>marcotulio_matuto</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -8486,12 +8696,12 @@
         <v>1</v>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>ianrochaf</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -8500,12 +8710,12 @@
         <v>1</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>ale.lagonegro</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -8514,12 +8724,12 @@
         <v>1</v>
       </c>
       <c r="D132">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>ganemfelipe</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -8533,7 +8743,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>f.ostini</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -8547,7 +8757,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>marcusvgsz</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -8561,7 +8771,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>wanderson.casttro</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -8575,7 +8785,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -8589,7 +8799,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>jotapeamancio</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -8603,7 +8813,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -8617,7 +8827,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -8631,7 +8841,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>zeferinomma</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -8645,7 +8855,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>tavaresguu</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -8659,7 +8869,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ildemarmarajo</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -8673,7 +8883,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -8687,7 +8897,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>peterson_arrais</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -8701,7 +8911,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>danieldias7s</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -8715,7 +8925,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>ohanna.anselmo</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -8729,7 +8939,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>brun_oguerreiro</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -8743,7 +8953,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>helman_mma70</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -8757,7 +8967,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>macio.almeida_89</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -8771,7 +8981,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>lyviaestherbjj</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -8785,7 +8995,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>wendel_bjj14</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -8799,7 +9009,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>karine_killer_ufc</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -8813,7 +9023,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>andressa_bjj_</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -8827,7 +9037,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>dreamartpro</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -8841,7 +9051,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>makelele_bjj</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -8855,7 +9065,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>fdanieljj</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -8869,7 +9079,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -8883,7 +9093,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>caioleonjj</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -8897,7 +9107,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -8911,7 +9121,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>malene_elleen</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -8925,7 +9135,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>leonardoo_paixao</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -8939,7 +9149,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>josita_bjj</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -8953,21 +9163,245 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
+        <v>karine_killer_ufc</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="D164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>andressa_bjj_</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
+      </c>
+      <c r="D165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>dreamartpro</v>
+      </c>
+      <c r="B166">
+        <v>0</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+      <c r="D166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>makelele_bjj</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="D167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>fdanieljj</v>
+      </c>
+      <c r="B168">
+        <v>0</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+      <c r="D168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>jeferson_tijolo1</v>
+      </c>
+      <c r="B169">
+        <v>0</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="D169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>caioleonjj</v>
+      </c>
+      <c r="B170">
+        <v>0</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="D170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>kevinlopes_bjj</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="D171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>malene_elleen</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="D172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>leonardoo_paixao</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>josita_bjj</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+      <c r="C174">
+        <v>1</v>
+      </c>
+      <c r="D174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
         <v>roxostrike</v>
       </c>
-      <c r="B164">
-        <v>0</v>
-      </c>
-      <c r="C164">
-        <v>1</v>
-      </c>
-      <c r="D164">
+      <c r="B175">
+        <v>0</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+      <c r="D175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>ruanmiqueias</v>
+      </c>
+      <c r="B176">
+        <v>0</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+      <c r="D176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>babimaciel1</v>
+      </c>
+      <c r="B177">
+        <v>0</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+      <c r="D177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>manoel.brum</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+      <c r="C178">
+        <v>1</v>
+      </c>
+      <c r="D178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>horadopower</v>
+      </c>
+      <c r="B179">
+        <v>0</v>
+      </c>
+      <c r="C179">
+        <v>1</v>
+      </c>
+      <c r="D179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>lyvia_genuina</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D164"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D180"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>493</v>
+        <v>530</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>438</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5">
@@ -472,30 +472,30 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B6">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>90</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>pablofiorindi</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B7">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="C7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -503,13 +503,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9">
@@ -531,13 +531,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B10">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C10">
         <v>2</v>
       </c>
       <c r="D10">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11">
@@ -545,13 +545,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B11">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12">
@@ -573,13 +573,13 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B13">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -590,10 +590,10 @@
         <v>49</v>
       </c>
       <c r="C14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
@@ -716,7 +716,7 @@
         <v>9</v>
       </c>
       <c r="C23">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D23">
         <v>43</v>
@@ -948,55 +948,55 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>rrafaelins</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C40">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>juniordiasmma</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B41">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B42">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>enzoferrari680</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B43">
         <v>7</v>
       </c>
       <c r="C43">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>2</v>
@@ -1004,30 +1004,30 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>italothearcher</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C44">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D44">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ninjatheorist</v>
+        <v>italothearcher</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D45">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46">
@@ -6912,13 +6912,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>492</v>
+        <v>529</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>438</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4">
@@ -6926,13 +6926,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="D4">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
@@ -6940,13 +6940,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>69</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6">
@@ -6982,13 +6982,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B8">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C8">
         <v>1</v>
       </c>
       <c r="D8">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
@@ -6996,13 +6996,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B9">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -7010,13 +7010,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -7055,10 +7055,10 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14">
@@ -7080,13 +7080,13 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16">
@@ -7167,7 +7167,7 @@
         <v>2</v>
       </c>
       <c r="C21">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D21">
         <v>14</v>
@@ -7175,30 +7175,30 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>gra_jpereira</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ninjatheorist</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">

--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>530</v>
+        <v>561</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4">
@@ -447,7 +447,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C4">
         <v>11</v>
@@ -461,13 +461,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B5">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C5">
         <v>26</v>
       </c>
       <c r="D5">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6">
@@ -475,13 +475,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B6">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C6">
         <v>11</v>
       </c>
       <c r="D6">
-        <v>101</v>
+        <v>104</v>
       </c>
     </row>
     <row r="7">
@@ -503,13 +503,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C8">
         <v>4</v>
       </c>
       <c r="D8">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9">
@@ -528,30 +528,30 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>rm.nicki</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B10">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>109</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>hugo7jj</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B11">
-        <v>157</v>
+        <v>125</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
-        <v>74</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -590,7 +590,7 @@
         <v>49</v>
       </c>
       <c r="C14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14">
         <v>50</v>
@@ -643,13 +643,13 @@
         <v>combintel</v>
       </c>
       <c r="B18">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -836,30 +836,30 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B32">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
         <v>5</v>
-      </c>
-      <c r="D32">
-        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>marc0s.azv</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B33">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34">
@@ -1046,55 +1046,55 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>gdazuera</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B47">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C47">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>gdazuera</v>
       </c>
       <c r="B48">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D48">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>excelentfightcompetition</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B49">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ravenrodriguez___</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B50">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C50">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -1102,30 +1102,30 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B51">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>kauepraciano</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B52">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -6895,30 +6895,30 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>peacegrappler_mma</v>
+        <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>503</v>
+        <v>560</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>485</v>
+        <v>472</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>peacegrappler</v>
+        <v>peacegrappler_mma</v>
       </c>
       <c r="B3">
-        <v>529</v>
+        <v>503</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>467</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4">
@@ -6926,13 +6926,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C4">
         <v>4</v>
       </c>
       <c r="D4">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -6940,7 +6940,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -6965,44 +6965,44 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>rpsantos_mma</v>
+        <v>pedr00jj</v>
       </c>
       <c r="B7">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>rm.nicki</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B8">
-        <v>87</v>
+        <v>123</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>pedr00jj</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B9">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>46</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -7010,7 +7010,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -7024,13 +7024,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B11">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
@@ -7055,7 +7055,7 @@
         <v>13</v>
       </c>
       <c r="C13">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D13">
         <v>21</v>
@@ -7094,13 +7094,13 @@
         <v>combintel</v>
       </c>
       <c r="B16">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -7108,7 +7108,7 @@
         <v>marc0s.azv</v>
       </c>
       <c r="B17">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17">
         <v>1</v>
@@ -7203,13 +7203,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>excelentfightcompetition</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -7217,13 +7217,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>kauepraciano</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D25">
         <v>2</v>

--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D462"/>
+  <dimension ref="A1:D463"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="5">
@@ -461,13 +461,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B5">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C5">
         <v>26</v>
       </c>
       <c r="D5">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6">
@@ -475,10 +475,10 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B6">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>104</v>
@@ -489,7 +489,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B7">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -531,7 +531,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B10">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -643,7 +643,7 @@
         <v>combintel</v>
       </c>
       <c r="B18">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -797,7 +797,7 @@
         <v>eliassilverio</v>
       </c>
       <c r="B29">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C29">
         <v>8</v>
@@ -1004,13 +1004,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>enzoferrari680</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B44">
         <v>7</v>
       </c>
       <c r="C44">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>2</v>
@@ -1018,44 +1018,44 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>italothearcher</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B45">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C45">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D45">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>badboykillermma</v>
+        <v>italothearcher</v>
       </c>
       <c r="B46">
         <v>4</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D46">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>kauepraciano</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B47">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -2390,13 +2390,13 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>viktor.torquato</v>
       </c>
       <c r="B143">
         <v>1</v>
       </c>
       <c r="C143">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D143">
         <v>1</v>
@@ -2404,27 +2404,27 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>treinaadorrafael</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>benjafloripabjj</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D145">
         <v>0</v>
@@ -2432,13 +2432,13 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>fernando.mma</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -2446,13 +2446,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -2460,13 +2460,13 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>estevaotoledo</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B148">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -2474,13 +2474,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B149">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -2502,13 +2502,13 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B151">
         <v>1</v>
       </c>
       <c r="C151">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>guiiviieira_</v>
+        <v>030sami</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,13 +2684,13 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B164">
         <v>1</v>
       </c>
       <c r="C164">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -2698,13 +2698,13 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>kalindrafaria</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B165">
         <v>1</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -2712,35 +2712,35 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B166">
         <v>1</v>
       </c>
       <c r="C166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D166">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B167">
         <v>1</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D167">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>chuck_tlp</v>
+        <v>andreibjj</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,35 +2782,35 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>cristianpsicologo</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B171">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C171">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D171">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C172">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,35 +2852,35 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>antonioemanuel.13</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C176">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D176">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C177">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,7 +2894,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>magnoddias</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,13 +2908,13 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>tonketjudes</v>
+        <v>magnoddias</v>
       </c>
       <c r="B180">
         <v>1</v>
       </c>
       <c r="C180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D180">
         <v>0</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,35 +3216,35 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B202">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C202">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D202">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C203">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>jaonevesz</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>camii_bonfim</v>
+        <v>flazuera14</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>sambagabrieloficial</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>_alcantara.bru</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B248">
         <v>1</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B249">
         <v>1</v>
@@ -3888,13 +3888,13 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B250">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C250">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D250">
         <v>0</v>
@@ -3902,13 +3902,13 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B251">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C251">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D251">
         <v>0</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B252">
         <v>1</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B257">
         <v>1</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B260">
         <v>1</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B261">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B262">
         <v>1</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B263">
         <v>1</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B264">
         <v>1</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B265">
         <v>1</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B266">
         <v>1</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>gustavomohallem</v>
+        <v>turmanmma</v>
       </c>
       <c r="B268">
         <v>1</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>atlta.marc0s</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B269">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B270">
         <v>1</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>hermaan10_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B271">
         <v>1</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B273">
         <v>1</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B275">
         <v>1</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B276">
         <v>1</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B277">
         <v>1</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B278">
         <v>1</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B279">
         <v>1</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>natalan_wilgner</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B280">
         <v>1</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B281">
         <v>1</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B282">
         <v>1</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B283">
         <v>1</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B284">
         <v>1</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B285">
         <v>1</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B286">
         <v>1</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B287">
         <v>1</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B288">
         <v>1</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B289">
         <v>1</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B291">
         <v>1</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B292">
         <v>1</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B293">
         <v>1</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B294">
         <v>1</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>fernandamourabjj</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B295">
         <v>1</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B296">
         <v>1</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B297">
         <v>1</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B298">
         <v>1</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B299">
         <v>1</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>joselia_1980</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B300">
         <v>1</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>soniarochaco</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B301">
         <v>1</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>leandro_pedro7</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B302">
         <v>1</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>camillinhamma</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B303">
         <v>1</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>martins.rauanee</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B304">
         <v>1</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>ever.soulson</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B305">
         <v>1</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>mestrevascobento</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B306">
         <v>1</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B307">
         <v>1</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B308">
         <v>1</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>santos39roger</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B309">
         <v>1</v>
@@ -4728,13 +4728,13 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>marinealcausa</v>
+        <v>santos39roger</v>
       </c>
       <c r="B310">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C310">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D310">
         <v>0</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -4756,63 +4756,63 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B312">
         <v>0</v>
       </c>
       <c r="C312">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D312">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B313">
         <v>0</v>
       </c>
       <c r="C313">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D313">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>giulia.fasolato</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B314">
         <v>0</v>
       </c>
       <c r="C314">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D314">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B315">
         <v>0</v>
       </c>
       <c r="C315">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D315">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -4826,21 +4826,21 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B317">
         <v>0</v>
       </c>
       <c r="C317">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D317">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>dayanaa1511</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>guerreirammaofc</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4877,26 +4877,26 @@
         <v>2</v>
       </c>
       <c r="D320">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>vanessamelomma</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B321">
         <v>0</v>
       </c>
       <c r="C321">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D321">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,21 +4924,21 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B324">
         <v>0</v>
       </c>
       <c r="C324">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D324">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4966,21 +4966,21 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B327">
         <v>0</v>
       </c>
       <c r="C327">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D327">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,21 +4994,21 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B329">
         <v>0</v>
       </c>
       <c r="C329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D329">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,21 +5036,21 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B332">
         <v>0</v>
       </c>
       <c r="C332">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D332">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>ommariotti</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B334">
         <v>0</v>
@@ -5078,7 +5078,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>brodschack_</v>
+        <v>ommariotti</v>
       </c>
       <c r="B335">
         <v>0</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>_vpft</v>
+        <v>brodschack_</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>izabeldelfino_</v>
+        <v>_vpft</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>janjaovix</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>janjaovix</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>peacegrappler_archive</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5199,12 +5199,12 @@
         <v>1</v>
       </c>
       <c r="D343">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B344">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B345">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B349">
         <v>0</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B350">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B351">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B352">
         <v>0</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>esteticaluharruda</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B356">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B359">
         <v>0</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B360">
         <v>0</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B363">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B364">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B365">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B366">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B367">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B368">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B369">
         <v>0</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B370">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B371">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B372">
         <v>0</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B373">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B374">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B375">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B376">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B377">
         <v>0</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B378">
         <v>0</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B379">
         <v>0</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B380">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B381">
         <v>0</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B382">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B383">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B384">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B386">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B387">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B388">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B389">
         <v>0</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B390">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B391">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B392">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B393">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B394">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B395">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B396">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B397">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B398">
         <v>0</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B399">
         <v>0</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B400">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B401">
         <v>0</v>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B402">
         <v>0</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B403">
         <v>0</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B404">
         <v>0</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B405">
         <v>0</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B406">
         <v>0</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B407">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B408">
         <v>0</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B409">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B410">
         <v>0</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B411">
         <v>0</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B412">
         <v>0</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B413">
         <v>0</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B414">
         <v>0</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B415">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B416">
         <v>0</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>dvlucc2k26_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B417">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>armysenju</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B418">
         <v>0</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>f.ostini</v>
+        <v>armysenju</v>
       </c>
       <c r="B419">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>fher.nando_</v>
+        <v>f.ostini</v>
       </c>
       <c r="B420">
         <v>0</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B421">
         <v>0</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>bastazinifilho</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B422">
         <v>0</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>pammygaryo</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B423">
         <v>0</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>anselmo.azevedo</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B424">
         <v>0</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>marcotulio_matuto</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B425">
         <v>0</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>ianrochaf</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B426">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>ale.lagonegro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B427">
         <v>0</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>ganemfelipe</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B428">
         <v>0</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>marcusvgsz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B429">
         <v>0</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>wanderson.casttro</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B430">
         <v>0</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B431">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>jotapeamancio</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B432">
         <v>0</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B433">
         <v>0</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B434">
         <v>0</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>zeferinomma</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B435">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>tavaresguu</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B436">
         <v>0</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>ildemarmarajo</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B437">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>peterson_arrais</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B438">
         <v>0</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>danieldias7s</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B439">
         <v>0</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>ohanna.anselmo</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B440">
         <v>0</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B441">
         <v>0</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>helman_mma70</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B442">
         <v>0</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>macio.almeida_89</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B443">
         <v>0</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>lyviaestherbjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B444">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>wendel_bjj14</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B445">
         <v>0</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>karine_killer_ufc</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B446">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>andressa_bjj_</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B447">
         <v>0</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>dreamartpro</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B448">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>makelele_bjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B449">
         <v>0</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>fdanieljj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B450">
         <v>0</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B451">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>caioleonjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B452">
         <v>0</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B453">
         <v>0</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>malene_elleen</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B454">
         <v>0</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>leonardoo_paixao</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B455">
         <v>0</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>josita_bjj</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B456">
         <v>0</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>roxostrike</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B457">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>ruanmiqueias</v>
+        <v>roxostrike</v>
       </c>
       <c r="B458">
         <v>0</v>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>babimaciel1</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B459">
         <v>0</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>manoel.brum</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B460">
         <v>0</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>horadopower</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B461">
         <v>0</v>
@@ -6856,28 +6856,42 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
+        <v>horadopower</v>
+      </c>
+      <c r="B462">
+        <v>0</v>
+      </c>
+      <c r="C462">
+        <v>1</v>
+      </c>
+      <c r="D462">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="str">
         <v>lyvia_genuina</v>
       </c>
-      <c r="B462">
-        <v>0</v>
-      </c>
-      <c r="C462">
-        <v>1</v>
-      </c>
-      <c r="D462">
+      <c r="B463">
+        <v>0</v>
+      </c>
+      <c r="C463">
+        <v>1</v>
+      </c>
+      <c r="D463">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D462"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D463"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D180"/>
+  <dimension ref="A1:D181"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6898,13 +6912,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="3">
@@ -6926,10 +6940,10 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>66</v>
@@ -6940,7 +6954,7 @@
         <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -6954,7 +6968,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -7010,13 +7024,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -7024,13 +7038,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B11">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
@@ -7063,35 +7077,35 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>mmmarc20</v>
+        <v>combintel</v>
       </c>
       <c r="B14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>anaaj_camargo</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>combintel</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B16">
         <v>13</v>
@@ -7100,7 +7114,7 @@
         <v>0</v>
       </c>
       <c r="D16">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17">
@@ -7189,30 +7203,30 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>gra_jpereira</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B23">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>kauepraciano</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -7245,13 +7259,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>alvesmidih</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -7259,13 +7273,13 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>eliassilverio</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B28">
         <v>3</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -7749,27 +7763,27 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>estevaotoledo</v>
+        <v>viktor.torquato</v>
       </c>
       <c r="B63">
         <v>1</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>kalindrafaria</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D64">
         <v>0</v>
@@ -7777,35 +7791,35 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -7819,7 +7833,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -7833,7 +7847,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>chuck_tlp</v>
+        <v>andreibjj</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -7847,35 +7861,35 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>antonioemanuel.13</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C70">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -7889,7 +7903,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>magnoddias</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -7903,13 +7917,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>gustavomohallem</v>
+        <v>magnoddias</v>
       </c>
       <c r="B74">
         <v>1</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -7917,7 +7931,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>atlta.marc0s</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -7931,7 +7945,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -7945,7 +7959,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>hermaan10_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -7959,7 +7973,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -7973,7 +7987,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -7987,7 +8001,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -8001,7 +8015,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -8015,7 +8029,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -8029,7 +8043,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -8043,7 +8057,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -8057,7 +8071,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -8071,7 +8085,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>cjrnavalha</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -8085,7 +8099,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>natalan_wilgner</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -8099,7 +8113,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -8113,7 +8127,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -8127,7 +8141,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -8141,7 +8155,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -8155,7 +8169,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>aliferpaulo_</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -8169,7 +8183,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>moisespira</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -8183,7 +8197,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -8197,7 +8211,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -8211,7 +8225,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -8225,7 +8239,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -8239,7 +8253,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -8253,7 +8267,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -8267,7 +8281,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -8281,7 +8295,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -8295,7 +8309,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -8309,7 +8323,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -8323,7 +8337,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>fernandamourabjj</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -8337,7 +8351,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -8351,7 +8365,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -8365,7 +8379,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -8379,7 +8393,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -8393,7 +8407,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>wlt_miguel</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -8407,7 +8421,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>wesley_bjjvc</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -8421,7 +8435,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>juniordiasmma</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -8435,7 +8449,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>joselia_1980</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -8449,7 +8463,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>kaua_limamma</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -8463,7 +8477,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>soniarochaco</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -8477,7 +8491,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>leandro_pedro7</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -8491,7 +8505,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>camillinhamma</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -8505,7 +8519,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>martins.rauanee</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -8519,7 +8533,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>ever.soulson</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -8533,7 +8547,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>mestrevascobento</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -8547,7 +8561,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -8561,7 +8575,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -8575,7 +8589,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>santos39roger</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -8589,27 +8603,27 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>guerreirammaofc</v>
+        <v>santos39roger</v>
       </c>
       <c r="B123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C123">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>izabeldelfino_</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B124">
         <v>0</v>
       </c>
       <c r="C124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -8617,7 +8631,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>janjaovix</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B125">
         <v>0</v>
@@ -8631,7 +8645,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>janjaovix</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -8645,7 +8659,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B127">
         <v>0</v>
@@ -8659,7 +8673,7 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B128">
         <v>0</v>
@@ -8673,7 +8687,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>edebetim_</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -8687,7 +8701,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>maca.mariotti</v>
+        <v>edebetim_</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -8701,7 +8715,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>peacegrappler_archive</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -8715,7 +8729,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>_oliveira09_</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -8729,7 +8743,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>benjafloripabjj</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -8738,12 +8752,12 @@
         <v>1</v>
       </c>
       <c r="D133">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>f.ostini</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -8757,7 +8771,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>fher.nando_</v>
+        <v>f.ostini</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -8771,7 +8785,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -8785,7 +8799,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>bastazinifilho</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -8799,7 +8813,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -8813,7 +8827,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>pammygaryo</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -8827,7 +8841,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>anselmo.azevedo</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -8841,7 +8855,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>marcotulio_matuto</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -8855,7 +8869,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ianrochaf</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -8869,7 +8883,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ale.lagonegro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -8883,7 +8897,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>ganemfelipe</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -8897,7 +8911,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -8911,7 +8925,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>marcusvgsz</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -8925,7 +8939,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>wanderson.casttro</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -8939,7 +8953,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -8953,7 +8967,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>jotapeamancio</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -8967,7 +8981,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -8981,7 +8995,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -8995,7 +9009,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>zeferinomma</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -9009,7 +9023,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>tavaresguu</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -9023,7 +9037,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>ildemarmarajo</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -9037,7 +9051,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -9051,7 +9065,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>peterson_arrais</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -9065,7 +9079,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>danieldias7s</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -9079,7 +9093,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>ohanna.anselmo</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -9093,7 +9107,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -9107,7 +9121,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>helman_mma70</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -9121,7 +9135,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>macio.almeida_89</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -9135,7 +9149,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>lyviaestherbjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -9149,7 +9163,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>wendel_bjj14</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -9163,7 +9177,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>karine_killer_ufc</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -9177,7 +9191,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>andressa_bjj_</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -9191,7 +9205,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>dreamartpro</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -9205,7 +9219,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>makelele_bjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -9219,7 +9233,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>fdanieljj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -9233,7 +9247,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -9247,7 +9261,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>caioleonjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -9261,7 +9275,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -9275,7 +9289,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>malene_elleen</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -9289,7 +9303,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>leonardoo_paixao</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -9303,7 +9317,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>josita_bjj</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -9317,7 +9331,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>roxostrike</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -9331,7 +9345,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>ruanmiqueias</v>
+        <v>roxostrike</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -9345,7 +9359,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>babimaciel1</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -9359,7 +9373,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>manoel.brum</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -9373,7 +9387,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>horadopower</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -9387,21 +9401,35 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
+        <v>horadopower</v>
+      </c>
+      <c r="B180">
+        <v>0</v>
+      </c>
+      <c r="C180">
+        <v>1</v>
+      </c>
+      <c r="D180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
         <v>lyvia_genuina</v>
       </c>
-      <c r="B180">
-        <v>0</v>
-      </c>
-      <c r="C180">
-        <v>1</v>
-      </c>
-      <c r="D180">
+      <c r="B181">
+        <v>0</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+      <c r="D181">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D180"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D463"/>
+  <dimension ref="A1:D465"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>577</v>
+        <v>639</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>475</v>
+        <v>512</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B5">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C5">
         <v>26</v>
@@ -475,13 +475,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B6">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="C6">
         <v>12</v>
       </c>
       <c r="D6">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7">
@@ -489,13 +489,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B7">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
       <c r="D7">
-        <v>90</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8">
@@ -517,10 +517,10 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B9">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>61</v>
@@ -531,13 +531,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B10">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="11">
@@ -626,30 +626,30 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ronemayanmorais</v>
+        <v>combintel</v>
       </c>
       <c r="B17">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C17">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17">
-        <v>11</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>combintel</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B18">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18">
-        <v>21</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19">
@@ -808,86 +808,86 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>tiwimma</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B30">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>pedromadeira.s</v>
+        <v>tiwimma</v>
       </c>
       <c r="B31">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>marc0s.azv</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B32">
         <v>14</v>
       </c>
       <c r="C32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B33">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
         <v>5</v>
-      </c>
-      <c r="D33">
-        <v>9</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>cjrnavalha</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B34">
         <v>11</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D34">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>tabajaraharu</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B35">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C35">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36">
@@ -1032,153 +1032,153 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>italothearcher</v>
+        <v>gdazuera</v>
       </c>
       <c r="B46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C46">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D46">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>badboykillermma</v>
+        <v>italothearcher</v>
       </c>
       <c r="B47">
         <v>4</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D47">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>gdazuera</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D48">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B49">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>excelentfightcompetition</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B50">
         <v>4</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ravenrodriguez___</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B51">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B52">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>marcos_tailandess</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B53">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C53">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D53">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>eolucasrosa</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B54">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C54">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>dagestan0920</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>paxlucta</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B56">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C56">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -1186,44 +1186,44 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>_.maduoliveira_</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B57">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>dogodoyfoto</v>
+        <v>paxlucta</v>
       </c>
       <c r="B58">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D58">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>adriano.trator</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C59">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60">
@@ -1578,35 +1578,35 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>reifernandes</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D85">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B86">
         <v>2</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B87">
         <v>2</v>
@@ -1620,16 +1620,16 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>maca.mariotti</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C88">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -2404,13 +2404,13 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B144">
         <v>1</v>
       </c>
       <c r="C144">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D144">
         <v>1</v>
@@ -2418,27 +2418,27 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>treinaadorrafael</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D145">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>benjafloripabjj</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D146">
         <v>0</v>
@@ -2446,13 +2446,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>fernando.mma</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -2460,13 +2460,13 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B148">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -2474,13 +2474,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>estevaotoledo</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B149">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -2488,13 +2488,13 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B150">
         <v>1</v>
       </c>
       <c r="C150">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -2502,7 +2502,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -2516,13 +2516,13 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B152">
         <v>1</v>
       </c>
       <c r="C152">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>guiiviieira_</v>
+        <v>030sami</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,13 +2698,13 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B165">
         <v>1</v>
       </c>
       <c r="C165">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -2712,13 +2712,13 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>kalindrafaria</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B166">
         <v>1</v>
       </c>
       <c r="C166">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -2726,35 +2726,35 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B167">
         <v>1</v>
       </c>
       <c r="C167">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D167">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B168">
         <v>1</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,7 +2768,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>chuck_tlp</v>
+        <v>andreibjj</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,35 +2796,35 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>cristianpsicologo</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C172">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D172">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C173">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D173">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,7 +2838,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,35 +2866,35 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>antonioemanuel.13</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C177">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D177">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C178">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>magnoddias</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,13 +2922,13 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>tonketjudes</v>
+        <v>magnoddias</v>
       </c>
       <c r="B181">
         <v>1</v>
       </c>
       <c r="C181">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D181">
         <v>0</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,35 +3230,35 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B203">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C203">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D203">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C204">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,7 +3272,7 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,7 +3328,7 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>jaonevesz</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>camii_bonfim</v>
+        <v>flazuera14</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>sambagabrieloficial</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>_alcantara.bru</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B248">
         <v>1</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B249">
         <v>1</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B250">
         <v>1</v>
@@ -3902,13 +3902,13 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B251">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C251">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D251">
         <v>0</v>
@@ -3916,13 +3916,13 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B252">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C252">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D252">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B257">
         <v>1</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B260">
         <v>1</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B261">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B262">
         <v>1</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B263">
         <v>1</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B264">
         <v>1</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B265">
         <v>1</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B266">
         <v>1</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B268">
         <v>1</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>gustavomohallem</v>
+        <v>turmanmma</v>
       </c>
       <c r="B269">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>atlta.marc0s</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B270">
         <v>1</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B271">
         <v>1</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>hermaan10_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B273">
         <v>1</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B275">
         <v>1</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B276">
         <v>1</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B277">
         <v>1</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B278">
         <v>1</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B279">
         <v>1</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B280">
         <v>1</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>natalan_wilgner</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B281">
         <v>1</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B282">
         <v>1</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B283">
         <v>1</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B284">
         <v>1</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B285">
         <v>1</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B286">
         <v>1</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B287">
         <v>1</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B288">
         <v>1</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B289">
         <v>1</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B291">
         <v>1</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B292">
         <v>1</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B293">
         <v>1</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B294">
         <v>1</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B295">
         <v>1</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>fernandamourabjj</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B296">
         <v>1</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B297">
         <v>1</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B298">
         <v>1</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B299">
         <v>1</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B300">
         <v>1</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>joselia_1980</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B301">
         <v>1</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>soniarochaco</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B302">
         <v>1</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>leandro_pedro7</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B303">
         <v>1</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>camillinhamma</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B304">
         <v>1</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>martins.rauanee</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B305">
         <v>1</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>ever.soulson</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B306">
         <v>1</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>mestrevascobento</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B307">
         <v>1</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B308">
         <v>1</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B309">
         <v>1</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>santos39roger</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B310">
         <v>1</v>
@@ -4742,13 +4742,13 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>marinealcausa</v>
+        <v>santos39roger</v>
       </c>
       <c r="B311">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C311">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D311">
         <v>0</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -4770,105 +4770,105 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B313">
         <v>0</v>
       </c>
       <c r="C313">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D313">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B314">
         <v>0</v>
       </c>
       <c r="C314">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D314">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>giulia.fasolato</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B315">
         <v>0</v>
       </c>
       <c r="C315">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D315">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>michelle_mirele</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B316">
         <v>0</v>
       </c>
       <c r="C316">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D316">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>danielfranzesilva</v>
+        <v>brodschack_</v>
       </c>
       <c r="B317">
         <v>0</v>
       </c>
       <c r="C317">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D317">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>ednilsonkaicai</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B318">
         <v>0</v>
       </c>
       <c r="C318">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D318">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>dayanaa1511</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B319">
         <v>0</v>
       </c>
       <c r="C319">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D319">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>guerreirammaofc</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,7 +4882,7 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4891,18 +4891,18 @@
         <v>2</v>
       </c>
       <c r="D321">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>vanessamelomma</v>
+        <v>ommariotti</v>
       </c>
       <c r="B322">
         <v>0</v>
       </c>
       <c r="C322">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D322">
         <v>1</v>
@@ -4910,13 +4910,13 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>leonardopateira</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B323">
         <v>0</v>
       </c>
       <c r="C323">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D323">
         <v>1</v>
@@ -4924,13 +4924,13 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>rahikikhalid</v>
+        <v>pedro_giraldi</v>
       </c>
       <c r="B324">
         <v>0</v>
       </c>
       <c r="C324">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D324">
         <v>1</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>manumito.oficial</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,35 +4952,35 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>carlosnoelblack</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B326">
         <v>0</v>
       </c>
       <c r="C326">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D326">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B327">
         <v>0</v>
       </c>
       <c r="C327">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D327">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>lokomemo_protetores</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,21 +4994,21 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>coutz11</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B329">
         <v>0</v>
       </c>
       <c r="C329">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D329">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>orlando_alfa09</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>vitorshowman</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,21 +5036,21 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>4lissson</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B332">
         <v>0</v>
       </c>
       <c r="C332">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D332">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>danilofernandescf</v>
+        <v>coutz11</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,49 +5064,49 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>bryandazuera</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B334">
         <v>0</v>
       </c>
       <c r="C334">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D334">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>ommariotti</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B335">
         <v>0</v>
       </c>
       <c r="C335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D335">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>brodschack_</v>
+        <v>4lissson</v>
       </c>
       <c r="B336">
         <v>0</v>
       </c>
       <c r="C336">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D336">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>_vpft</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5120,7 +5120,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>izabeldelfino_</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>janjaovix</v>
+        <v>_vpft</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>edsonbahienseb</v>
+        <v>janjaovix</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>peacegrappler_archive</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B344">
         <v>0</v>
@@ -5213,12 +5213,12 @@
         <v>1</v>
       </c>
       <c r="D344">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>helenaseveribjj</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B345">
         <v>0</v>
@@ -5227,12 +5227,12 @@
         <v>1</v>
       </c>
       <c r="D345">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>_kainanlima</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>jimmy_indioap</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>omar_alneaimi</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>victor_brunopersonal</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B349">
         <v>0</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>motumbo_team</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B350">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>vanemessina</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B351">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>dadwillians</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B352">
         <v>0</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>thalytabjj</v>
+        <v>vanemessina</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>esteticaluharruda</v>
+        <v>dadwillians</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>chubotaru_lilu</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>eusoufernandosaito</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B356">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>dandraco_</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>sejamotivadorofc</v>
+        <v>dandraco_</v>
       </c>
       <c r="B359">
         <v>0</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>tpapereira</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B360">
         <v>0</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>kfcampeoes</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>herrickmarinho</v>
+        <v>tpapereira</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>rafaelcmjj</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B363">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>cristianomarcello</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B364">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>_gabrielpego</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B365">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>taylor_71kg</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B366">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B367">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>doraasivla</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B368">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>pe.mirandas</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B369">
         <v>0</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>leaoanaalice</v>
+        <v>doraasivla</v>
       </c>
       <c r="B370">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>caioparangole</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B371">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>sabrinaalsilva</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B372">
         <v>0</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>caioparangole</v>
       </c>
       <c r="B373">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>eglaudiomma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B374">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>strong_stg_oficial</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B375">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>ricardotofanello</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B376">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>taporondebruno</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B377">
         <v>0</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>anamatias.m</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B378">
         <v>0</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>claudio_marchese_7</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B379">
         <v>0</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>1000ton_n</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B380">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>paulo.titoo</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B381">
         <v>0</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>vitorcosta_mma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B382">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>couragemma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B383">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>romulerasilva</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B384">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>edergama.mma</v>
+        <v>couragemma</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>alineanne_</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B386">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>julckreis</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B387">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>andreza.thais.1</v>
+        <v>alineanne_</v>
       </c>
       <c r="B388">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>benicius_edu</v>
+        <v>julckreis</v>
       </c>
       <c r="B389">
         <v>0</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B390">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>michele_mixa</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B391">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>joaolauar_</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B392">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>igorbrasileiro01</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B393">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>felipeocalmon</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B394">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>rejr_mma</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B395">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>deivssonmanin</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B396">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>andrey_m_s_</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B397">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>vidaldanin</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B398">
         <v>0</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>barbaracontadora</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B399">
         <v>0</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>natalves5</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B400">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B401">
         <v>0</v>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>boradepodcastoficial</v>
+        <v>natalves5</v>
       </c>
       <c r="B402">
         <v>0</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>audizioandrade</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B403">
         <v>0</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>isadoragolimpio</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B404">
         <v>0</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>dudu.acabamentos</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B405">
         <v>0</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>katlembrenda</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B406">
         <v>0</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>aline.amaral21</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B407">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>tamysregina</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B408">
         <v>0</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>guilhermews1994</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B409">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>percepcar</v>
+        <v>tamysregina</v>
       </c>
       <c r="B410">
         <v>0</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>kevin.mota95</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B411">
         <v>0</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>_marcos_.71</v>
+        <v>percepcar</v>
       </c>
       <c r="B412">
         <v>0</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B413">
         <v>0</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B414">
         <v>0</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>raulcarvalho1010</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B415">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>roginbrito</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B416">
         <v>0</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>meirelesmma</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B417">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>dvlucc2k26_</v>
+        <v>roginbrito</v>
       </c>
       <c r="B418">
         <v>0</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>armysenju</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B419">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>f.ostini</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B420">
         <v>0</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>fher.nando_</v>
+        <v>armysenju</v>
       </c>
       <c r="B421">
         <v>0</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>f.ostini</v>
       </c>
       <c r="B422">
         <v>0</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>bastazinifilho</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B423">
         <v>0</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>pammygaryo</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B424">
         <v>0</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>anselmo.azevedo</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B425">
         <v>0</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>marcotulio_matuto</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B426">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>ianrochaf</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B427">
         <v>0</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>ale.lagonegro</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B428">
         <v>0</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>ganemfelipe</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B429">
         <v>0</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>marcusvgsz</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B430">
         <v>0</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>wanderson.casttro</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B431">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B432">
         <v>0</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>jotapeamancio</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B433">
         <v>0</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B434">
         <v>0</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B435">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>zeferinomma</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B436">
         <v>0</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>tavaresguu</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B437">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>ildemarmarajo</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B438">
         <v>0</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>peterson_arrais</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B439">
         <v>0</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>danieldias7s</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B440">
         <v>0</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>ohanna.anselmo</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B441">
         <v>0</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>brun_oguerreiro</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B442">
         <v>0</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>helman_mma70</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B443">
         <v>0</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>macio.almeida_89</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B444">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>lyviaestherbjj</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B445">
         <v>0</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>wendel_bjj14</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B446">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>karine_killer_ufc</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B447">
         <v>0</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>andressa_bjj_</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B448">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>dreamartpro</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B449">
         <v>0</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>makelele_bjj</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B450">
         <v>0</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>fdanieljj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B451">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B452">
         <v>0</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>caioleonjj</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B453">
         <v>0</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B454">
         <v>0</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>malene_elleen</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B455">
         <v>0</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>leonardoo_paixao</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B456">
         <v>0</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>josita_bjj</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B457">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>roxostrike</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B458">
         <v>0</v>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>ruanmiqueias</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B459">
         <v>0</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>babimaciel1</v>
+        <v>roxostrike</v>
       </c>
       <c r="B460">
         <v>0</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>manoel.brum</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B461">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>horadopower</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B462">
         <v>0</v>
@@ -6870,28 +6870,56 @@
     </row>
     <row r="463">
       <c r="A463" t="str">
+        <v>manoel.brum</v>
+      </c>
+      <c r="B463">
+        <v>0</v>
+      </c>
+      <c r="C463">
+        <v>1</v>
+      </c>
+      <c r="D463">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="str">
+        <v>horadopower</v>
+      </c>
+      <c r="B464">
+        <v>0</v>
+      </c>
+      <c r="C464">
+        <v>1</v>
+      </c>
+      <c r="D464">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="str">
         <v>lyvia_genuina</v>
       </c>
-      <c r="B463">
-        <v>0</v>
-      </c>
-      <c r="C463">
-        <v>1</v>
-      </c>
-      <c r="D463">
+      <c r="B465">
+        <v>0</v>
+      </c>
+      <c r="C465">
+        <v>1</v>
+      </c>
+      <c r="D465">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D463"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D465"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D181"/>
+  <dimension ref="A1:D186"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6912,13 +6940,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>576</v>
+        <v>638</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>475</v>
+        <v>512</v>
       </c>
     </row>
     <row r="3">
@@ -6940,13 +6968,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5">
@@ -6954,13 +6982,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -6968,41 +6996,41 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>pedr00jj</v>
+        <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>rpsantos_mma</v>
+        <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>38</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -7024,13 +7052,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -7038,7 +7066,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B11">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -7080,13 +7108,13 @@
         <v>combintel</v>
       </c>
       <c r="B14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -7231,27 +7259,27 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>excelentfightcompetition</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>irmandadefightteam</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B26">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26">
         <v>2</v>
@@ -7259,27 +7287,27 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>eliassilverio</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B27">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>alvesmidih</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -7287,7 +7315,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>_beegomes_</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B29">
         <v>3</v>
@@ -7296,29 +7324,29 @@
         <v>0</v>
       </c>
       <c r="D29">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>pitbullandrade</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B30">
+        <v>2</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
         <v>3</v>
-      </c>
-      <c r="C30">
-        <v>0</v>
-      </c>
-      <c r="D30">
-        <v>2</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>karen.ottoni</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -7329,10 +7357,10 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>alfredo_miras</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -7343,21 +7371,21 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B33">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>badboykillermma</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B34">
         <v>2</v>
@@ -7371,105 +7399,105 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>pedromadeira.s</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35">
         <v>3</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>livreseseguras</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B36">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B37">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>_pizzariabambina_</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>vndcardoso</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>artewebpersonalizados</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B40">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>tatibscardoso</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B41">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>z.proddd</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B42">
         <v>2</v>
@@ -7478,26 +7506,26 @@
         <v>0</v>
       </c>
       <c r="D42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>multiplicaaba</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ronemayanmorais</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B44">
         <v>2</v>
@@ -7506,74 +7534,74 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>meol.socialmidia</v>
+        <v>z.proddd</v>
       </c>
       <c r="B45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>adriano.trator</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C46">
         <v>1</v>
       </c>
       <c r="D46">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>marcos_tailandess</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B47">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>tabajaraharu</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ravenrodriguez___</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B49">
         <v>1</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D49">
         <v>2</v>
@@ -7581,7 +7609,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>dogodoyfoto</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -7777,27 +7805,27 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>estevaotoledo</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B64">
         <v>1</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>kalindrafaria</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -7805,35 +7833,35 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B66">
         <v>1</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -7847,7 +7875,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B69">
         <v>1</v>
@@ -7861,7 +7889,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>chuck_tlp</v>
+        <v>andreibjj</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -7875,35 +7903,35 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>antonioemanuel.13</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C71">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -7917,7 +7945,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>magnoddias</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -7931,13 +7959,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>gustavomohallem</v>
+        <v>magnoddias</v>
       </c>
       <c r="B75">
         <v>1</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -7945,7 +7973,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>atlta.marc0s</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -7959,7 +7987,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -7973,7 +8001,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>hermaan10_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -7987,7 +8015,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -8001,7 +8029,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -8015,7 +8043,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -8029,7 +8057,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -8043,7 +8071,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -8057,7 +8085,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -8071,7 +8099,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -8085,7 +8113,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -8099,7 +8127,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>cjrnavalha</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -8113,7 +8141,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>natalan_wilgner</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -8127,7 +8155,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -8141,7 +8169,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -8155,7 +8183,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -8169,7 +8197,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -8183,7 +8211,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>aliferpaulo_</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -8197,7 +8225,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>moisespira</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -8211,7 +8239,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -8225,7 +8253,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -8239,7 +8267,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -8253,7 +8281,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -8267,7 +8295,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -8281,7 +8309,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -8295,7 +8323,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -8309,7 +8337,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -8323,7 +8351,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -8337,7 +8365,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -8351,7 +8379,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>fernandamourabjj</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -8365,7 +8393,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -8379,7 +8407,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -8393,7 +8421,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -8407,7 +8435,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -8421,7 +8449,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>wlt_miguel</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -8435,7 +8463,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>wesley_bjjvc</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -8449,7 +8477,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>juniordiasmma</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -8463,7 +8491,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>joselia_1980</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -8477,7 +8505,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>kaua_limamma</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -8491,7 +8519,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>soniarochaco</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -8505,7 +8533,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>leandro_pedro7</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -8519,7 +8547,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>camillinhamma</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -8533,7 +8561,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>martins.rauanee</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -8547,7 +8575,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>ever.soulson</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -8561,7 +8589,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>mestrevascobento</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -8575,7 +8603,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -8589,7 +8617,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -8603,7 +8631,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>santos39roger</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -8617,27 +8645,27 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>guerreirammaofc</v>
+        <v>santos39roger</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C124">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>izabeldelfino_</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B125">
         <v>0</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -8645,27 +8673,27 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>janjaovix</v>
+        <v>gdazuera</v>
       </c>
       <c r="B126">
         <v>0</v>
       </c>
       <c r="C126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B127">
         <v>0</v>
       </c>
       <c r="C127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -8673,13 +8701,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>edsonbahienseb</v>
+        <v>pedro_giraldi</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
       <c r="C128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -8687,7 +8715,7 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B129">
         <v>0</v>
@@ -8701,7 +8729,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>edebetim_</v>
+        <v>janjaovix</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -8715,21 +8743,21 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>maca.mariotti</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B131">
         <v>0</v>
       </c>
       <c r="C131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>peacegrappler_archive</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -8743,7 +8771,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>_oliveira09_</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -8757,7 +8785,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>benjafloripabjj</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -8766,12 +8794,12 @@
         <v>1</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>f.ostini</v>
+        <v>edebetim_</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -8780,12 +8808,12 @@
         <v>1</v>
       </c>
       <c r="D135">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>fher.nando_</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -8794,12 +8822,12 @@
         <v>1</v>
       </c>
       <c r="D136">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -8808,12 +8836,12 @@
         <v>1</v>
       </c>
       <c r="D137">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>bastazinifilho</v>
+        <v>brodschack_</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -8822,12 +8850,12 @@
         <v>1</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -8841,7 +8869,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>pammygaryo</v>
+        <v>f.ostini</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -8855,7 +8883,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>anselmo.azevedo</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -8869,7 +8897,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>marcotulio_matuto</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -8883,7 +8911,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>ianrochaf</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -8897,7 +8925,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>ale.lagonegro</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -8911,7 +8939,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>ganemfelipe</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -8925,7 +8953,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -8939,7 +8967,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>marcusvgsz</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -8953,7 +8981,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>wanderson.casttro</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -8967,7 +8995,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -8981,7 +9009,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>jotapeamancio</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -8995,7 +9023,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -9009,7 +9037,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -9023,7 +9051,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>zeferinomma</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -9037,7 +9065,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>tavaresguu</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -9051,7 +9079,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>ildemarmarajo</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -9065,7 +9093,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -9079,7 +9107,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>peterson_arrais</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -9093,7 +9121,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>danieldias7s</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -9107,7 +9135,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>ohanna.anselmo</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -9121,7 +9149,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>brun_oguerreiro</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -9135,7 +9163,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>helman_mma70</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -9149,7 +9177,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>macio.almeida_89</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -9163,7 +9191,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>lyviaestherbjj</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -9177,7 +9205,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>wendel_bjj14</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -9191,7 +9219,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>karine_killer_ufc</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -9205,7 +9233,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>andressa_bjj_</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -9219,7 +9247,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>dreamartpro</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -9233,7 +9261,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>makelele_bjj</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -9247,7 +9275,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>fdanieljj</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -9261,7 +9289,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -9275,7 +9303,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>caioleonjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -9289,7 +9317,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -9303,7 +9331,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>malene_elleen</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -9317,7 +9345,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>leonardoo_paixao</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -9331,7 +9359,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>josita_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -9345,7 +9373,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>roxostrike</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -9359,7 +9387,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>ruanmiqueias</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -9373,7 +9401,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>babimaciel1</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -9387,7 +9415,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>manoel.brum</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -9401,7 +9429,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>horadopower</v>
+        <v>roxostrike</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -9415,21 +9443,91 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
+        <v>ruanmiqueias</v>
+      </c>
+      <c r="B181">
+        <v>0</v>
+      </c>
+      <c r="C181">
+        <v>1</v>
+      </c>
+      <c r="D181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>babimaciel1</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+      <c r="C182">
+        <v>1</v>
+      </c>
+      <c r="D182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>manoel.brum</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+      <c r="C183">
+        <v>1</v>
+      </c>
+      <c r="D183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>horadopower</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+      <c r="C184">
+        <v>1</v>
+      </c>
+      <c r="D184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
         <v>lyvia_genuina</v>
       </c>
-      <c r="B181">
-        <v>0</v>
-      </c>
-      <c r="C181">
-        <v>1</v>
-      </c>
-      <c r="D181">
+      <c r="B185">
+        <v>0</v>
+      </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
+      <c r="D185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>ommariotti</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D186"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>639</v>
+        <v>665</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>512</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5">
@@ -461,13 +461,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B5">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C5">
         <v>26</v>
       </c>
       <c r="D5">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B6">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -489,7 +489,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B7">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C7">
         <v>10</v>
@@ -531,13 +531,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B10">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11">
@@ -545,13 +545,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B11">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12">
@@ -559,13 +559,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B12">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13">
@@ -696,30 +696,30 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B22">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>god.motivacao</v>
+        <v>aline.r15</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="C23">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D23">
-        <v>43</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
@@ -962,49 +962,49 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>rrafaelins</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B41">
         <v>4</v>
       </c>
       <c r="C41">
+        <v>8</v>
+      </c>
+      <c r="D41">
         <v>4</v>
-      </c>
-      <c r="D41">
-        <v>5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>juniordiasmma</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B42">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B43">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>kauepraciano</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B44">
         <v>7</v>
@@ -1018,13 +1018,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>enzoferrari680</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B45">
         <v>7</v>
       </c>
       <c r="C45">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>2</v>
@@ -1032,44 +1032,44 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>gdazuera</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B46">
+        <v>7</v>
+      </c>
+      <c r="C46">
         <v>3</v>
       </c>
-      <c r="C46">
-        <v>17</v>
-      </c>
       <c r="D46">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>italothearcher</v>
+        <v>gdazuera</v>
       </c>
       <c r="B47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C47">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D47">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>adriano.trator</v>
+        <v>italothearcher</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D48">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
@@ -6940,13 +6940,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>638</v>
+        <v>664</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>512</v>
+        <v>538</v>
       </c>
     </row>
     <row r="3">
@@ -6968,7 +6968,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -6982,13 +6982,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6">
@@ -6996,7 +6996,7 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -7021,30 +7021,30 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>pedr00jj</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B8">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>48</v>
+        <v>76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>rm.nicki</v>
+        <v>pedr00jj</v>
       </c>
       <c r="B9">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>73</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -7052,13 +7052,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -7066,13 +7066,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B11">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12">
@@ -7080,13 +7080,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B12">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -7189,30 +7189,30 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B20">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D20">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>god.motivacao</v>
+        <v>aline.r15</v>
       </c>
       <c r="B21">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C21">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
@@ -7315,13 +7315,13 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>alvesmidih</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B29">
         <v>3</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -7329,13 +7329,13 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>adriano.trator</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>3</v>

--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D465"/>
+  <dimension ref="A1:D467"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>665</v>
+        <v>715</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>538</v>
+        <v>587</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5">
@@ -461,13 +461,13 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B5">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C5">
         <v>26</v>
       </c>
       <c r="D5">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B6">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C6">
         <v>12</v>
@@ -489,13 +489,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B7">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
       <c r="D7">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8">
@@ -517,13 +517,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B9">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C9">
         <v>5</v>
       </c>
       <c r="D9">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -531,13 +531,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B10">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -573,13 +573,13 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B13">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
@@ -590,7 +590,7 @@
         <v>49</v>
       </c>
       <c r="C14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14">
         <v>50</v>
@@ -598,44 +598,44 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>irmandadefightteam</v>
+        <v>combintel</v>
       </c>
       <c r="B15">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15">
-        <v>4</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>mmmarc20</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B16">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>combintel</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B17">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -783,7 +783,7 @@
         <v>maxgandra</v>
       </c>
       <c r="B28">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -836,44 +836,44 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>pedromadeira.s</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B32">
         <v>14</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D32">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>marc0s.azv</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B33">
         <v>14</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B34">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34">
         <v>5</v>
-      </c>
-      <c r="D34">
-        <v>9</v>
       </c>
     </row>
     <row r="35">
@@ -892,41 +892,41 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>_beegomes_</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B36">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C36">
         <v>1</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>vndcardoso</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B37">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>tawanregismma</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B38">
         <v>7</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -934,13 +934,13 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>karen.ottoni</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B39">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -948,77 +948,77 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>ninjatheorist</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B40">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>adriano.trator</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C41">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>rrafaelins</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B42">
         <v>4</v>
       </c>
       <c r="C42">
+        <v>8</v>
+      </c>
+      <c r="D42">
         <v>4</v>
-      </c>
-      <c r="D42">
-        <v>5</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>juniordiasmma</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B43">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C43">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D43">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B44">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>kauepraciano</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B45">
         <v>7</v>
@@ -1298,52 +1298,52 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>gabrielsouzamma</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B65">
         <v>2</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B66">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>pitbullandrade</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>alfredo_miras</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B68">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -1354,27 +1354,27 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>fabinho_falcao_</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B69">
         <v>2</v>
       </c>
       <c r="C69">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -1382,27 +1382,27 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D72">
         <v>0</v>
@@ -1410,13 +1410,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>lipe.ftt</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B73">
         <v>4</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -1424,7 +1424,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B74">
         <v>4</v>
@@ -1438,35 +1438,35 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>livreseseguras</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B75">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>_pizzariabambina_</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B77">
         <v>4</v>
@@ -1480,21 +1480,21 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>artewebpersonalizados</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B78">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>tatibscardoso</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B79">
         <v>2</v>
@@ -1508,7 +1508,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>shawlin13oficial</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -1517,12 +1517,12 @@
         <v>0</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>z.proddd</v>
+        <v>febrancatti</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -1578,49 +1578,49 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>maca.mariotti</v>
+        <v>z.proddd</v>
       </c>
       <c r="B85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D85">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>reifernandes</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D86">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B87">
         <v>2</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B88">
         <v>2</v>
@@ -1634,27 +1634,27 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B89">
         <v>2</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D89">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>multiplicaaba</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D90">
         <v>0</v>
@@ -1662,13 +1662,13 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>f.luan_11</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B91">
         <v>3</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -1676,21 +1676,21 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B93">
         <v>2</v>
@@ -1704,77 +1704,77 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B94">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B95">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>meol.socialmidia</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>odeivisoncardoso</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C97">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>s__simone__</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B99">
         <v>2</v>
@@ -1788,7 +1788,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B100">
         <v>2</v>
@@ -1802,21 +1802,21 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C101">
         <v>0</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -1830,16 +1830,16 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>washington_cassisno</v>
+        <v>ruangzk</v>
       </c>
       <c r="B103">
         <v>1</v>
       </c>
       <c r="C103">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D103">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -4756,13 +4756,13 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>marinealcausa</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B312">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C312">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D312">
         <v>0</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B313">
         <v>0</v>
@@ -4784,49 +4784,49 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B314">
         <v>0</v>
       </c>
       <c r="C314">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D314">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B315">
         <v>0</v>
       </c>
       <c r="C315">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D315">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>giulia.fasolato</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B316">
         <v>0</v>
       </c>
       <c r="C316">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D316">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>brodschack_</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,21 +4840,21 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>michelle_mirele</v>
+        <v>brodschack_</v>
       </c>
       <c r="B318">
         <v>0</v>
       </c>
       <c r="C318">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D318">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B319">
         <v>0</v>
@@ -4868,21 +4868,21 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B320">
         <v>0</v>
       </c>
       <c r="C320">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D320">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>dayanaa1511</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -4896,7 +4896,7 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>ommariotti</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>guerreirammaofc</v>
+        <v>ommariotti</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>pedro_giraldi</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>pedro_giraldi</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4947,26 +4947,26 @@
         <v>2</v>
       </c>
       <c r="D325">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>vanessamelomma</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B326">
         <v>0</v>
       </c>
       <c r="C326">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D326">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B327">
         <v>0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,21 +4994,21 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B329">
         <v>0</v>
       </c>
       <c r="C329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D329">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B330">
         <v>0</v>
@@ -5022,7 +5022,7 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,21 +5036,21 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B332">
         <v>0</v>
       </c>
       <c r="C332">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D332">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B333">
         <v>0</v>
@@ -5064,21 +5064,21 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B334">
         <v>0</v>
       </c>
       <c r="C334">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D334">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B335">
         <v>0</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5106,21 +5106,21 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B337">
         <v>0</v>
       </c>
       <c r="C337">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D337">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>_vpft</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>izabeldelfino_</v>
+        <v>_vpft</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>janjaovix</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>janjaovix</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B344">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>peacegrappler_archive</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B345">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -5241,12 +5241,12 @@
         <v>1</v>
       </c>
       <c r="D346">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>helenaseveribjj</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5255,12 +5255,12 @@
         <v>1</v>
       </c>
       <c r="D347">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>_kainanlima</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>jimmy_indioap</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B349">
         <v>0</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>omar_alneaimi</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B350">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>victor_brunopersonal</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B351">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>motumbo_team</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B352">
         <v>0</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>vanemessina</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>dadwillians</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>thalytabjj</v>
+        <v>vanemessina</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>esteticaluharruda</v>
+        <v>dadwillians</v>
       </c>
       <c r="B356">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>chubotaru_lilu</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>eusoufernandosaito</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>dandraco_</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B359">
         <v>0</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B360">
         <v>0</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>sejamotivadorofc</v>
+        <v>dandraco_</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>tpapereira</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>kfcampeoes</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B363">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>herrickmarinho</v>
+        <v>tpapereira</v>
       </c>
       <c r="B364">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>rafaelcmjj</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B365">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>cristianomarcello</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B366">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>_gabrielpego</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B367">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>taylor_71kg</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B368">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B369">
         <v>0</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>doraasivla</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B370">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>pe.mirandas</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B371">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>leaoanaalice</v>
+        <v>doraasivla</v>
       </c>
       <c r="B372">
         <v>0</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>caioparangole</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B373">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>sabrinaalsilva</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B374">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>caioparangole</v>
       </c>
       <c r="B375">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>eglaudiomma</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B376">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>strong_stg_oficial</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B377">
         <v>0</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>ricardotofanello</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B378">
         <v>0</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>taporondebruno</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B379">
         <v>0</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>anamatias.m</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B380">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>claudio_marchese_7</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B381">
         <v>0</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>1000ton_n</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B382">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>paulo.titoo</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B383">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>vitorcosta_mma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B384">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>couragemma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>romulerasilva</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B386">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>edergama.mma</v>
+        <v>couragemma</v>
       </c>
       <c r="B387">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>alineanne_</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B388">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>julckreis</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B389">
         <v>0</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>andreza.thais.1</v>
+        <v>alineanne_</v>
       </c>
       <c r="B390">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>benicius_edu</v>
+        <v>julckreis</v>
       </c>
       <c r="B391">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B392">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>michele_mixa</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B393">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>joaolauar_</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B394">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>igorbrasileiro01</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B395">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>felipeocalmon</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B396">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>rejr_mma</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B397">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>deivssonmanin</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B398">
         <v>0</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>andrey_m_s_</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B399">
         <v>0</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>vidaldanin</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B400">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>barbaracontadora</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B401">
         <v>0</v>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>natalves5</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B402">
         <v>0</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B403">
         <v>0</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>boradepodcastoficial</v>
+        <v>natalves5</v>
       </c>
       <c r="B404">
         <v>0</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>audizioandrade</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B405">
         <v>0</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>isadoragolimpio</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B406">
         <v>0</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>dudu.acabamentos</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B407">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>katlembrenda</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B408">
         <v>0</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>aline.amaral21</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B409">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>tamysregina</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B410">
         <v>0</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>guilhermews1994</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B411">
         <v>0</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>percepcar</v>
+        <v>tamysregina</v>
       </c>
       <c r="B412">
         <v>0</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>kevin.mota95</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B413">
         <v>0</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>_marcos_.71</v>
+        <v>percepcar</v>
       </c>
       <c r="B414">
         <v>0</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>douglas_vitor8</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B415">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B416">
         <v>0</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>raulcarvalho1010</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B417">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>roginbrito</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B418">
         <v>0</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>meirelesmma</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B419">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>dvlucc2k26_</v>
+        <v>roginbrito</v>
       </c>
       <c r="B420">
         <v>0</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>armysenju</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B421">
         <v>0</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>f.ostini</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B422">
         <v>0</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>fher.nando_</v>
+        <v>armysenju</v>
       </c>
       <c r="B423">
         <v>0</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>f.ostini</v>
       </c>
       <c r="B424">
         <v>0</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>bastazinifilho</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B425">
         <v>0</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>pammygaryo</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B426">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>anselmo.azevedo</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B427">
         <v>0</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>marcotulio_matuto</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B428">
         <v>0</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>ianrochaf</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B429">
         <v>0</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>ale.lagonegro</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B430">
         <v>0</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>ganemfelipe</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B431">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>marcusvgsz</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B432">
         <v>0</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>wanderson.casttro</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B433">
         <v>0</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B434">
         <v>0</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>jotapeamancio</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B435">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B436">
         <v>0</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B437">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>zeferinomma</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B438">
         <v>0</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>tavaresguu</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B439">
         <v>0</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>ildemarmarajo</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B440">
         <v>0</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>peterson_arrais</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B441">
         <v>0</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>danieldias7s</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B442">
         <v>0</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>ohanna.anselmo</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B443">
         <v>0</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>brun_oguerreiro</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B444">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>helman_mma70</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B445">
         <v>0</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>macio.almeida_89</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B446">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>lyviaestherbjj</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B447">
         <v>0</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>wendel_bjj14</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B448">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>karine_killer_ufc</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B449">
         <v>0</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>andressa_bjj_</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B450">
         <v>0</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>dreamartpro</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B451">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>makelele_bjj</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B452">
         <v>0</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>fdanieljj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B453">
         <v>0</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B454">
         <v>0</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>caioleonjj</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B455">
         <v>0</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B456">
         <v>0</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>malene_elleen</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B457">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>leonardoo_paixao</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B458">
         <v>0</v>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>josita_bjj</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B459">
         <v>0</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>roxostrike</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B460">
         <v>0</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>ruanmiqueias</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B461">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>babimaciel1</v>
+        <v>roxostrike</v>
       </c>
       <c r="B462">
         <v>0</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>manoel.brum</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B463">
         <v>0</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>horadopower</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B464">
         <v>0</v>
@@ -6898,28 +6898,56 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
+        <v>manoel.brum</v>
+      </c>
+      <c r="B465">
+        <v>0</v>
+      </c>
+      <c r="C465">
+        <v>1</v>
+      </c>
+      <c r="D465">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="str">
+        <v>horadopower</v>
+      </c>
+      <c r="B466">
+        <v>0</v>
+      </c>
+      <c r="C466">
+        <v>1</v>
+      </c>
+      <c r="D466">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="str">
         <v>lyvia_genuina</v>
       </c>
-      <c r="B465">
-        <v>0</v>
-      </c>
-      <c r="C465">
-        <v>1</v>
-      </c>
-      <c r="D465">
+      <c r="B467">
+        <v>0</v>
+      </c>
+      <c r="C467">
+        <v>1</v>
+      </c>
+      <c r="D467">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D465"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D467"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D186"/>
+  <dimension ref="A1:D190"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6940,13 +6968,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>664</v>
+        <v>714</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>538</v>
+        <v>587</v>
       </c>
     </row>
     <row r="3">
@@ -6968,7 +6996,7 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -6982,13 +7010,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6">
@@ -6996,13 +7024,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7">
@@ -7010,13 +7038,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -7052,13 +7080,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -7066,83 +7094,83 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>pg_grappling</v>
+        <v>combintel</v>
       </c>
       <c r="B12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>ryangandraufc</v>
+        <v>pg_grappling</v>
       </c>
       <c r="B13">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C13">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>combintel</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D14">
-        <v>10</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>mmmarc20</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B15">
+        <v>15</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
         <v>12</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15">
-        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>anaaj_camargo</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B16">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -7161,16 +7189,16 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>cleyton_jesuss</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B18">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -7178,7 +7206,7 @@
         <v>maxgandra</v>
       </c>
       <c r="B19">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19">
         <v>2</v>
@@ -7189,63 +7217,63 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>god.motivacao</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B20">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C20">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D20">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B21">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>ninjatheorist</v>
+        <v>aline.r15</v>
       </c>
       <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22">
+        <v>2</v>
+      </c>
+      <c r="D22">
         <v>6</v>
-      </c>
-      <c r="C22">
-        <v>0</v>
-      </c>
-      <c r="D22">
-        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>kauepraciano</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>gra_jpereira</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B24">
         <v>4</v>
@@ -7254,46 +7282,46 @@
         <v>0</v>
       </c>
       <c r="D24">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>tabajaraharu</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B25">
         <v>4</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>excelentfightcompetition</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>irmandadefightteam</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B27">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -7595,27 +7623,27 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>marcos_tailandess</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>ravenrodriguez___</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B50">
         <v>1</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -7623,21 +7651,21 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>leticiamartinspro</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>enzoferrari680</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B52">
         <v>2</v>
@@ -7651,35 +7679,35 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>pedrinhosbjj</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B53">
         <v>1</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>araujojonaspenhade</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -7693,7 +7721,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>jesabelmelo9</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -7707,7 +7735,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>marcocanatelli</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -7721,63 +7749,63 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>pvd_._dudis</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>boia_capoeira</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B59">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>sr.valter</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B60">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>devessonjj</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B61">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>tatianeaguiarp</v>
+        <v>sr.valter</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -7791,7 +7819,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>viktor.torquato</v>
+        <v>devessonjj</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -7805,7 +7833,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>eric.shpritz</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -7819,21 +7847,21 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>estevaotoledo</v>
+        <v>viktor.torquato</v>
       </c>
       <c r="B65">
         <v>1</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>kalindrafaria</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -7842,12 +7870,12 @@
         <v>0</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -7856,12 +7884,12 @@
         <v>1</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B68">
         <v>1</v>
@@ -7875,21 +7903,21 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>oniszczuk_ko</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>andreibjj</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -7903,7 +7931,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>chuck_tlp</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -7917,27 +7945,27 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>antonioemanuel.13</v>
+        <v>andreibjj</v>
       </c>
       <c r="B72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D72">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>gasparjr1983</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B73">
         <v>1</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -7945,21 +7973,21 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>magnoddias</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B75">
         <v>1</v>
@@ -7973,13 +8001,13 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>gustavomohallem</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B76">
         <v>1</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D76">
         <v>0</v>
@@ -7987,13 +8015,13 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>atlta.marc0s</v>
+        <v>magnoddias</v>
       </c>
       <c r="B77">
         <v>1</v>
       </c>
       <c r="C77">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D77">
         <v>0</v>
@@ -8001,7 +8029,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>arturbambam</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -8015,7 +8043,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>hermaan10_</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B79">
         <v>1</v>
@@ -8029,7 +8057,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>danieljsantoss_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -8043,7 +8071,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>rodrigojansen_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -8057,7 +8085,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>markakasocks</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -8071,7 +8099,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>hunter.mccrary</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -8085,7 +8113,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>omarcotomaz</v>
+        <v>markakasocks</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -8099,7 +8127,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>alphavillesup</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -8113,7 +8141,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>ricieritonan</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -8127,7 +8155,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>lucasampaio</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -8141,7 +8169,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>cjrnavalha</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -8155,7 +8183,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>natalan_wilgner</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -8169,7 +8197,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>manmoska</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -8183,7 +8211,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>renatoevangelistaa</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -8197,7 +8225,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>cassius.paula</v>
+        <v>manmoska</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -8211,7 +8239,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -8225,7 +8253,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>aliferpaulo_</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -8239,7 +8267,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -8253,7 +8281,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>rodrigolidiosales</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -8267,7 +8295,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>moisespira</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -8281,7 +8309,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>marciocatenacci</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -8295,7 +8323,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>cristiane.c.santana</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -8309,7 +8337,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>ariel_alvees</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -8323,7 +8351,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>flahvinhotreinador</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -8337,7 +8365,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -8351,7 +8379,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>selma.oscar12</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -8365,7 +8393,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>romulobelarmino</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -8379,7 +8407,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -8393,7 +8421,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>fernandamourabjj</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -8407,7 +8435,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>larissamartinsbjj</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -8421,7 +8449,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -8435,7 +8463,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>leitefelippez</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -8449,7 +8477,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>israelbahiensebraz</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -8463,7 +8491,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>wlt_miguel</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -8477,7 +8505,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>wesley_bjjvc</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -8491,7 +8519,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>juniordiasmma</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -8505,7 +8533,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>joselia_1980</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -8519,7 +8547,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>kaua_limamma</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -8533,7 +8561,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>soniarochaco</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -8547,7 +8575,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>leandro_pedro7</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -8561,7 +8589,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>camillinhamma</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -8575,7 +8603,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>martins.rauanee</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -8589,7 +8617,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>ever.soulson</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -8603,7 +8631,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>mestrevascobento</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -8617,7 +8645,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -8631,7 +8659,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -8645,7 +8673,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>santos39roger</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -8659,55 +8687,55 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>maca.mariotti</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>gdazuera</v>
+        <v>santos39roger</v>
       </c>
       <c r="B126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>guerreirammaofc</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>pedro_giraldi</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
       <c r="C128">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -8715,27 +8743,27 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>izabeldelfino_</v>
+        <v>gdazuera</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>janjaovix</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B130">
         <v>0</v>
       </c>
       <c r="C130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -8743,7 +8771,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>pedro_giraldi</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -8752,12 +8780,12 @@
         <v>2</v>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -8771,7 +8799,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>edsonbahienseb</v>
+        <v>janjaovix</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -8785,21 +8813,21 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B134">
         <v>0</v>
       </c>
       <c r="C134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D134">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>edebetim_</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -8813,7 +8841,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>peacegrappler_archive</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -8827,7 +8855,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>_oliveira09_</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -8841,7 +8869,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>brodschack_</v>
+        <v>edebetim_</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -8855,7 +8883,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>benjafloripabjj</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -8864,12 +8892,12 @@
         <v>1</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>f.ostini</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -8878,12 +8906,12 @@
         <v>1</v>
       </c>
       <c r="D140">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>fher.nando_</v>
+        <v>brodschack_</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -8892,12 +8920,12 @@
         <v>1</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -8906,12 +8934,12 @@
         <v>1</v>
       </c>
       <c r="D142">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>bastazinifilho</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -8925,7 +8953,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>pammygaryo</v>
+        <v>f.ostini</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -8939,7 +8967,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>anselmo.azevedo</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -8953,7 +8981,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>marcotulio_matuto</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -8967,7 +8995,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>ianrochaf</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -8981,7 +9009,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>ale.lagonegro</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -8995,7 +9023,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>ganemfelipe</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -9009,7 +9037,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -9023,7 +9051,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>marcusvgsz</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -9037,7 +9065,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>wanderson.casttro</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -9051,7 +9079,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -9065,7 +9093,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>jotapeamancio</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -9079,7 +9107,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -9093,7 +9121,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -9107,7 +9135,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>zeferinomma</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -9121,7 +9149,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>tavaresguu</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -9135,7 +9163,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>ildemarmarajo</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -9149,7 +9177,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -9163,7 +9191,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>peterson_arrais</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -9177,7 +9205,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>danieldias7s</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -9191,7 +9219,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>ohanna.anselmo</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -9205,7 +9233,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>brun_oguerreiro</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -9219,7 +9247,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>helman_mma70</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -9233,7 +9261,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>macio.almeida_89</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -9247,7 +9275,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>lyviaestherbjj</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -9261,7 +9289,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>wendel_bjj14</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -9275,7 +9303,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>karine_killer_ufc</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -9289,7 +9317,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>andressa_bjj_</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -9303,7 +9331,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>dreamartpro</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -9317,7 +9345,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>makelele_bjj</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -9331,7 +9359,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>fdanieljj</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -9345,7 +9373,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -9359,7 +9387,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>caioleonjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -9373,7 +9401,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -9387,7 +9415,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>malene_elleen</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -9401,7 +9429,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>leonardoo_paixao</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -9415,7 +9443,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>josita_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -9429,7 +9457,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>roxostrike</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -9443,7 +9471,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>ruanmiqueias</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -9457,7 +9485,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>babimaciel1</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -9471,7 +9499,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>manoel.brum</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -9485,7 +9513,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>horadopower</v>
+        <v>roxostrike</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -9499,7 +9527,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>lyvia_genuina</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -9513,21 +9541,77 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
+        <v>babimaciel1</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+      <c r="C186">
+        <v>1</v>
+      </c>
+      <c r="D186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>manoel.brum</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+      <c r="C187">
+        <v>1</v>
+      </c>
+      <c r="D187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>horadopower</v>
+      </c>
+      <c r="B188">
+        <v>0</v>
+      </c>
+      <c r="C188">
+        <v>1</v>
+      </c>
+      <c r="D188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>lyvia_genuina</v>
+      </c>
+      <c r="B189">
+        <v>0</v>
+      </c>
+      <c r="C189">
+        <v>1</v>
+      </c>
+      <c r="D189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
         <v>ommariotti</v>
       </c>
-      <c r="B186">
-        <v>0</v>
-      </c>
-      <c r="C186">
-        <v>1</v>
-      </c>
-      <c r="D186">
+      <c r="B190">
+        <v>0</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D186"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D467"/>
+  <dimension ref="A1:D468"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>715</v>
+        <v>780</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>587</v>
+        <v>644</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5">
@@ -461,7 +461,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B5">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="C5">
         <v>26</v>
@@ -475,13 +475,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B6">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="C6">
         <v>12</v>
       </c>
       <c r="D6">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -489,13 +489,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B7">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
       <c r="D7">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="8">
@@ -503,7 +503,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -517,13 +517,13 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B9">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="C9">
         <v>5</v>
       </c>
       <c r="D9">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
@@ -531,13 +531,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B10">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -573,13 +573,13 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B13">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14">
@@ -601,13 +601,13 @@
         <v>combintel</v>
       </c>
       <c r="B15">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16">
@@ -696,30 +696,30 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>god.motivacao</v>
+        <v>aline.r15</v>
       </c>
       <c r="B22">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C22">
-        <v>139</v>
+        <v>8</v>
       </c>
       <c r="D22">
-        <v>44</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B23">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C23">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="D23">
-        <v>11</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24">
@@ -780,72 +780,72 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>maxgandra</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B28">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>eliassilverio</v>
+        <v>maxgandra</v>
       </c>
       <c r="B29">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D29">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>tabajaraharu</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B30">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C30">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D30">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>tiwimma</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B31">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C31">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D31">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>tiwimma</v>
       </c>
       <c r="B32">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32">
         <v>5</v>
-      </c>
-      <c r="D32">
-        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -962,83 +962,83 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>ninjatheorist</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B41">
         <v>6</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D41">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>adriano.trator</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C42">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>rrafaelins</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B43">
         <v>4</v>
       </c>
       <c r="C43">
+        <v>8</v>
+      </c>
+      <c r="D43">
         <v>4</v>
-      </c>
-      <c r="D43">
-        <v>5</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>juniordiasmma</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B44">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D44">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B45">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>enzoferrari680</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B46">
         <v>7</v>
       </c>
       <c r="C46">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -1046,55 +1046,55 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>gdazuera</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B47">
+        <v>7</v>
+      </c>
+      <c r="C47">
         <v>3</v>
       </c>
-      <c r="C47">
-        <v>17</v>
-      </c>
       <c r="D47">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>italothearcher</v>
+        <v>gdazuera</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C48">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D48">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>badboykillermma</v>
+        <v>italothearcher</v>
       </c>
       <c r="B49">
         <v>4</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D49">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>dogodoyfoto</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B50">
         <v>4</v>
       </c>
       <c r="C50">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>4</v>
@@ -1102,30 +1102,30 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B51">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C51">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D51">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>excelentfightcompetition</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -1158,41 +1158,41 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>marcos_tailandess</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B55">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C55">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>eolucasrosa</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C56">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>dagestan0920</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B57">
         <v>5</v>
       </c>
       <c r="C57">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -1200,13 +1200,13 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>paxlucta</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B58">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C58">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -1214,27 +1214,27 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>_.maduoliveira_</v>
+        <v>paxlucta</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D59">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B60">
         <v>3</v>
       </c>
       <c r="C60">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D60">
         <v>3</v>
@@ -1242,122 +1242,122 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>_oliveira09_</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B61">
         <v>3</v>
       </c>
       <c r="C61">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D61">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>edebetim_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62">
+        <v>5</v>
+      </c>
+      <c r="D62">
         <v>4</v>
-      </c>
-      <c r="D62">
-        <v>6</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>glm.barbosa</v>
+        <v>edebetim_</v>
       </c>
       <c r="B63">
         <v>2</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D63">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>marcelogabrielmma</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>washington_cassisno</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
         <v>3</v>
-      </c>
-      <c r="D65">
-        <v>4</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>gabrielsouzamma</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B66">
         <v>2</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D66">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>salost.ofc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B67">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>pitbullandrade</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B68">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>alfredo_miras</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B69">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -1368,27 +1368,27 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>fabinho_falcao_</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B70">
         <v>2</v>
       </c>
       <c r="C70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -1396,27 +1396,27 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B73">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D73">
         <v>0</v>
@@ -1424,13 +1424,13 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>lipe.ftt</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B74">
         <v>4</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B75">
         <v>4</v>
@@ -1452,21 +1452,21 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>livreseseguras</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D76">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B77">
         <v>4</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>_pizzariabambina_</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B78">
         <v>4</v>
@@ -1494,21 +1494,21 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>artewebpersonalizados</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B79">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>tatibscardoso</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B80">
         <v>2</v>
@@ -1522,7 +1522,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>shawlin13oficial</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1531,12 +1531,12 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>eduardorodrigrs</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B82">
         <v>2</v>
@@ -1550,7 +1550,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B83">
         <v>2</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>febrancatti</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B84">
         <v>2</v>
@@ -1578,7 +1578,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>z.proddd</v>
+        <v>febrancatti</v>
       </c>
       <c r="B85">
         <v>2</v>
@@ -1592,49 +1592,49 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>maca.mariotti</v>
+        <v>z.proddd</v>
       </c>
       <c r="B86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C86">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D86">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>reifernandes</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D87">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>daniel_dias_214</v>
+        <v>reifernandes</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D88">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -1648,27 +1648,27 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>alexsandra_kairos</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B90">
         <v>2</v>
       </c>
       <c r="C90">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>multiplicaaba</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91">
         <v>0</v>
@@ -1676,13 +1676,13 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>f.luan_11</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B92">
         <v>3</v>
       </c>
       <c r="C92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D92">
         <v>0</v>
@@ -1690,21 +1690,21 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>vitorpetrino</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B93">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>jcchagas_</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -1718,77 +1718,77 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>anderson.logan.35</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>marifferreirac</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B96">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>meol.socialmidia</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D97">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>odeivisoncardoso</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C98">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D98">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>s__simone__</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B100">
         <v>2</v>
@@ -1802,7 +1802,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B101">
         <v>2</v>
@@ -1816,21 +1816,21 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B102">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C102">
         <v>0</v>
       </c>
       <c r="D102">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -1844,55 +1844,55 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ismaeldaniell</v>
+        <v>ruangzk</v>
       </c>
       <c r="B104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C104">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D105">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B107">
         <v>2</v>
       </c>
       <c r="C107">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D107">
         <v>0</v>
@@ -1900,13 +1900,13 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -1914,35 +1914,35 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B109">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B110">
         <v>1</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D110">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -1956,41 +1956,41 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>leticiamartinspro</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>fredoctmma</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B114">
         <v>1</v>
       </c>
       <c r="C114">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D114">
         <v>1</v>
@@ -1998,13 +1998,13 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -2012,21 +2012,21 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B117">
         <v>2</v>
@@ -2040,7 +2040,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B118">
         <v>2</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B119">
         <v>2</v>
@@ -2068,21 +2068,21 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B120">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C120">
         <v>0</v>
       </c>
       <c r="D120">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,21 +2110,21 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>wlt_miguel</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B123">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C123">
         <v>0</v>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B124">
         <v>2</v>
@@ -2138,7 +2138,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>wesley_bjjvc</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B125">
         <v>2</v>
@@ -2152,21 +2152,21 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>heltoncm2002</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126">
         <v>0</v>
       </c>
       <c r="D126">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -2180,35 +2180,35 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>aliferpaulo_</v>
+        <v>raelduraes</v>
       </c>
       <c r="B128">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C128">
         <v>0</v>
       </c>
       <c r="D128">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129">
         <v>0</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>pedrinhosbjj</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>jesabelmelo9</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>marcocanatelli</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,21 +2320,21 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>pvd_._dudis</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C138">
         <v>0</v>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B139">
         <v>2</v>
@@ -2348,21 +2348,21 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>sr.valter</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B140">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140">
         <v>0</v>
       </c>
       <c r="D140">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>devessonjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>tatianeaguiarp</v>
+        <v>devessonjj</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>viktor.torquato</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>eric.shpritz</v>
+        <v>viktor.torquato</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,13 +2418,13 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B145">
         <v>1</v>
       </c>
       <c r="C145">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D145">
         <v>1</v>
@@ -2432,27 +2432,27 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>treinaadorrafael</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>benjafloripabjj</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D147">
         <v>0</v>
@@ -2460,13 +2460,13 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>fernando.mma</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B148">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -2474,13 +2474,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B149">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -2488,13 +2488,13 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>estevaotoledo</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B150">
         <v>1</v>
       </c>
       <c r="C150">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -2502,13 +2502,13 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B151">
         <v>1</v>
       </c>
       <c r="C151">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -2516,7 +2516,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B152">
         <v>1</v>
@@ -2530,13 +2530,13 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B153">
         <v>1</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D153">
         <v>0</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>guiiviieira_</v>
+        <v>030sami</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,13 +2712,13 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B166">
         <v>1</v>
       </c>
       <c r="C166">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D166">
         <v>0</v>
@@ -2726,13 +2726,13 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>kalindrafaria</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B167">
         <v>1</v>
       </c>
       <c r="C167">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -2740,35 +2740,35 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B168">
         <v>1</v>
       </c>
       <c r="C168">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D168">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B169">
         <v>1</v>
       </c>
       <c r="C169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D169">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -2782,7 +2782,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>chuck_tlp</v>
+        <v>andreibjj</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,35 +2810,35 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>cristianpsicologo</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C173">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D173">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C174">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D174">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,35 +2880,35 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>antonioemanuel.13</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C178">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D178">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C179">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>magnoddias</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,13 +2936,13 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>tonketjudes</v>
+        <v>magnoddias</v>
       </c>
       <c r="B182">
         <v>1</v>
       </c>
       <c r="C182">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -2950,7 +2950,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,35 +3244,35 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B204">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C204">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D204">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B205">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C205">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D205">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -3286,7 +3286,7 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>charlesanthony2466</v>
+        <v>eliandropires</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,21 +3314,21 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C209">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D209">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>draanapaulaponceano</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -3342,7 +3342,7 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>saj_photo_miami</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>alternativaremocoes</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>benivalentinn</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>navarro_9430</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>_puroosso88</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>_rayysp</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>cami.terra_</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>gabicardoson</v>
+        <v>_rayysp</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>martta.mariah</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>jaonevesz</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>pietroshz</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>___neller</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>_bety_marcal</v>
+        <v>pietroshz</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>guilhermeefelix__</v>
+        <v>___neller</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>pativinisf</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>judadany</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>andre_alcausa</v>
+        <v>pativinisf</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>_fernunes</v>
+        <v>judadany</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>aloirmarcal</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>gilberto_7606</v>
+        <v>_fernunes</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>flazuera14</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>camii_bonfim</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>danlouiz.jj</v>
+        <v>flazuera14</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>gabriel_trevelin</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>y.arthur_01</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>muricunha</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>victorhenriquebjj</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>_lsanchess_</v>
+        <v>muricunha</v>
       </c>
       <c r="B240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>__bielgg</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>mr__rlk01</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>vitor_buck</v>
+        <v>__bielgg</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>fran.ruys</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>sambagabrieloficial</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>_alcantara.bru</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>cesar.boanerges</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B248">
         <v>1</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B249">
         <v>1</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>alexandreconsentino</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B250">
         <v>1</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B251">
         <v>1</v>
@@ -3916,13 +3916,13 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>rafaela_duaartee</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C252">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D252">
         <v>0</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>andre.legendre.10</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B254">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C254">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D254">
         <v>0</v>
@@ -3958,7 +3958,7 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>phillipe.harry</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B255">
         <v>1</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>andrejetx</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>leandro_motiv4</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B257">
         <v>1</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>olga.oliveira013</v>
+        <v>andrejetx</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>leosacraa</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B260">
         <v>1</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>gutocriativo</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B261">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>igorfso_</v>
+        <v>leosacraa</v>
       </c>
       <c r="B262">
         <v>1</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B263">
         <v>1</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>lay_roqs</v>
+        <v>igorfso_</v>
       </c>
       <c r="B264">
         <v>1</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>bigjota.artist</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B265">
         <v>1</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B266">
         <v>1</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>mth_fernandes031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B268">
         <v>1</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>turmanmma</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B269">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>gustavomohallem</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B270">
         <v>1</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>atlta.marc0s</v>
+        <v>turmanmma</v>
       </c>
       <c r="B271">
         <v>1</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>hermaan10_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B273">
         <v>1</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B275">
         <v>1</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B276">
         <v>1</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B277">
         <v>1</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B278">
         <v>1</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B279">
         <v>1</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B280">
         <v>1</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B281">
         <v>1</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>natalan_wilgner</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B282">
         <v>1</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B283">
         <v>1</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B284">
         <v>1</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B285">
         <v>1</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B286">
         <v>1</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B287">
         <v>1</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B288">
         <v>1</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B289">
         <v>1</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B291">
         <v>1</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B292">
         <v>1</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B293">
         <v>1</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B294">
         <v>1</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B295">
         <v>1</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B296">
         <v>1</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>fernandamourabjj</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B297">
         <v>1</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B298">
         <v>1</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B299">
         <v>1</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B300">
         <v>1</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B301">
         <v>1</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>joselia_1980</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B302">
         <v>1</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>soniarochaco</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B303">
         <v>1</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>leandro_pedro7</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B304">
         <v>1</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>camillinhamma</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B305">
         <v>1</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>martins.rauanee</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B306">
         <v>1</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>ever.soulson</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B307">
         <v>1</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>mestrevascobento</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B308">
         <v>1</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B309">
         <v>1</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B310">
         <v>1</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>santos39roger</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B311">
         <v>1</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>leonardomesquitamma</v>
+        <v>santos39roger</v>
       </c>
       <c r="B312">
         <v>1</v>
@@ -4770,13 +4770,13 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>marinealcausa</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B313">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C313">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D313">
         <v>0</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4798,30 +4798,30 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B315">
         <v>0</v>
       </c>
       <c r="C315">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D315">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B316">
         <v>0</v>
       </c>
       <c r="C316">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D316">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="317">
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>macamariotti</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5269,12 +5269,12 @@
         <v>1</v>
       </c>
       <c r="D348">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>helenaseveribjj</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B349">
         <v>0</v>
@@ -5288,7 +5288,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>_kainanlima</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B350">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>jimmy_indioap</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B351">
         <v>0</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>omar_alneaimi</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B352">
         <v>0</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>victor_brunopersonal</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -5344,7 +5344,7 @@
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>motumbo_team</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -5358,7 +5358,7 @@
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>vanemessina</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>dadwillians</v>
+        <v>vanemessina</v>
       </c>
       <c r="B356">
         <v>0</v>
@@ -5386,7 +5386,7 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>thalytabjj</v>
+        <v>dadwillians</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -5400,7 +5400,7 @@
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>esteticaluharruda</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -5414,7 +5414,7 @@
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>chubotaru_lilu</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B359">
         <v>0</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>eusoufernandosaito</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B360">
         <v>0</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>dandraco_</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dandraco_</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>sejamotivadorofc</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B363">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>tpapereira</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B364">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>kfcampeoes</v>
+        <v>tpapereira</v>
       </c>
       <c r="B365">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>herrickmarinho</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B366">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>rafaelcmjj</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B367">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>cristianomarcello</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B368">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>_gabrielpego</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B369">
         <v>0</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>taylor_71kg</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B370">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B371">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>doraasivla</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B372">
         <v>0</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>pe.mirandas</v>
+        <v>doraasivla</v>
       </c>
       <c r="B373">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>leaoanaalice</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B374">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>caioparangole</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B375">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>sabrinaalsilva</v>
+        <v>caioparangole</v>
       </c>
       <c r="B376">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B377">
         <v>0</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>eglaudiomma</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B378">
         <v>0</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>strong_stg_oficial</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B379">
         <v>0</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>ricardotofanello</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B380">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>taporondebruno</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B381">
         <v>0</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>anamatias.m</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B382">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>claudio_marchese_7</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B383">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>1000ton_n</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B384">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>paulo.titoo</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>vitorcosta_mma</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B386">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>couragemma</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B387">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>romulerasilva</v>
+        <v>couragemma</v>
       </c>
       <c r="B388">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>edergama.mma</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B389">
         <v>0</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>alineanne_</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B390">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>julckreis</v>
+        <v>alineanne_</v>
       </c>
       <c r="B391">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>andreza.thais.1</v>
+        <v>julckreis</v>
       </c>
       <c r="B392">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>benicius_edu</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B393">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B394">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>michele_mixa</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B395">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>joaolauar_</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B396">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>igorbrasileiro01</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B397">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>felipeocalmon</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B398">
         <v>0</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>rejr_mma</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B399">
         <v>0</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>deivssonmanin</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B400">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>andrey_m_s_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B401">
         <v>0</v>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>vidaldanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B402">
         <v>0</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>barbaracontadora</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B403">
         <v>0</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>natalves5</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B404">
         <v>0</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>natalves5</v>
       </c>
       <c r="B405">
         <v>0</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>boradepodcastoficial</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B406">
         <v>0</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>audizioandrade</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B407">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>isadoragolimpio</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B408">
         <v>0</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>dudu.acabamentos</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B409">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>katlembrenda</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B410">
         <v>0</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>aline.amaral21</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B411">
         <v>0</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>tamysregina</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B412">
         <v>0</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>guilhermews1994</v>
+        <v>tamysregina</v>
       </c>
       <c r="B413">
         <v>0</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>percepcar</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B414">
         <v>0</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>kevin.mota95</v>
+        <v>percepcar</v>
       </c>
       <c r="B415">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>_marcos_.71</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B416">
         <v>0</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>douglas_vitor8</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B417">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B418">
         <v>0</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>raulcarvalho1010</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B419">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>roginbrito</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B420">
         <v>0</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>meirelesmma</v>
+        <v>roginbrito</v>
       </c>
       <c r="B421">
         <v>0</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>dvlucc2k26_</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B422">
         <v>0</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>armysenju</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B423">
         <v>0</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>f.ostini</v>
+        <v>armysenju</v>
       </c>
       <c r="B424">
         <v>0</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>fher.nando_</v>
+        <v>f.ostini</v>
       </c>
       <c r="B425">
         <v>0</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B426">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>bastazinifilho</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B427">
         <v>0</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>pammygaryo</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B428">
         <v>0</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>anselmo.azevedo</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B429">
         <v>0</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>marcotulio_matuto</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B430">
         <v>0</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>ianrochaf</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B431">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>ale.lagonegro</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B432">
         <v>0</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>ganemfelipe</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B433">
         <v>0</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>marcusvgsz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B434">
         <v>0</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>wanderson.casttro</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B435">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B436">
         <v>0</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>jotapeamancio</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B437">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B438">
         <v>0</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B439">
         <v>0</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>zeferinomma</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B440">
         <v>0</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>tavaresguu</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B441">
         <v>0</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>ildemarmarajo</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B442">
         <v>0</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>peterson_arrais</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B443">
         <v>0</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>danieldias7s</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B444">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>ohanna.anselmo</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B445">
         <v>0</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B446">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>helman_mma70</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B447">
         <v>0</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>macio.almeida_89</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B448">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>lyviaestherbjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B449">
         <v>0</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>wendel_bjj14</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B450">
         <v>0</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>karine_killer_ufc</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B451">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>andressa_bjj_</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B452">
         <v>0</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>dreamartpro</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B453">
         <v>0</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>makelele_bjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B454">
         <v>0</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>fdanieljj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B455">
         <v>0</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B456">
         <v>0</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>caioleonjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B457">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B458">
         <v>0</v>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>malene_elleen</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B459">
         <v>0</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>leonardoo_paixao</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B460">
         <v>0</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>josita_bjj</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B461">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>roxostrike</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B462">
         <v>0</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>ruanmiqueias</v>
+        <v>roxostrike</v>
       </c>
       <c r="B463">
         <v>0</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>babimaciel1</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B464">
         <v>0</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>manoel.brum</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B465">
         <v>0</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>horadopower</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B466">
         <v>0</v>
@@ -6926,28 +6926,42 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
+        <v>horadopower</v>
+      </c>
+      <c r="B467">
+        <v>0</v>
+      </c>
+      <c r="C467">
+        <v>1</v>
+      </c>
+      <c r="D467">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="str">
         <v>lyvia_genuina</v>
       </c>
-      <c r="B467">
-        <v>0</v>
-      </c>
-      <c r="C467">
-        <v>1</v>
-      </c>
-      <c r="D467">
+      <c r="B468">
+        <v>0</v>
+      </c>
+      <c r="C468">
+        <v>1</v>
+      </c>
+      <c r="D468">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D467"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D468"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D190"/>
+  <dimension ref="A1:D191"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6968,13 +6982,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>714</v>
+        <v>779</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>587</v>
+        <v>644</v>
       </c>
     </row>
     <row r="3">
@@ -6996,13 +7010,13 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>208</v>
+        <v>227</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
@@ -7010,13 +7024,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6">
@@ -7024,13 +7038,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
@@ -7038,41 +7052,41 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B7">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>rm.nicki</v>
+        <v>pedr00jj</v>
       </c>
       <c r="B8">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="C8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>pedr00jj</v>
+        <v>rm.nicki</v>
       </c>
       <c r="B9">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>48</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
@@ -7080,13 +7094,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11">
@@ -7094,7 +7108,7 @@
         <v>luis_pequeno_mma</v>
       </c>
       <c r="B11">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -7108,13 +7122,13 @@
         <v>combintel</v>
       </c>
       <c r="B12">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -7133,30 +7147,30 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ryangandraufc</v>
+        <v>anaaj_camargo</v>
       </c>
       <c r="B14">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C14">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>anaaj_camargo</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D15">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -7217,66 +7231,66 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>cleyton_jesuss</v>
+        <v>aline.r15</v>
       </c>
       <c r="B20">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20">
         <v>2</v>
       </c>
       <c r="D20">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>god.motivacao</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B21">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C21">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D21">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>aline.r15</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B22">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C22">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ninjatheorist</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B23">
         <v>6</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D23">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>irmandadefightteam</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -7287,7 +7301,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>gra_jpereira</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B25">
         <v>4</v>
@@ -7296,74 +7310,74 @@
         <v>0</v>
       </c>
       <c r="D25">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>tabajaraharu</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B26">
         <v>4</v>
       </c>
       <c r="C26">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>excelentfightcompetition</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D27">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>eliassilverio</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B28">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>adriano.trator</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B29">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D29">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>alvesmidih</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B30">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -7371,21 +7385,21 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>_beegomes_</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B31">
         <v>3</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D31">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>pitbullandrade</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B32">
         <v>3</v>
@@ -7394,15 +7408,15 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>karen.ottoni</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -7413,10 +7427,10 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>alfredo_miras</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -7427,77 +7441,77 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>dogodoyfoto</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B36">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>badboykillermma</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D37">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>pedromadeira.s</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B38">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>livreseseguras</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B39">
         <v>2</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -7511,49 +7525,49 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>_pizzariabambina_</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B41">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>vndcardoso</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B42">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>artewebpersonalizados</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>tatibscardoso</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B44">
         <v>2</v>
@@ -7567,7 +7581,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>z.proddd</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B45">
         <v>2</v>
@@ -7576,26 +7590,26 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>multiplicaaba</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ronemayanmorais</v>
+        <v>z.proddd</v>
       </c>
       <c r="B47">
         <v>2</v>
@@ -7609,13 +7623,13 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>meol.socialmidia</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B48">
         <v>3</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -7623,41 +7637,41 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B49">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>marcos_tailandess</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B50">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D50">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>ravenrodriguez___</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B51">
         <v>1</v>
       </c>
       <c r="C51">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51">
         <v>2</v>
@@ -7665,63 +7679,63 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>leticiamartinspro</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D52">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>washington_cassisno</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B53">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D53">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>enzoferrari680</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>pedrinhosbjj</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -7735,7 +7749,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -7749,7 +7763,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>jesabelmelo9</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -7763,7 +7777,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>marcocanatelli</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -7777,21 +7791,21 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>pvd_._dudis</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B60">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B61">
         <v>2</v>
@@ -7805,21 +7819,21 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>sr.valter</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B62">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>devessonjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -7833,7 +7847,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>tatianeaguiarp</v>
+        <v>devessonjj</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -7847,7 +7861,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>viktor.torquato</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -7861,7 +7875,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>eric.shpritz</v>
+        <v>viktor.torquato</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -7875,27 +7889,27 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>estevaotoledo</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B67">
         <v>1</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>kalindrafaria</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -7903,35 +7917,35 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D70">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -7945,7 +7959,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -7959,7 +7973,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>chuck_tlp</v>
+        <v>andreibjj</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -7973,35 +7987,35 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>antonioemanuel.13</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B74">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C74">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B76">
         <v>1</v>
@@ -8015,7 +8029,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>magnoddias</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -8029,13 +8043,13 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>gustavomohallem</v>
+        <v>magnoddias</v>
       </c>
       <c r="B78">
         <v>1</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D78">
         <v>0</v>
@@ -8827,21 +8841,21 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B135">
         <v>0</v>
       </c>
       <c r="C135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -8855,7 +8869,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -8869,7 +8883,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>edebetim_</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -8883,7 +8897,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>peacegrappler_archive</v>
+        <v>edebetim_</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -8897,7 +8911,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>_oliveira09_</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -8911,7 +8925,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>brodschack_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -8925,7 +8939,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>paulomartins.mma</v>
+        <v>brodschack_</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -8939,7 +8953,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>benjafloripabjj</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -8948,12 +8962,12 @@
         <v>1</v>
       </c>
       <c r="D143">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>f.ostini</v>
+        <v>macamariotti</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -8962,12 +8976,12 @@
         <v>1</v>
       </c>
       <c r="D144">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>fher.nando_</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B145">
         <v>0</v>
@@ -8981,7 +8995,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>f.ostini</v>
       </c>
       <c r="B146">
         <v>0</v>
@@ -8995,7 +9009,7 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>bastazinifilho</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B147">
         <v>0</v>
@@ -9009,7 +9023,7 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>pammygaryo</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B148">
         <v>0</v>
@@ -9023,7 +9037,7 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>anselmo.azevedo</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B149">
         <v>0</v>
@@ -9037,7 +9051,7 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>marcotulio_matuto</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B150">
         <v>0</v>
@@ -9051,7 +9065,7 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>ianrochaf</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B151">
         <v>0</v>
@@ -9065,7 +9079,7 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>ale.lagonegro</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B152">
         <v>0</v>
@@ -9079,7 +9093,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>ganemfelipe</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B153">
         <v>0</v>
@@ -9093,7 +9107,7 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B154">
         <v>0</v>
@@ -9107,7 +9121,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>marcusvgsz</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -9121,7 +9135,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>wanderson.casttro</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -9135,7 +9149,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B157">
         <v>0</v>
@@ -9149,7 +9163,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>jotapeamancio</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B158">
         <v>0</v>
@@ -9163,7 +9177,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -9177,7 +9191,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -9191,7 +9205,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>zeferinomma</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -9205,7 +9219,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>tavaresguu</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -9219,7 +9233,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>ildemarmarajo</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B163">
         <v>0</v>
@@ -9233,7 +9247,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B164">
         <v>0</v>
@@ -9247,7 +9261,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>peterson_arrais</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B165">
         <v>0</v>
@@ -9261,7 +9275,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>danieldias7s</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -9275,7 +9289,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>ohanna.anselmo</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -9289,7 +9303,7 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -9303,7 +9317,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>helman_mma70</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B169">
         <v>0</v>
@@ -9317,7 +9331,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>macio.almeida_89</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -9331,7 +9345,7 @@
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>lyviaestherbjj</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -9345,7 +9359,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>wendel_bjj14</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B172">
         <v>0</v>
@@ -9359,7 +9373,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>karine_killer_ufc</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B173">
         <v>0</v>
@@ -9373,7 +9387,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>andressa_bjj_</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -9387,7 +9401,7 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>dreamartpro</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -9401,7 +9415,7 @@
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>makelele_bjj</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B176">
         <v>0</v>
@@ -9415,7 +9429,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>fdanieljj</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B177">
         <v>0</v>
@@ -9429,7 +9443,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -9443,7 +9457,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>caioleonjj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B179">
         <v>0</v>
@@ -9457,7 +9471,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B180">
         <v>0</v>
@@ -9471,7 +9485,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>malene_elleen</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B181">
         <v>0</v>
@@ -9485,7 +9499,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>leonardoo_paixao</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B182">
         <v>0</v>
@@ -9499,7 +9513,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>josita_bjj</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -9513,7 +9527,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>roxostrike</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -9527,7 +9541,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>ruanmiqueias</v>
+        <v>roxostrike</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -9541,7 +9555,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>babimaciel1</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -9555,7 +9569,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>manoel.brum</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -9569,7 +9583,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>horadopower</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -9583,7 +9597,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>lyvia_genuina</v>
+        <v>horadopower</v>
       </c>
       <c r="B189">
         <v>0</v>
@@ -9597,21 +9611,35 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
+        <v>lyvia_genuina</v>
+      </c>
+      <c r="B190">
+        <v>0</v>
+      </c>
+      <c r="C190">
+        <v>1</v>
+      </c>
+      <c r="D190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
         <v>ommariotti</v>
       </c>
-      <c r="B190">
-        <v>0</v>
-      </c>
-      <c r="C190">
-        <v>1</v>
-      </c>
-      <c r="D190">
+      <c r="B191">
+        <v>0</v>
+      </c>
+      <c r="C191">
+        <v>1</v>
+      </c>
+      <c r="D191">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D191"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>780</v>
+        <v>826</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>644</v>
+        <v>689</v>
       </c>
     </row>
     <row r="4">
@@ -447,13 +447,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5">
@@ -475,10 +475,10 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B6">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6">
         <v>120</v>
@@ -489,13 +489,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B7">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="C7">
         <v>10</v>
       </c>
       <c r="D7">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8">
@@ -531,13 +531,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B10">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         <v>combintel</v>
       </c>
       <c r="B15">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -702,7 +702,7 @@
         <v>28</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22">
         <v>11</v>
@@ -752,44 +752,44 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>leandro._bjj</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B26">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C26">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D26">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>alvesmidih</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B27">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D27">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B28">
         <v>18</v>
       </c>
       <c r="C28">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -800,7 +800,7 @@
         <v>19</v>
       </c>
       <c r="C29">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>6</v>
@@ -1130,58 +1130,58 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ravenrodriguez___</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B53">
+        <v>3</v>
+      </c>
+      <c r="C53">
+        <v>9</v>
+      </c>
+      <c r="D53">
         <v>5</v>
-      </c>
-      <c r="C53">
-        <v>4</v>
-      </c>
-      <c r="D53">
-        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B54">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>livreseseguras</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B55">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>marcos_tailandess</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B56">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C56">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D56">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1354,7 +1354,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>pitbullandrade</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B69">
         <v>3</v>
@@ -1368,10 +1368,10 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>alfredo_miras</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B70">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -1382,27 +1382,27 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>fabinho_falcao_</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B71">
         <v>2</v>
       </c>
       <c r="C71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D71">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>ailinperezufc</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B72">
         <v>2</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D72">
         <v>1</v>
@@ -1410,27 +1410,27 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>mah__vergueiro</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B74">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D74">
         <v>0</v>
@@ -1438,13 +1438,13 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>lipe.ftt</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B75">
         <v>4</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D75">
         <v>0</v>
@@ -1452,7 +1452,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>fau_gfs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B76">
         <v>4</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>gustavomohallem</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B77">
         <v>4</v>
@@ -1480,7 +1480,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B78">
         <v>4</v>
@@ -1494,7 +1494,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>_pizzariabambina_</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B79">
         <v>4</v>
@@ -1508,21 +1508,21 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>artewebpersonalizados</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B80">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>tatibscardoso</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B81">
         <v>2</v>
@@ -1774,35 +1774,35 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>odeivisoncardoso</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C99">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D99">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>s__simone__</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D100">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>kaua_limaofc</v>
+        <v>s__simone__</v>
       </c>
       <c r="B101">
         <v>2</v>
@@ -1816,7 +1816,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>clouddhidden</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B102">
         <v>2</v>
@@ -1830,21 +1830,21 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>lucascardosol__</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103">
         <v>0</v>
       </c>
       <c r="D103">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>ruangzk</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -1858,55 +1858,55 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ismaeldaniell</v>
+        <v>ruangzk</v>
       </c>
       <c r="B105">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C105">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D105">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>douglasipvr_mma</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D106">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>tassiogiloficial</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>vnciuss__df</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B108">
         <v>2</v>
       </c>
       <c r="C108">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D108">
         <v>0</v>
@@ -1914,13 +1914,13 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>jhee_dias</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D109">
         <v>0</v>
@@ -1928,35 +1928,35 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>albertoleandromoco</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B110">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C110">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>pauloserrati</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B111">
         <v>1</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D111">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -1970,41 +1970,41 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>leticiamartinspro</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D113">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>fredoctmma</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D114">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>diegopaivajj</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -2012,13 +2012,13 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>fabaotipster</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B116">
         <v>1</v>
       </c>
       <c r="C116">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D116">
         <v>1</v>
@@ -2026,21 +2026,21 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>joegam3r</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B117">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D117">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>mimuniz.bjj</v>
+        <v>joegam3r</v>
       </c>
       <c r="B118">
         <v>2</v>
@@ -2054,7 +2054,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>orafao1</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B119">
         <v>2</v>
@@ -2068,7 +2068,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>fabi.godooy</v>
+        <v>orafao1</v>
       </c>
       <c r="B120">
         <v>2</v>
@@ -2082,21 +2082,21 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>leobahiamma</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C121">
         <v>0</v>
       </c>
       <c r="D121">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -2110,7 +2110,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -2124,21 +2124,21 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>wlt_miguel</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B124">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C124">
         <v>0</v>
       </c>
       <c r="D124">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B125">
         <v>2</v>
@@ -2152,7 +2152,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>wesley_bjjvc</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B126">
         <v>2</v>
@@ -2166,21 +2166,21 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>heltoncm2002</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127">
         <v>0</v>
       </c>
       <c r="D127">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>raelduraes</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B128">
         <v>1</v>
@@ -2194,35 +2194,35 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>aliferpaulo_</v>
+        <v>raelduraes</v>
       </c>
       <c r="B129">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C129">
         <v>0</v>
       </c>
       <c r="D129">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B130">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C130">
         <v>0</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>mineirinho_jj</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -2236,7 +2236,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>graalino</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>lopesbrunao</v>
+        <v>graalino</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>pedrinhosbjj</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,7 +2278,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -2306,7 +2306,7 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>jesabelmelo9</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -2320,7 +2320,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>marcocanatelli</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,21 +2334,21 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>pvd_._dudis</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B139">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C139">
         <v>0</v>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B140">
         <v>2</v>
@@ -2362,21 +2362,21 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>sr.valter</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C141">
         <v>0</v>
       </c>
       <c r="D141">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>devessonjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>tatianeaguiarp</v>
+        <v>devessonjj</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>viktor.torquato</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>eric.shpritz</v>
+        <v>viktor.torquato</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,13 +2432,13 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B146">
         <v>1</v>
       </c>
       <c r="C146">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -2446,27 +2446,27 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>treinaadorrafael</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>benjafloripabjj</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B148">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -2474,13 +2474,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>fernando.mma</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B149">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -2488,13 +2488,13 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B150">
         <v>1</v>
       </c>
       <c r="C150">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -2502,13 +2502,13 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>estevaotoledo</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B151">
         <v>1</v>
       </c>
       <c r="C151">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -2516,13 +2516,13 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B152">
         <v>1</v>
       </c>
       <c r="C152">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D152">
         <v>0</v>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>fagnerosensei</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -2544,13 +2544,13 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>030sami</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B154">
         <v>1</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D154">
         <v>0</v>
@@ -2558,7 +2558,7 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>guiiviieira_</v>
+        <v>030sami</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2572,7 +2572,7 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2586,7 +2586,7 @@
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2600,7 +2600,7 @@
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>emerson_lucaszx</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -2614,7 +2614,7 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>danni_goncalves12</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -2628,7 +2628,7 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -2642,7 +2642,7 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -2656,7 +2656,7 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>kawannsennast</v>
+        <v>gildojiu</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -2684,7 +2684,7 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>yurimartins1_</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -2698,7 +2698,7 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>matheusteodoro_1</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,13 +2726,13 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>kael_lyto</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B167">
         <v>1</v>
       </c>
       <c r="C167">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D167">
         <v>0</v>
@@ -2740,13 +2740,13 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>kalindrafaria</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B168">
         <v>1</v>
       </c>
       <c r="C168">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -2754,35 +2754,35 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B169">
         <v>1</v>
       </c>
       <c r="C169">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D169">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B170">
         <v>1</v>
       </c>
       <c r="C170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>chuck_tlp</v>
+        <v>andreibjj</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,35 +2824,35 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>cristianpsicologo</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B174">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C174">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D174">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>juanx.pontes</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B175">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C175">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D175">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>select_from_joao</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -2866,7 +2866,7 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>yeslifeacademia</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -2880,7 +2880,7 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>ojaimerocha</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -2894,35 +2894,35 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>antonioemanuel.13</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C179">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D179">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C180">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>magnoddias</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -2950,13 +2950,13 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>tonketjudes</v>
+        <v>magnoddias</v>
       </c>
       <c r="B183">
         <v>1</v>
       </c>
       <c r="C183">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>_eliasffx</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>pdfiv</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,7 +2992,7 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>mariaraimundad940</v>
+        <v>pdfiv</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -3006,7 +3006,7 @@
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>gabesantos.13</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>euvitormirandaa</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>thompsonborralho</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>frankikolimabjj</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -3062,7 +3062,7 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>alerrandrojj</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -3076,7 +3076,7 @@
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>anahangelica</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -3090,7 +3090,7 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>anahangelica</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -3104,7 +3104,7 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>minotaurinho</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>lara.rpr</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>codasqueves</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>yan_touro.7766</v>
+        <v>codasqueves</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>carolinne.xwp</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>davicorbella</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>davicorbella</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>artemio_bjj</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>katiaecarreraf</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>geraldocnetomma</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,35 +3258,35 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>pedro_pavin_</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B205">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C205">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D205">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>xavyeroficial</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C206">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D206">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>maryanagandra</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>eliandropires</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,35 +3314,35 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>eliandropires</v>
       </c>
       <c r="B209">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C209">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D209">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>charlesanthony2466</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B210">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C210">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>draanapaulaponceano</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>saj_photo_miami</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>alternativaremocoes</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>benivalentinn</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,7 +3426,7 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>navarro_9430</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>_puroosso88</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>_rayysp</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>cami.terra_</v>
+        <v>_rayysp</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,7 +3482,7 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>gabicardoson</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -3496,7 +3496,7 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>martta.mariah</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>jaonevesz</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>pietroshz</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>___neller</v>
+        <v>pietroshz</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>_bety_marcal</v>
+        <v>___neller</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>guilhermeefelix__</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>pativinisf</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>judadany</v>
+        <v>pativinisf</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>andre_alcausa</v>
+        <v>judadany</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>_fernunes</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>aloirmarcal</v>
+        <v>_fernunes</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>gilberto_7606</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>flazuera14</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>camii_bonfim</v>
+        <v>flazuera14</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>danlouiz.jj</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>gabriel_trevelin</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>y.arthur_01</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>muricunha</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>victorhenriquebjj</v>
+        <v>muricunha</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>_lsanchess_</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>__bielgg</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>mr__rlk01</v>
+        <v>__bielgg</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>vitor_buck</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>fran.ruys</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>sambagabrieloficial</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B248">
         <v>1</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>_alcantara.bru</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B249">
         <v>1</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>cesar.boanerges</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B250">
         <v>1</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B251">
         <v>1</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>alexandreconsentino</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B252">
         <v>1</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,13 +3944,13 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>rafaela_duaartee</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B254">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C254">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D254">
         <v>0</v>
@@ -3958,13 +3958,13 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B255">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C255">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>andre.legendre.10</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>phillipe.harry</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B257">
         <v>1</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>andrejetx</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>leandro_motiv4</v>
+        <v>andrejetx</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>olga.oliveira013</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B260">
         <v>1</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B261">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>leosacraa</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B262">
         <v>1</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>gutocriativo</v>
+        <v>leosacraa</v>
       </c>
       <c r="B263">
         <v>1</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>igorfso_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B264">
         <v>1</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>igorfso_</v>
       </c>
       <c r="B265">
         <v>1</v>
@@ -4112,7 +4112,7 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>lay_roqs</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B266">
         <v>1</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>bigjota.artist</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B268">
         <v>1</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>mth_fernandes031</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B269">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B270">
         <v>1</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>turmanmma</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B271">
         <v>1</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>atlta.marc0s</v>
+        <v>turmanmma</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B273">
         <v>1</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>hermaan10_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B275">
         <v>1</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B276">
         <v>1</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B277">
         <v>1</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B278">
         <v>1</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B279">
         <v>1</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B280">
         <v>1</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B281">
         <v>1</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B282">
         <v>1</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>natalan_wilgner</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B283">
         <v>1</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B284">
         <v>1</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B285">
         <v>1</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B286">
         <v>1</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B287">
         <v>1</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>moisespira</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B288">
         <v>1</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B289">
         <v>1</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B291">
         <v>1</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B292">
         <v>1</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B293">
         <v>1</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B294">
         <v>1</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B295">
         <v>1</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B296">
         <v>1</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B297">
         <v>1</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>fernandamourabjj</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B298">
         <v>1</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B299">
         <v>1</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B300">
         <v>1</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B301">
         <v>1</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B302">
         <v>1</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>joselia_1980</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B303">
         <v>1</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>soniarochaco</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B304">
         <v>1</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>leandro_pedro7</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B305">
         <v>1</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>camillinhamma</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B306">
         <v>1</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>martins.rauanee</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B307">
         <v>1</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>ever.soulson</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B308">
         <v>1</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>mestrevascobento</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B309">
         <v>1</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B310">
         <v>1</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B311">
         <v>1</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>santos39roger</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B312">
         <v>1</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>leonardomesquitamma</v>
+        <v>santos39roger</v>
       </c>
       <c r="B313">
         <v>1</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>marinealcausa</v>
+        <v>macamariotti</v>
       </c>
       <c r="B314">
         <v>0</v>
@@ -4793,12 +4793,12 @@
         <v>4</v>
       </c>
       <c r="D314">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>emersonriosmma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -4812,21 +4812,21 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>luizcosta_mma</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B316">
         <v>0</v>
       </c>
       <c r="C316">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D316">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>giulia.fasolato</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>brodschack_</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -4854,21 +4854,21 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>michelle_mirele</v>
+        <v>brodschack_</v>
       </c>
       <c r="B319">
         <v>0</v>
       </c>
       <c r="C319">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D319">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>danielfranzesilva</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B320">
         <v>0</v>
@@ -4882,21 +4882,21 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B321">
         <v>0</v>
       </c>
       <c r="C321">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D321">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>dayanaa1511</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>ommariotti</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>guerreirammaofc</v>
+        <v>ommariotti</v>
       </c>
       <c r="B324">
         <v>0</v>
@@ -4938,7 +4938,7 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>pedro_giraldi</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B325">
         <v>0</v>
@@ -4952,7 +4952,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>pedro_giraldi</v>
       </c>
       <c r="B326">
         <v>0</v>
@@ -4961,26 +4961,26 @@
         <v>2</v>
       </c>
       <c r="D326">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>vanessamelomma</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B327">
         <v>0</v>
       </c>
       <c r="C327">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D327">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>leonardopateira</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B328">
         <v>0</v>
@@ -4994,7 +4994,7 @@
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>rahikikhalid</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B329">
         <v>0</v>
@@ -5008,21 +5008,21 @@
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>manumito.oficial</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B330">
         <v>0</v>
       </c>
       <c r="C330">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D330">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5050,21 +5050,21 @@
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B333">
         <v>0</v>
       </c>
       <c r="C333">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D333">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>coutz11</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B334">
         <v>0</v>
@@ -5078,21 +5078,21 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>orlando_alfa09</v>
+        <v>coutz11</v>
       </c>
       <c r="B335">
         <v>0</v>
       </c>
       <c r="C335">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D335">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>vitorshowman</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5106,7 +5106,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>4lissson</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5120,21 +5120,21 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>danilofernandescf</v>
+        <v>4lissson</v>
       </c>
       <c r="B338">
         <v>0</v>
       </c>
       <c r="C338">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D338">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>bryandazuera</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B339">
         <v>0</v>
@@ -5148,7 +5148,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>_vpft</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B340">
         <v>0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>izabeldelfino_</v>
+        <v>_vpft</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>janjaovix</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>janjaovix</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,7 +5204,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B344">
         <v>0</v>
@@ -5218,7 +5218,7 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B345">
         <v>0</v>
@@ -5232,7 +5232,7 @@
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>peacegrappler_archive</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>paulomartins.mma</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>macamariotti</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -6982,13 +6982,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B2">
-        <v>779</v>
+        <v>825</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>644</v>
+        <v>689</v>
       </c>
     </row>
     <row r="3">
@@ -7010,10 +7010,10 @@
         <v>pablofiorindi</v>
       </c>
       <c r="B4">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="C4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D4">
         <v>82</v>
@@ -7024,13 +7024,13 @@
         <v>hugo7jj</v>
       </c>
       <c r="B5">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6">
@@ -7038,13 +7038,13 @@
         <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="C6">
         <v>1</v>
       </c>
       <c r="D6">
-        <v>62</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7">
@@ -7094,13 +7094,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B10">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C10">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11">
@@ -7122,13 +7122,13 @@
         <v>combintel</v>
       </c>
       <c r="B12">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -7223,7 +7223,7 @@
         <v>12</v>
       </c>
       <c r="C19">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -7237,7 +7237,7 @@
         <v>6</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20">
         <v>6</v>
@@ -7287,24 +7287,24 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>ninjatheorist</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B24">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>irmandadefightteam</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B25">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -7315,7 +7315,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>gra_jpereira</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B26">
         <v>4</v>
@@ -7324,35 +7324,35 @@
         <v>0</v>
       </c>
       <c r="D26">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>tabajaraharu</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B27">
         <v>4</v>
       </c>
       <c r="C27">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B28">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D28">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -7427,7 +7427,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>pitbullandrade</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B34">
         <v>3</v>
@@ -7441,10 +7441,10 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>karen.ottoni</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C35">
         <v>0</v>
@@ -7455,7 +7455,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>alfredo_miras</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B36">
         <v>2</v>
@@ -7469,91 +7469,91 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>dogodoyfoto</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B37">
         <v>2</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C38">
         <v>1</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>badboykillermma</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B39">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>gustavomohallem</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B40">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>pedromadeira.s</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B41">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B42">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>_pizzariabambina_</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B43">
         <v>4</v>
@@ -7567,21 +7567,21 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>vndcardoso</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>artewebpersonalizados</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B45">
         <v>2</v>
@@ -7595,7 +7595,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>tatibscardoso</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B46">
         <v>2</v>
@@ -7651,105 +7651,105 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>meol.socialmidia</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
         <v>3</v>
       </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
       <c r="D50">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>marcos_tailandess</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C51">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>ravenrodriguez___</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B52">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D52">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>leticiamartinspro</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D53">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>washington_cassisno</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>enzoferrari680</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>pedrinhosbjj</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B56">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>araujojonaspenhade</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -7777,7 +7777,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>jesabelmelo9</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -7791,7 +7791,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>marcocanatelli</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -7805,21 +7805,21 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>pvd_._dudis</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B61">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>boia_capoeira</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -7833,21 +7833,21 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>sr.valter</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B63">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>devessonjj</v>
+        <v>sr.valter</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -7861,7 +7861,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>tatianeaguiarp</v>
+        <v>devessonjj</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -7875,7 +7875,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>viktor.torquato</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B66">
         <v>1</v>
@@ -7889,7 +7889,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>eric.shpritz</v>
+        <v>viktor.torquato</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -7903,27 +7903,27 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>estevaotoledo</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B68">
         <v>1</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>kalindrafaria</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B69">
         <v>1</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D69">
         <v>0</v>
@@ -7931,35 +7931,35 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B70">
         <v>1</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D70">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B71">
         <v>1</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>oniszczuk_ko</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B72">
         <v>1</v>
@@ -7973,7 +7973,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -7987,7 +7987,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>chuck_tlp</v>
+        <v>andreibjj</v>
       </c>
       <c r="B74">
         <v>1</v>
@@ -8001,35 +8001,35 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>antonioemanuel.13</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C75">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B76">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B77">
         <v>1</v>
@@ -8043,7 +8043,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>magnoddias</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B78">
         <v>1</v>
@@ -8057,13 +8057,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>atlta.marc0s</v>
+        <v>magnoddias</v>
       </c>
       <c r="B79">
         <v>1</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D79">
         <v>0</v>
@@ -8071,7 +8071,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>arturbambam</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B80">
         <v>1</v>
@@ -8085,7 +8085,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>hermaan10_</v>
+        <v>arturbambam</v>
       </c>
       <c r="B81">
         <v>1</v>
@@ -8099,7 +8099,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>danieljsantoss_</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B82">
         <v>1</v>
@@ -8113,7 +8113,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>rodrigojansen_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B83">
         <v>1</v>
@@ -8127,7 +8127,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>markakasocks</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B84">
         <v>1</v>
@@ -8141,7 +8141,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>hunter.mccrary</v>
+        <v>markakasocks</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -8155,7 +8155,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>omarcotomaz</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B86">
         <v>1</v>
@@ -8169,7 +8169,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>alphavillesup</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B87">
         <v>1</v>
@@ -8183,7 +8183,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>ricieritonan</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B88">
         <v>1</v>
@@ -8197,7 +8197,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>lucasampaio</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B89">
         <v>1</v>
@@ -8211,7 +8211,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>cjrnavalha</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B90">
         <v>1</v>
@@ -8225,7 +8225,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>natalan_wilgner</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B91">
         <v>1</v>
@@ -8239,7 +8239,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>manmoska</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B92">
         <v>1</v>
@@ -8253,7 +8253,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>renatoevangelistaa</v>
+        <v>manmoska</v>
       </c>
       <c r="B93">
         <v>1</v>
@@ -8267,7 +8267,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>cassius.paula</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B94">
         <v>1</v>
@@ -8281,7 +8281,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B95">
         <v>1</v>
@@ -8295,7 +8295,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>aliferpaulo_</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B96">
         <v>1</v>
@@ -8309,7 +8309,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>moisespira</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B97">
         <v>1</v>
@@ -8323,7 +8323,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>rodrigolidiosales</v>
+        <v>moisespira</v>
       </c>
       <c r="B98">
         <v>1</v>
@@ -8337,7 +8337,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B99">
         <v>1</v>
@@ -8351,7 +8351,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>marciocatenacci</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B100">
         <v>1</v>
@@ -8365,7 +8365,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>cristiane.c.santana</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B101">
         <v>1</v>
@@ -8379,7 +8379,7 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>ariel_alvees</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B102">
         <v>1</v>
@@ -8393,7 +8393,7 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>flahvinhotreinador</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B103">
         <v>1</v>
@@ -8407,7 +8407,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B104">
         <v>1</v>
@@ -8421,7 +8421,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>selma.oscar12</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B105">
         <v>1</v>
@@ -8435,7 +8435,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>romulobelarmino</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B106">
         <v>1</v>
@@ -8449,7 +8449,7 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -8463,7 +8463,7 @@
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>fernandamourabjj</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B108">
         <v>1</v>
@@ -8477,7 +8477,7 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>larissamartinsbjj</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -8491,7 +8491,7 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B110">
         <v>1</v>
@@ -8505,7 +8505,7 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>leitefelippez</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B111">
         <v>1</v>
@@ -8519,7 +8519,7 @@
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>israelbahiensebraz</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B112">
         <v>1</v>
@@ -8533,7 +8533,7 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>wlt_miguel</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B113">
         <v>1</v>
@@ -8547,7 +8547,7 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>wesley_bjjvc</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B114">
         <v>1</v>
@@ -8561,7 +8561,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>juniordiasmma</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B115">
         <v>1</v>
@@ -8575,7 +8575,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>joselia_1980</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B116">
         <v>1</v>
@@ -8589,7 +8589,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>kaua_limamma</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B117">
         <v>1</v>
@@ -8603,7 +8603,7 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>soniarochaco</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B118">
         <v>1</v>
@@ -8617,7 +8617,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>leandro_pedro7</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B119">
         <v>1</v>
@@ -8631,7 +8631,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>camillinhamma</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B120">
         <v>1</v>
@@ -8645,7 +8645,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>martins.rauanee</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B121">
         <v>1</v>
@@ -8659,7 +8659,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>ever.soulson</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B122">
         <v>1</v>
@@ -8673,7 +8673,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>mestrevascobento</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B123">
         <v>1</v>
@@ -8687,7 +8687,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B124">
         <v>1</v>
@@ -8701,7 +8701,7 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B125">
         <v>1</v>
@@ -8715,7 +8715,7 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>santos39roger</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B126">
         <v>1</v>
@@ -8729,7 +8729,7 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>leonardomesquitamma</v>
+        <v>santos39roger</v>
       </c>
       <c r="B127">
         <v>1</v>
@@ -8743,13 +8743,13 @@
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>maca.mariotti</v>
+        <v>macamariotti</v>
       </c>
       <c r="B128">
         <v>0</v>
       </c>
       <c r="C128">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D128">
         <v>1</v>
@@ -8757,21 +8757,21 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>gdazuera</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B129">
         <v>0</v>
       </c>
       <c r="C129">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D129">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>guerreirammaofc</v>
+        <v>gdazuera</v>
       </c>
       <c r="B130">
         <v>0</v>
@@ -8780,12 +8780,12 @@
         <v>2</v>
       </c>
       <c r="D130">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>pedro_giraldi</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -8799,13 +8799,13 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>izabeldelfino_</v>
+        <v>pedro_giraldi</v>
       </c>
       <c r="B132">
         <v>0</v>
       </c>
       <c r="C132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -8813,7 +8813,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>janjaovix</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -8827,21 +8827,21 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>janjaovix</v>
       </c>
       <c r="B134">
         <v>0</v>
       </c>
       <c r="C134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D134">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -8855,21 +8855,21 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B136">
         <v>0</v>
       </c>
       <c r="C136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B137">
         <v>0</v>
@@ -8883,7 +8883,7 @@
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B138">
         <v>0</v>
@@ -8897,7 +8897,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>edebetim_</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B139">
         <v>0</v>
@@ -8911,7 +8911,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>peacegrappler_archive</v>
+        <v>edebetim_</v>
       </c>
       <c r="B140">
         <v>0</v>
@@ -8925,7 +8925,7 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>_oliveira09_</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B141">
         <v>0</v>
@@ -8939,7 +8939,7 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>brodschack_</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B142">
         <v>0</v>
@@ -8953,7 +8953,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>paulomartins.mma</v>
+        <v>brodschack_</v>
       </c>
       <c r="B143">
         <v>0</v>
@@ -8967,7 +8967,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>macamariotti</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B144">
         <v>0</v>

--- a/Engagement Rankings 2026-04.xlsx
+++ b/Engagement Rankings 2026-04.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D468"/>
+  <dimension ref="A1:D485"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,13 +433,13 @@
         <v>peacegrappler</v>
       </c>
       <c r="B3">
-        <v>826</v>
+        <v>1223</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>689</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="4">
@@ -447,69 +447,69 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B4">
-        <v>387</v>
+        <v>471</v>
       </c>
       <c r="C4">
         <v>11</v>
       </c>
       <c r="D4">
-        <v>323</v>
+        <v>401</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>luis_pequeno_mma</v>
+        <v>pablofiorindi</v>
       </c>
       <c r="B5">
-        <v>368</v>
+        <v>481</v>
       </c>
       <c r="C5">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D5">
-        <v>53</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>pablofiorindi</v>
+        <v>enzocardoso.bjj</v>
       </c>
       <c r="B6">
-        <v>338</v>
+        <v>448</v>
       </c>
       <c r="C6">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>120</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>enzocardoso.bjj</v>
+        <v>luis_pequeno_mma</v>
       </c>
       <c r="B7">
-        <v>327</v>
+        <v>420</v>
       </c>
       <c r="C7">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D7">
-        <v>107</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>pedr00jj</v>
+        <v>hugo7jj</v>
       </c>
       <c r="B8">
-        <v>235</v>
+        <v>283</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>96</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9">
@@ -517,27 +517,27 @@
         <v>rpsantos_mma</v>
       </c>
       <c r="B9">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="C9">
         <v>5</v>
       </c>
       <c r="D9">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>hugo7jj</v>
+        <v>pedr00jj</v>
       </c>
       <c r="B10">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D10">
-        <v>107</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -545,13 +545,13 @@
         <v>rm.nicki</v>
       </c>
       <c r="B11">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="C11">
         <v>2</v>
       </c>
       <c r="D11">
-        <v>112</v>
+        <v>120</v>
       </c>
     </row>
     <row r="12">
@@ -559,13 +559,13 @@
         <v>pg_grappling</v>
       </c>
       <c r="B12">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
@@ -573,119 +573,119 @@
         <v>anaaj_camargo</v>
       </c>
       <c r="B13">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>ryangandraufc</v>
+        <v>combintel</v>
       </c>
       <c r="B14">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C14">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>combintel</v>
+        <v>irmandadefightteam</v>
       </c>
       <c r="B15">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C15">
         <v>1</v>
       </c>
       <c r="D15">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>irmandadefightteam</v>
+        <v>ryangandraufc</v>
       </c>
       <c r="B16">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>mmmarc20</v>
+        <v>rmml_fight</v>
       </c>
       <c r="B17">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ronemayanmorais</v>
+        <v>mmmarc20</v>
       </c>
       <c r="B18">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>bellsouza816</v>
+        <v>ronemayanmorais</v>
       </c>
       <c r="B19">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>erik_.mma</v>
+        <v>bellsouza816</v>
       </c>
       <c r="B20">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>kaua_limamma</v>
+        <v>erik_.mma</v>
       </c>
       <c r="B21">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -696,307 +696,307 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>aline.r15</v>
+        <v>kaua_limamma</v>
       </c>
       <c r="B22">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C22">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>god.motivacao</v>
+        <v>aline.r15</v>
       </c>
       <c r="B23">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="C23">
-        <v>139</v>
+        <v>9</v>
       </c>
       <c r="D23">
-        <v>44</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>cleyton_jesuss</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B24">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>139</v>
       </c>
       <c r="D24">
-        <v>18</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>gra_jpereira</v>
+        <v>cleyton_jesuss</v>
       </c>
       <c r="B25">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lucasluiz911_mma</v>
+        <v>gra_jpereira</v>
       </c>
       <c r="B26">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C26">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>leandro._bjj</v>
+        <v>lucasluiz911_mma</v>
       </c>
       <c r="B27">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C27">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>alvesmidih</v>
+        <v>leandro._bjj</v>
       </c>
       <c r="B28">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D28">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>maxgandra</v>
+        <v>alvesmidih</v>
       </c>
       <c r="B29">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C29">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>eliassilverio</v>
+        <v>maxgandra</v>
       </c>
       <c r="B30">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D30">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>tabajaraharu</v>
+        <v>eliassilverio</v>
       </c>
       <c r="B31">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C31">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D31">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>tiwimma</v>
+        <v>tabajaraharu</v>
       </c>
       <c r="B32">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>pedromadeira.s</v>
+        <v>tiwimma</v>
       </c>
       <c r="B33">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>marc0s.azv</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B34">
         <v>14</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>cjrnavalha</v>
+        <v>marc0s.azv</v>
       </c>
       <c r="B35">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D35">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>kauepraciano</v>
+        <v>cjrnavalha</v>
       </c>
       <c r="B36">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>_beegomes_</v>
+        <v>excelentfightcompetition</v>
       </c>
       <c r="B37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C37">
         <v>1</v>
       </c>
       <c r="D37">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>vndcardoso</v>
+        <v>livreseseguras</v>
       </c>
       <c r="B38">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D38">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>tawanregismma</v>
+        <v>kauepraciano</v>
       </c>
       <c r="B39">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C39">
         <v>1</v>
       </c>
       <c r="D39">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>karen.ottoni</v>
+        <v>vndcardoso</v>
       </c>
       <c r="B40">
+        <v>8</v>
+      </c>
+      <c r="C40">
+        <v>0</v>
+      </c>
+      <c r="D40">
         <v>5</v>
-      </c>
-      <c r="C40">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <v>4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>excelentfightcompetition</v>
+        <v>_beegomes_</v>
       </c>
       <c r="B41">
+        <v>8</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
         <v>6</v>
-      </c>
-      <c r="C41">
-        <v>1</v>
-      </c>
-      <c r="D41">
-        <v>2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>ninjatheorist</v>
+        <v>tawanregismma</v>
       </c>
       <c r="B42">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D42">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>adriano.trator</v>
+        <v>shawlin13oficial</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C43">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -1004,195 +1004,195 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>rrafaelins</v>
+        <v>enzoferrari680</v>
       </c>
       <c r="B44">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>juniordiasmma</v>
+        <v>karen.ottoni</v>
       </c>
       <c r="B45">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>jvxz______</v>
       </c>
       <c r="B46">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>enzoferrari680</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
         <v>3</v>
-      </c>
-      <c r="D47">
-        <v>2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>gdazuera</v>
+        <v>adriano.trator</v>
       </c>
       <c r="B48">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D48">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>italothearcher</v>
+        <v>rrafaelins</v>
       </c>
       <c r="B49">
         <v>4</v>
       </c>
       <c r="C49">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D49">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>badboykillermma</v>
+        <v>juniordiasmma</v>
       </c>
       <c r="B50">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>dogodoyfoto</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B51">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C51">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D51">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>decio_bjj</v>
       </c>
       <c r="B52">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>marcos_tailandess</v>
+        <v>gdazuera</v>
       </c>
       <c r="B53">
         <v>3</v>
       </c>
       <c r="C53">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>ravenrodriguez___</v>
+        <v>italothearcher</v>
       </c>
       <c r="B54">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C54">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="D54">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>maria_bonita_kairos</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B55">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>livreseseguras</v>
+        <v>dogodoyfoto</v>
       </c>
       <c r="B56">
         <v>4</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>eolucasrosa</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B57">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D57">
         <v>1</v>
@@ -1200,111 +1200,111 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>dagestan0920</v>
+        <v>marcos_tailandess</v>
       </c>
       <c r="B58">
+        <v>3</v>
+      </c>
+      <c r="C58">
+        <v>9</v>
+      </c>
+      <c r="D58">
         <v>5</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>paxlucta</v>
+        <v>ravenrodriguez___</v>
       </c>
       <c r="B59">
+        <v>5</v>
+      </c>
+      <c r="C59">
         <v>4</v>
       </c>
-      <c r="C59">
-        <v>5</v>
-      </c>
       <c r="D59">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>_.maduoliveira_</v>
+        <v>maria_bonita_kairos</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ailtonjuniorbarbeiro</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D61">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>_oliveira09_</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B62">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C62">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>edebetim_</v>
+        <v>paxlucta</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C63">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D63">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>glm.barbosa</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D64">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>marcelogabrielmma</v>
+        <v>_.maduoliveira_</v>
       </c>
       <c r="B65">
         <v>3</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>3</v>
@@ -1312,27 +1312,27 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>washington_cassisno</v>
+        <v>gustavomohallem</v>
       </c>
       <c r="B66">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D66">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>gabrielsouzamma</v>
+        <v>_cardoso_caio_</v>
       </c>
       <c r="B67">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -1340,49 +1340,49 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>salost.ofc</v>
+        <v>ailtonjuniorbarbeiro</v>
       </c>
       <c r="B68">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C68">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>tatibscardoso</v>
+        <v>_oliveira09_</v>
       </c>
       <c r="B69">
         <v>3</v>
       </c>
       <c r="C69">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D69">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>pitbullandrade</v>
+        <v>edebetim_</v>
       </c>
       <c r="B70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C70">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D70">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>alfredo_miras</v>
+        <v>glm.barbosa</v>
       </c>
       <c r="B71">
         <v>2</v>
@@ -1396,21 +1396,21 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>fabinho_falcao_</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D72">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>ailinperezufc</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B73">
         <v>2</v>
@@ -1419,15 +1419,15 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>mah__vergueiro</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B74">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -1438,195 +1438,195 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>pizzaria.bambina_</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>lipe.ftt</v>
+        <v>pitbullandrade</v>
       </c>
       <c r="B76">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>fau_gfs</v>
+        <v>alfredo_miras</v>
       </c>
       <c r="B77">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>gustavomohallem</v>
+        <v>tiwifenixmma</v>
       </c>
       <c r="B78">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>espaco_jhayoliveira</v>
+        <v>fabinho_falcao_</v>
       </c>
       <c r="B79">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C79">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D79">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>_pizzariabambina_</v>
+        <v>ailinperezufc</v>
       </c>
       <c r="B80">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D80">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>artewebpersonalizados</v>
+        <v>mah__vergueiro</v>
       </c>
       <c r="B81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>shawlin13oficial</v>
+        <v>pizzaria.bambina_</v>
       </c>
       <c r="B82">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D82">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>eduardorodrigrs</v>
+        <v>lipe.ftt</v>
       </c>
       <c r="B83">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>diego.dieguito.3914</v>
+        <v>fau_gfs</v>
       </c>
       <c r="B84">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>febrancatti</v>
+        <v>anderson.logan.35</v>
       </c>
       <c r="B85">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>z.proddd</v>
+        <v>espaco_jhayoliveira</v>
       </c>
       <c r="B86">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>maca.mariotti</v>
+        <v>_pizzariabambina_</v>
       </c>
       <c r="B87">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C87">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>reifernandes</v>
+        <v>artewebpersonalizados</v>
       </c>
       <c r="B88">
         <v>2</v>
       </c>
       <c r="C88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D88">
         <v>2</v>
@@ -1634,7 +1634,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>daniel_dias_214</v>
+        <v>eduardorodrigrs</v>
       </c>
       <c r="B89">
         <v>2</v>
@@ -1648,7 +1648,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>fabiomarcelinopersonal</v>
+        <v>diego.dieguito.3914</v>
       </c>
       <c r="B90">
         <v>2</v>
@@ -1662,49 +1662,49 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>alexsandra_kairos</v>
+        <v>febrancatti</v>
       </c>
       <c r="B91">
         <v>2</v>
       </c>
       <c r="C91">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>multiplicaaba</v>
+        <v>z.proddd</v>
       </c>
       <c r="B92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D92">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>f.luan_11</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>vitorpetrino</v>
+        <v>_falcao95_</v>
       </c>
       <c r="B94">
         <v>2</v>
@@ -1718,7 +1718,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>jcchagas_</v>
+        <v>janyson.s</v>
       </c>
       <c r="B95">
         <v>2</v>
@@ -1732,55 +1732,55 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>anderson.logan.35</v>
+        <v>maca.mariotti</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>marifferreirac</v>
+        <v>reifernandes</v>
       </c>
       <c r="B97">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97">
         <v>1</v>
       </c>
       <c r="D97">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>meol.socialmidia</v>
+        <v>daniel_dias_214</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C98">
         <v>0</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>leonardomesquitamma</v>
+        <v>albertoleandromoco</v>
       </c>
       <c r="B99">
         <v>2</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -1788,41 +1788,41 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>odeivisoncardoso</v>
+        <v>fabiomarcelinopersonal</v>
       </c>
       <c r="B100">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D100">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>s__simone__</v>
+        <v>diegopaivajj</v>
       </c>
       <c r="B101">
         <v>2</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D101">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>kaua_limaofc</v>
+        <v>alexsandra_kairos</v>
       </c>
       <c r="B102">
         <v>2</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D102">
         <v>0</v>
@@ -1830,13 +1830,13 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>clouddhidden</v>
+        <v>multiplicaaba</v>
       </c>
       <c r="B103">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D103">
         <v>0</v>
@@ -1844,24 +1844,24 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>lucascardosol__</v>
+        <v>f.luan_11</v>
       </c>
       <c r="B104">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C104">
         <v>0</v>
       </c>
       <c r="D104">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ruangzk</v>
+        <v>vitorpetrino</v>
       </c>
       <c r="B105">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -1872,21 +1872,21 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ismaeldaniell</v>
+        <v>jcchagas_</v>
       </c>
       <c r="B106">
         <v>2</v>
       </c>
       <c r="C106">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>douglasipvr_mma</v>
+        <v>marifferreirac</v>
       </c>
       <c r="B107">
         <v>1</v>
@@ -1895,15 +1895,15 @@
         <v>1</v>
       </c>
       <c r="D107">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>tassiogiloficial</v>
+        <v>meol.socialmidia</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -1914,97 +1914,97 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>vnciuss__df</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B109">
         <v>2</v>
       </c>
       <c r="C109">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>jhee_dias</v>
+        <v>odeivisoncardoso</v>
       </c>
       <c r="B110">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D110">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>albertoleandromoco</v>
+        <v>s__simone__</v>
       </c>
       <c r="B111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C111">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>pauloserrati</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C112">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>leticiamartinspro</v>
+        <v>lucascardosol__</v>
       </c>
       <c r="B114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C114">
         <v>0</v>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>fredoctmma</v>
+        <v>ruangzk</v>
       </c>
       <c r="B115">
         <v>1</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D115">
         <v>1</v>
@@ -2012,49 +2012,49 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>diegopaivajj</v>
+        <v>docinhos26</v>
       </c>
       <c r="B116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C116">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>fabaotipster</v>
+        <v>ismaeldaniell</v>
       </c>
       <c r="B117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D117">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>joegam3r</v>
+        <v>douglasipvr_mma</v>
       </c>
       <c r="B118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D118">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>mimuniz.bjj</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B119">
         <v>2</v>
@@ -2068,13 +2068,13 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>orafao1</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B120">
         <v>2</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D120">
         <v>0</v>
@@ -2082,7 +2082,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>fabi.godooy</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B121">
         <v>2</v>
@@ -2096,119 +2096,119 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>leobahiamma</v>
+        <v>pauloserrati</v>
       </c>
       <c r="B122">
         <v>1</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D122">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B123">
         <v>1</v>
       </c>
       <c r="C123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D123">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C124">
         <v>0</v>
       </c>
       <c r="D124">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>wlt_miguel</v>
+        <v>fredoctmma</v>
       </c>
       <c r="B125">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B126">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D126">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>wesley_bjjvc</v>
+        <v>cristianpsicologo</v>
       </c>
       <c r="B127">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D127">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>heltoncm2002</v>
+        <v>joegam3r</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128">
         <v>0</v>
       </c>
       <c r="D128">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>raelduraes</v>
+        <v>mimuniz.bjj</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129">
         <v>0</v>
       </c>
       <c r="D129">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>aliferpaulo_</v>
+        <v>orafao1</v>
       </c>
       <c r="B130">
         <v>2</v>
@@ -2222,21 +2222,21 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B131">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C131">
         <v>0</v>
       </c>
       <c r="D131">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>mineirinho_jj</v>
+        <v>leobahiamma</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -2250,7 +2250,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>graalino</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2264,7 +2264,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>lopesbrunao</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -2278,49 +2278,49 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>pedrinhosbjj</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B135">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C135">
         <v>0</v>
       </c>
       <c r="D135">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>araujojonaspenhade</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B136">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C136">
         <v>0</v>
       </c>
       <c r="D136">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>japanjapanjapanjapanjapannihon</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B137">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C137">
         <v>0</v>
       </c>
       <c r="D137">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>jesabelmelo9</v>
+        <v>heltoncm2002</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>marcocanatelli</v>
+        <v>raelduraes</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -2348,7 +2348,7 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>pvd_._dudis</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B140">
         <v>2</v>
@@ -2362,21 +2362,21 @@
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>boia_capoeira</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B141">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C141">
         <v>0</v>
       </c>
       <c r="D141">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>sr.valter</v>
+        <v>mineirinho_jj</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -2390,7 +2390,7 @@
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>devessonjj</v>
+        <v>graalino</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -2404,7 +2404,7 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>tatianeaguiarp</v>
+        <v>lopesbrunao</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -2418,7 +2418,7 @@
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>viktor.torquato</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -2432,7 +2432,7 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>eric.shpritz</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -2446,13 +2446,13 @@
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>japanjapanjapanjapanjapannihon</v>
       </c>
       <c r="B147">
         <v>1</v>
       </c>
       <c r="C147">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -2460,41 +2460,41 @@
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>treinaadorrafael</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B148">
         <v>1</v>
       </c>
       <c r="C148">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D148">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>benjafloripabjj</v>
+        <v>marcocanatelli</v>
       </c>
       <c r="B149">
         <v>1</v>
       </c>
       <c r="C149">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D149">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>fernando.mma</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C150">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -2502,13 +2502,13 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C151">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D151">
         <v>0</v>
@@ -2516,49 +2516,49 @@
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>estevaotoledo</v>
+        <v>sr.valter</v>
       </c>
       <c r="B152">
         <v>1</v>
       </c>
       <c r="C152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>devessonjj</v>
       </c>
       <c r="B153">
         <v>1</v>
       </c>
       <c r="C153">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D153">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>fagnerosensei</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B154">
         <v>1</v>
       </c>
       <c r="C154">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>030sami</v>
+        <v>viktor.torquato</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -2567,12 +2567,12 @@
         <v>0</v>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>guiiviieira_</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -2581,12 +2581,12 @@
         <v>0</v>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>cshigueo</v>
+        <v>misskelsc</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -2595,32 +2595,32 @@
         <v>0</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B158">
         <v>1</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D158">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>emerson_lucaszx</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B159">
         <v>1</v>
       </c>
       <c r="C159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D159">
         <v>0</v>
@@ -2628,13 +2628,13 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>danni_goncalves12</v>
+        <v>benjafloripabjj</v>
       </c>
       <c r="B160">
         <v>1</v>
       </c>
       <c r="C160">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D160">
         <v>0</v>
@@ -2642,13 +2642,13 @@
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>mttsm._</v>
+        <v>fernando.mma</v>
       </c>
       <c r="B161">
         <v>1</v>
       </c>
       <c r="C161">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D161">
         <v>0</v>
@@ -2656,13 +2656,13 @@
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>andrealvess02</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B162">
         <v>1</v>
       </c>
       <c r="C162">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D162">
         <v>0</v>
@@ -2670,13 +2670,13 @@
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>gildojiu</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B163">
         <v>1</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D163">
         <v>0</v>
@@ -2684,13 +2684,13 @@
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>kawannsennast</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B164">
         <v>1</v>
       </c>
       <c r="C164">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D164">
         <v>0</v>
@@ -2698,13 +2698,13 @@
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>yurimartins1_</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B165">
         <v>1</v>
       </c>
       <c r="C165">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D165">
         <v>0</v>
@@ -2712,7 +2712,7 @@
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>matheusteodoro_1</v>
+        <v>030sami</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -2726,7 +2726,7 @@
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -2740,13 +2740,13 @@
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>kael_lyto</v>
+        <v>cshigueo</v>
       </c>
       <c r="B168">
         <v>1</v>
       </c>
       <c r="C168">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D168">
         <v>0</v>
@@ -2754,7 +2754,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>kalindrafaria</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -2768,21 +2768,21 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B170">
         <v>1</v>
       </c>
       <c r="C170">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D170">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -2796,7 +2796,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>oniszczuk_ko</v>
+        <v>mttsm._</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>andreibjj</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>chuck_tlp</v>
+        <v>gildojiu</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -2838,27 +2838,27 @@
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>cristianpsicologo</v>
+        <v>kawannsennast</v>
       </c>
       <c r="B175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C175">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D175">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>juanx.pontes</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B176">
         <v>1</v>
       </c>
       <c r="C176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D176">
         <v>0</v>
@@ -2866,13 +2866,13 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>select_from_joao</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B177">
         <v>1</v>
       </c>
       <c r="C177">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D177">
         <v>0</v>
@@ -2880,13 +2880,13 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>yeslifeacademia</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B178">
         <v>1</v>
       </c>
       <c r="C178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D178">
         <v>0</v>
@@ -2894,13 +2894,13 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>ojaimerocha</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B179">
         <v>1</v>
       </c>
       <c r="C179">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D179">
         <v>0</v>
@@ -2908,21 +2908,21 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>antonioemanuel.13</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B180">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C180">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D180">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>gasparjr1983</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -2931,18 +2931,18 @@
         <v>1</v>
       </c>
       <c r="D181">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>tuizainocenciorodrigues</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B182">
         <v>1</v>
       </c>
       <c r="C182">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D182">
         <v>0</v>
@@ -2950,13 +2950,13 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>magnoddias</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B183">
         <v>1</v>
       </c>
       <c r="C183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D183">
         <v>0</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>tonketjudes</v>
+        <v>andreibjj</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -2978,7 +2978,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>_eliasffx</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -2992,27 +2992,27 @@
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>pdfiv</v>
+        <v>macamariotti</v>
       </c>
       <c r="B186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C186">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>mariaraimundad940</v>
+        <v>juanx.pontes</v>
       </c>
       <c r="B187">
         <v>1</v>
       </c>
       <c r="C187">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D187">
         <v>0</v>
@@ -3020,13 +3020,13 @@
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>gabesantos.13</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B188">
         <v>1</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D188">
         <v>0</v>
@@ -3034,13 +3034,13 @@
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>euvitormirandaa</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B189">
         <v>1</v>
       </c>
       <c r="C189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D189">
         <v>0</v>
@@ -3048,13 +3048,13 @@
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>thompsonborralho</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B190">
         <v>1</v>
       </c>
       <c r="C190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D190">
         <v>0</v>
@@ -3062,27 +3062,27 @@
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>frankikolimabjj</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C191">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D191">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>alerrandrojj</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B192">
         <v>1</v>
       </c>
       <c r="C192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D192">
         <v>0</v>
@@ -3090,13 +3090,13 @@
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>anahangelica</v>
+        <v>tuizainocenciorodrigues</v>
       </c>
       <c r="B193">
         <v>1</v>
       </c>
       <c r="C193">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D193">
         <v>0</v>
@@ -3104,13 +3104,13 @@
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>magnoddias</v>
       </c>
       <c r="B194">
         <v>1</v>
       </c>
       <c r="C194">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D194">
         <v>0</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>minotaurinho</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -3132,7 +3132,7 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>lara.rpr</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>codasqueves</v>
+        <v>pdfiv</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -3160,7 +3160,7 @@
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>yan_touro.7766</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -3174,7 +3174,7 @@
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>carolinne.xwp</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>davicorbella</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -3202,7 +3202,7 @@
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>thompsonborralho</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -3216,7 +3216,7 @@
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>cjrnavalhaoficial</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -3230,7 +3230,7 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>artemio_bjj</v>
+        <v>alerrandrojj</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -3244,7 +3244,7 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>katiaecarreraf</v>
+        <v>anahangelica</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -3258,7 +3258,7 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>geraldocnetomma</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -3272,21 +3272,21 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>pedro_pavin_</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B206">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C206">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D206">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>xavyeroficial</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>maryanagandra</v>
+        <v>codasqueves</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>eliandropires</v>
+        <v>yan_touro.7766</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -3328,21 +3328,21 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B210">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C210">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D210">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>charlesanthony2466</v>
+        <v>davicorbella</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -3356,7 +3356,7 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -3370,7 +3370,7 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>draanapaulaponceano</v>
+        <v>cjrnavalhaoficial</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -3384,7 +3384,7 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>saj_photo_miami</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -3398,7 +3398,7 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>alternativaremocoes</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -3412,7 +3412,7 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>benivalentinn</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -3426,21 +3426,21 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B217">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C217">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D217">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>navarro_9430</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -3454,7 +3454,7 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>_puroosso88</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -3468,7 +3468,7 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>_rayysp</v>
+        <v>eliandropires</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -3482,21 +3482,21 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>cami.terra_</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C221">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D221">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>gabicardoson</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -3510,7 +3510,7 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>martta.mariah</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -3524,7 +3524,7 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>jaonevesz</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>pietroshz</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -3552,7 +3552,7 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>___neller</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -3566,7 +3566,7 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>_bety_marcal</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -3580,7 +3580,7 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>guilhermeefelix__</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>pativinisf</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -3608,7 +3608,7 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>judadany</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>andre_alcausa</v>
+        <v>_rayysp</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -3636,7 +3636,7 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>_fernunes</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -3650,7 +3650,7 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>aloirmarcal</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -3664,7 +3664,7 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>gilberto_7606</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -3678,7 +3678,7 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>jaonevesz</v>
       </c>
       <c r="B235">
         <v>1</v>
@@ -3692,7 +3692,7 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>flazuera14</v>
+        <v>pietroshz</v>
       </c>
       <c r="B236">
         <v>1</v>
@@ -3706,7 +3706,7 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>camii_bonfim</v>
+        <v>___neller</v>
       </c>
       <c r="B237">
         <v>1</v>
@@ -3720,7 +3720,7 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>danlouiz.jj</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B238">
         <v>1</v>
@@ -3734,7 +3734,7 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>gabriel_trevelin</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B239">
         <v>1</v>
@@ -3748,7 +3748,7 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>y.arthur_01</v>
+        <v>pativinisf</v>
       </c>
       <c r="B240">
         <v>1</v>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>muricunha</v>
+        <v>judadany</v>
       </c>
       <c r="B241">
         <v>1</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="242">
       <c r="A242" t="str">
-        <v>victorhenriquebjj</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B242">
         <v>1</v>
@@ -3790,7 +3790,7 @@
     </row>
     <row r="243">
       <c r="A243" t="str">
-        <v>_lsanchess_</v>
+        <v>_fernunes</v>
       </c>
       <c r="B243">
         <v>1</v>
@@ -3804,7 +3804,7 @@
     </row>
     <row r="244">
       <c r="A244" t="str">
-        <v>__bielgg</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B244">
         <v>1</v>
@@ -3818,7 +3818,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>mr__rlk01</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B245">
         <v>1</v>
@@ -3832,7 +3832,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>vitor_buck</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B246">
         <v>1</v>
@@ -3846,7 +3846,7 @@
     </row>
     <row r="247">
       <c r="A247" t="str">
-        <v>fran.ruys</v>
+        <v>flazuera14</v>
       </c>
       <c r="B247">
         <v>1</v>
@@ -3860,7 +3860,7 @@
     </row>
     <row r="248">
       <c r="A248" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B248">
         <v>1</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="249">
       <c r="A249" t="str">
-        <v>sambagabrieloficial</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B249">
         <v>1</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="250">
       <c r="A250" t="str">
-        <v>_alcantara.bru</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B250">
         <v>1</v>
@@ -3902,7 +3902,7 @@
     </row>
     <row r="251">
       <c r="A251" t="str">
-        <v>cesar.boanerges</v>
+        <v>y.arthur_01</v>
       </c>
       <c r="B251">
         <v>1</v>
@@ -3916,7 +3916,7 @@
     </row>
     <row r="252">
       <c r="A252" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>muricunha</v>
       </c>
       <c r="B252">
         <v>1</v>
@@ -3930,7 +3930,7 @@
     </row>
     <row r="253">
       <c r="A253" t="str">
-        <v>alexandreconsentino</v>
+        <v>victorhenriquebjj</v>
       </c>
       <c r="B253">
         <v>1</v>
@@ -3944,7 +3944,7 @@
     </row>
     <row r="254">
       <c r="A254" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B254">
         <v>1</v>
@@ -3958,13 +3958,13 @@
     </row>
     <row r="255">
       <c r="A255" t="str">
-        <v>rafaela_duaartee</v>
+        <v>__bielgg</v>
       </c>
       <c r="B255">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C255">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D255">
         <v>0</v>
@@ -3972,7 +3972,7 @@
     </row>
     <row r="256">
       <c r="A256" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B256">
         <v>1</v>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="257">
       <c r="A257" t="str">
-        <v>andre.legendre.10</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B257">
         <v>1</v>
@@ -4000,7 +4000,7 @@
     </row>
     <row r="258">
       <c r="A258" t="str">
-        <v>phillipe.harry</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B258">
         <v>1</v>
@@ -4014,7 +4014,7 @@
     </row>
     <row r="259">
       <c r="A259" t="str">
-        <v>andrejetx</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B259">
         <v>1</v>
@@ -4028,7 +4028,7 @@
     </row>
     <row r="260">
       <c r="A260" t="str">
-        <v>leandro_motiv4</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B260">
         <v>1</v>
@@ -4042,7 +4042,7 @@
     </row>
     <row r="261">
       <c r="A261" t="str">
-        <v>olga.oliveira013</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B261">
         <v>1</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="262">
       <c r="A262" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B262">
         <v>1</v>
@@ -4070,7 +4070,7 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>leosacraa</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B263">
         <v>1</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>gutocriativo</v>
+        <v>alexandreconsentino</v>
       </c>
       <c r="B264">
         <v>1</v>
@@ -4098,7 +4098,7 @@
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>igorfso_</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B265">
         <v>1</v>
@@ -4112,13 +4112,13 @@
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B266">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C266">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D266">
         <v>0</v>
@@ -4126,7 +4126,7 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>lay_roqs</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B267">
         <v>1</v>
@@ -4140,7 +4140,7 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>bigjota.artist</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B268">
         <v>1</v>
@@ -4154,7 +4154,7 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B269">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>mth_fernandes031</v>
+        <v>andrejetx</v>
       </c>
       <c r="B270">
         <v>1</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B271">
         <v>1</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>turmanmma</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>atlta.marc0s</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B273">
         <v>1</v>
@@ -4224,7 +4224,7 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>arturbambam</v>
+        <v>leosacraa</v>
       </c>
       <c r="B274">
         <v>1</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>hermaan10_</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B275">
         <v>1</v>
@@ -4252,7 +4252,7 @@
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>danieljsantoss_</v>
+        <v>igorfso_</v>
       </c>
       <c r="B276">
         <v>1</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>rodrigojansen_</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B277">
         <v>1</v>
@@ -4280,7 +4280,7 @@
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>markakasocks</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B278">
         <v>1</v>
@@ -4294,7 +4294,7 @@
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>hunter.mccrary</v>
+        <v>bigjota.artist</v>
       </c>
       <c r="B279">
         <v>1</v>
@@ -4308,7 +4308,7 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>omarcotomaz</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B280">
         <v>1</v>
@@ -4322,7 +4322,7 @@
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>alphavillesup</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B281">
         <v>1</v>
@@ -4336,7 +4336,7 @@
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>ricieritonan</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B282">
         <v>1</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>lucasampaio</v>
+        <v>turmanmma</v>
       </c>
       <c r="B283">
         <v>1</v>
@@ -4364,7 +4364,7 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>natalan_wilgner</v>
+        <v>atlta.marc0s</v>
       </c>
       <c r="B284">
         <v>1</v>
@@ -4378,7 +4378,7 @@
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>manmoska</v>
+        <v>arturbambam</v>
       </c>
       <c r="B285">
         <v>1</v>
@@ -4392,7 +4392,7 @@
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>renatoevangelistaa</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B286">
         <v>1</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>cassius.paula</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B287">
         <v>1</v>
@@ -4420,7 +4420,7 @@
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B288">
         <v>1</v>
@@ -4434,7 +4434,7 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>moisespira</v>
+        <v>markakasocks</v>
       </c>
       <c r="B289">
         <v>1</v>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>rodrigolidiosales</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -4462,7 +4462,7 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B291">
         <v>1</v>
@@ -4476,7 +4476,7 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>marciocatenacci</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B292">
         <v>1</v>
@@ -4490,7 +4490,7 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>cristiane.c.santana</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B293">
         <v>1</v>
@@ -4504,7 +4504,7 @@
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>ariel_alvees</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B294">
         <v>1</v>
@@ -4518,7 +4518,7 @@
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>flahvinhotreinador</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B295">
         <v>1</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>marcos.jordao.bjj</v>
+        <v>manmoska</v>
       </c>
       <c r="B296">
         <v>1</v>
@@ -4546,7 +4546,7 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>selma.oscar12</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B297">
         <v>1</v>
@@ -4560,7 +4560,7 @@
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>romulobelarmino</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B298">
         <v>1</v>
@@ -4574,7 +4574,7 @@
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>fernandamourabjj</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B299">
         <v>1</v>
@@ -4588,7 +4588,7 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>larissamartinsbjj</v>
+        <v>moisespira</v>
       </c>
       <c r="B300">
         <v>1</v>
@@ -4602,7 +4602,7 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B301">
         <v>1</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>leitefelippez</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B302">
         <v>1</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>israelbahiensebraz</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B303">
         <v>1</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>joselia_1980</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B304">
         <v>1</v>
@@ -4658,7 +4658,7 @@
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>soniarochaco</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B305">
         <v>1</v>
@@ -4672,7 +4672,7 @@
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>leandro_pedro7</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B306">
         <v>1</v>
@@ -4686,7 +4686,7 @@
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>camillinhamma</v>
+        <v>marcos.jordao.bjj</v>
       </c>
       <c r="B307">
         <v>1</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>martins.rauanee</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B308">
         <v>1</v>
@@ -4714,7 +4714,7 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>ever.soulson</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B309">
         <v>1</v>
@@ -4728,7 +4728,7 @@
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>mestrevascobento</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B310">
         <v>1</v>
@@ -4742,7 +4742,7 @@
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B311">
         <v>1</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B312">
         <v>1</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>santos39roger</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B313">
         <v>1</v>
@@ -4784,27 +4784,27 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>macamariotti</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B314">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C314">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D314">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>marinealcausa</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B315">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C315">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D315">
         <v>0</v>
@@ -4812,13 +4812,13 @@
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>emersonriosmma</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B316">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C316">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D316">
         <v>0</v>
@@ -4826,55 +4826,55 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>luizcosta_mma</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B317">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C317">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D317">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>giulia.fasolato</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B318">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C318">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D318">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>brodschack_</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B319">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C319">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D319">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>michelle_mirele</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B320">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C320">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D320">
         <v>0</v>
@@ -4882,13 +4882,13 @@
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>danielfranzesilva</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B321">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C321">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D321">
         <v>0</v>
@@ -4896,83 +4896,83 @@
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>ednilsonkaicai</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B322">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C322">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D322">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>dayanaa1511</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B323">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C323">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D323">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>ommariotti</v>
+        <v>santos39roger</v>
       </c>
       <c r="B324">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C324">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D324">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>guerreirammaofc</v>
+        <v>ricardosousa811</v>
       </c>
       <c r="B325">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C325">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D325">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>pedro_giraldi</v>
+        <v>ludelmaraujo</v>
       </c>
       <c r="B326">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C326">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D326">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>homemdeita</v>
       </c>
       <c r="B327">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C327">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D327">
         <v>0</v>
@@ -4980,49 +4980,49 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>vanessamelomma</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B328">
         <v>0</v>
       </c>
       <c r="C328">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D328">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>leonardopateira</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B329">
         <v>0</v>
       </c>
       <c r="C329">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D329">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>rahikikhalid</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B330">
         <v>0</v>
       </c>
       <c r="C330">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D330">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>manumito.oficial</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B331">
         <v>0</v>
@@ -5031,12 +5031,12 @@
         <v>2</v>
       </c>
       <c r="D331">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>carlosnoelblack</v>
+        <v>brodschack_</v>
       </c>
       <c r="B332">
         <v>0</v>
@@ -5045,18 +5045,18 @@
         <v>2</v>
       </c>
       <c r="D332">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B333">
         <v>0</v>
       </c>
       <c r="C333">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D333">
         <v>0</v>
@@ -5064,27 +5064,27 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>lokomemo_protetores</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B334">
         <v>0</v>
       </c>
       <c r="C334">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D334">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>coutz11</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B335">
         <v>0</v>
       </c>
       <c r="C335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D335">
         <v>1</v>
@@ -5092,7 +5092,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>orlando_alfa09</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B336">
         <v>0</v>
@@ -5101,12 +5101,12 @@
         <v>2</v>
       </c>
       <c r="D336">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>vitorshowman</v>
+        <v>ommariotti</v>
       </c>
       <c r="B337">
         <v>0</v>
@@ -5115,12 +5115,12 @@
         <v>2</v>
       </c>
       <c r="D337">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>4lissson</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B338">
         <v>0</v>
@@ -5129,18 +5129,18 @@
         <v>2</v>
       </c>
       <c r="D338">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>danilofernandescf</v>
+        <v>pedro_giraldi</v>
       </c>
       <c r="B339">
         <v>0</v>
       </c>
       <c r="C339">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D339">
         <v>1</v>
@@ -5148,21 +5148,21 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>bryandazuera</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B340">
         <v>0</v>
       </c>
       <c r="C340">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D340">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>_vpft</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B341">
         <v>0</v>
@@ -5176,7 +5176,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>izabeldelfino_</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B342">
         <v>0</v>
@@ -5190,7 +5190,7 @@
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>janjaovix</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B343">
         <v>0</v>
@@ -5204,49 +5204,49 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B344">
         <v>0</v>
       </c>
       <c r="C344">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D344">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>edsonbahienseb</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B345">
         <v>0</v>
       </c>
       <c r="C345">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D345">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B346">
         <v>0</v>
       </c>
       <c r="C346">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D346">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>peacegrappler_archive</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>paulomartins.mma</v>
+        <v>coutz11</v>
       </c>
       <c r="B348">
         <v>0</v>
@@ -5274,13 +5274,13 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B349">
         <v>0</v>
       </c>
       <c r="C349">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D349">
         <v>0</v>
@@ -5288,13 +5288,13 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>helenaseveribjj</v>
+        <v>couragemma</v>
       </c>
       <c r="B350">
         <v>0</v>
       </c>
       <c r="C350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D350">
         <v>0</v>
@@ -5302,13 +5302,13 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>_kainanlima</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B351">
         <v>0</v>
       </c>
       <c r="C351">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D351">
         <v>0</v>
@@ -5316,13 +5316,13 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>jimmy_indioap</v>
+        <v>4lissson</v>
       </c>
       <c r="B352">
         <v>0</v>
       </c>
       <c r="C352">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D352">
         <v>0</v>
@@ -5330,7 +5330,7 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>omar_alneaimi</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B353">
         <v>0</v>
@@ -5339,12 +5339,12 @@
         <v>1</v>
       </c>
       <c r="D353">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>victor_brunopersonal</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B354">
         <v>0</v>
@@ -5353,12 +5353,12 @@
         <v>1</v>
       </c>
       <c r="D354">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>motumbo_team</v>
+        <v>_vpft</v>
       </c>
       <c r="B355">
         <v>0</v>
@@ -5367,12 +5367,12 @@
         <v>1</v>
       </c>
       <c r="D355">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>vanemessina</v>
+        <v>izabeldelfino_</v>
       </c>
       <c r="B356">
         <v>0</v>
@@ -5381,12 +5381,12 @@
         <v>1</v>
       </c>
       <c r="D356">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>dadwillians</v>
+        <v>janjaovix</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -5395,12 +5395,12 @@
         <v>1</v>
       </c>
       <c r="D357">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>thalytabjj</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -5409,12 +5409,12 @@
         <v>1</v>
       </c>
       <c r="D358">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>esteticaluharruda</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B359">
         <v>0</v>
@@ -5423,12 +5423,12 @@
         <v>1</v>
       </c>
       <c r="D359">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>chubotaru_lilu</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B360">
         <v>0</v>
@@ -5437,12 +5437,12 @@
         <v>1</v>
       </c>
       <c r="D360">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>eusoufernandosaito</v>
+        <v>peacegrappler_archive</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -5451,12 +5451,12 @@
         <v>1</v>
       </c>
       <c r="D361">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>dandraco_</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -5465,12 +5465,12 @@
         <v>1</v>
       </c>
       <c r="D362">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>dhuks11</v>
       </c>
       <c r="B363">
         <v>0</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>sejamotivadorofc</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B364">
         <v>0</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>tpapereira</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B365">
         <v>0</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>kfcampeoes</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B366">
         <v>0</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>herrickmarinho</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B367">
         <v>0</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>rafaelcmjj</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B368">
         <v>0</v>
@@ -5554,7 +5554,7 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>cristianomarcello</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B369">
         <v>0</v>
@@ -5568,7 +5568,7 @@
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>_gabrielpego</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B370">
         <v>0</v>
@@ -5582,7 +5582,7 @@
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>taylor_71kg</v>
+        <v>vanemessina</v>
       </c>
       <c r="B371">
         <v>0</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>dadwillians</v>
       </c>
       <c r="B372">
         <v>0</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>doraasivla</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B373">
         <v>0</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>pe.mirandas</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B374">
         <v>0</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>leaoanaalice</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B375">
         <v>0</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>caioparangole</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B376">
         <v>0</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>sabrinaalsilva</v>
+        <v>dandraco_</v>
       </c>
       <c r="B377">
         <v>0</v>
@@ -5680,7 +5680,7 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B378">
         <v>0</v>
@@ -5694,7 +5694,7 @@
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>eglaudiomma</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B379">
         <v>0</v>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>strong_stg_oficial</v>
+        <v>tpapereira</v>
       </c>
       <c r="B380">
         <v>0</v>
@@ -5722,7 +5722,7 @@
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>ricardotofanello</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B381">
         <v>0</v>
@@ -5736,7 +5736,7 @@
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>taporondebruno</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B382">
         <v>0</v>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>anamatias.m</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B383">
         <v>0</v>
@@ -5764,7 +5764,7 @@
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>claudio_marchese_7</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B384">
         <v>0</v>
@@ -5778,7 +5778,7 @@
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>1000ton_n</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B385">
         <v>0</v>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>paulo.titoo</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B386">
         <v>0</v>
@@ -5806,7 +5806,7 @@
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>vitorcosta_mma</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B387">
         <v>0</v>
@@ -5820,7 +5820,7 @@
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>couragemma</v>
+        <v>doraasivla</v>
       </c>
       <c r="B388">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>romulerasilva</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B389">
         <v>0</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>edergama.mma</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B390">
         <v>0</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>alineanne_</v>
+        <v>caioparangole</v>
       </c>
       <c r="B391">
         <v>0</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>julckreis</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B392">
         <v>0</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>andreza.thais.1</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B393">
         <v>0</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>benicius_edu</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B394">
         <v>0</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B395">
         <v>0</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>michele_mixa</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B396">
         <v>0</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>joaolauar_</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B397">
         <v>0</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>igorbrasileiro01</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B398">
         <v>0</v>
@@ -5974,7 +5974,7 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>felipeocalmon</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B399">
         <v>0</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>rejr_mma</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B400">
         <v>0</v>
@@ -6002,7 +6002,7 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>deivssonmanin</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B401">
         <v>0</v>
@@ -6016,7 +6016,7 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>andrey_m_s_</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B402">
         <v>0</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>vidaldanin</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B403">
         <v>0</v>
@@ -6044,7 +6044,7 @@
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>barbaracontadora</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B404">
         <v>0</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>natalves5</v>
+        <v>alineanne_</v>
       </c>
       <c r="B405">
         <v>0</v>
@@ -6072,7 +6072,7 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>julckreis</v>
       </c>
       <c r="B406">
         <v>0</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>boradepodcastoficial</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B407">
         <v>0</v>
@@ -6100,7 +6100,7 @@
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>audizioandrade</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B408">
         <v>0</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>isadoragolimpio</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B409">
         <v>0</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>dudu.acabamentos</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B410">
         <v>0</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>katlembrenda</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B411">
         <v>0</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>aline.amaral21</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B412">
         <v>0</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>tamysregina</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B413">
         <v>0</v>
@@ -6184,7 +6184,7 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>guilhermews1994</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B414">
         <v>0</v>
@@ -6198,7 +6198,7 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>percepcar</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B415">
         <v>0</v>
@@ -6212,7 +6212,7 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>kevin.mota95</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B416">
         <v>0</v>
@@ -6226,7 +6226,7 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>_marcos_.71</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B417">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>douglas_vitor8</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B418">
         <v>0</v>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>natalves5</v>
       </c>
       <c r="B419">
         <v>0</v>
@@ -6268,7 +6268,7 @@
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>raulcarvalho1010</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B420">
         <v>0</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>roginbrito</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B421">
         <v>0</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>meirelesmma</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B422">
         <v>0</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>dvlucc2k26_</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B423">
         <v>0</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>armysenju</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B424">
         <v>0</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>f.ostini</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B425">
         <v>0</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>fher.nando_</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B426">
         <v>0</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>tamysregina</v>
       </c>
       <c r="B427">
         <v>0</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>bastazinifilho</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B428">
         <v>0</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>pammygaryo</v>
+        <v>percepcar</v>
       </c>
       <c r="B429">
         <v>0</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>anselmo.azevedo</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B430">
         <v>0</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>marcotulio_matuto</v>
+        <v>_marcos_.71</v>
       </c>
       <c r="B431">
         <v>0</v>
@@ -6436,7 +6436,7 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>ianrochaf</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B432">
         <v>0</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>ale.lagonegro</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B433">
         <v>0</v>
@@ -6464,7 +6464,7 @@
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>ganemfelipe</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B434">
         <v>0</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>marcusvgsz</v>
+        <v>roginbrito</v>
       </c>
       <c r="B435">
         <v>0</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>wanderson.casttro</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B436">
         <v>0</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B437">
         <v>0</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>jotapeamancio</v>
+        <v>armysenju</v>
       </c>
       <c r="B438">
         <v>0</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>f.ostini</v>
       </c>
       <c r="B439">
         <v>0</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B440">
         <v>0</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>zeferinomma</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B441">
         <v>0</v>
@@ -6576,7 +6576,7 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>tavaresguu</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B442">
         <v>0</v>
@@ -6590,7 +6590,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>ildemarmarajo</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B443">
         <v>0</v>
@@ -6604,7 +6604,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>peterson_arrais</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B444">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>danieldias7s</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B445">
         <v>0</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>ohanna.anselmo</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B446">
         <v>0</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>brun_oguerreiro</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B447">
         <v>0</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>helman_mma70</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B448">
         <v>0</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>macio.almeida_89</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B449">
         <v>0</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>lyviaestherbjj</v>
+        <v>wanderson.casttro</v>
       </c>
       <c r="B450">
         <v>0</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>wendel_bjj14</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B451">
         <v>0</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>karine_killer_ufc</v>
+        <v>jotapeamancio</v>
       </c>
       <c r="B452">
         <v>0</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>andressa_bjj_</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B453">
         <v>0</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>dreamartpro</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B454">
         <v>0</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>makelele_bjj</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B455">
         <v>0</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>fdanieljj</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B456">
         <v>0</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B457">
         <v>0</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>caioleonjj</v>
+        <v>peterson_arrais</v>
       </c>
       <c r="B458">
         <v>0</v>
@@ -6814,7 +6814,7 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B459">
         <v>0</v>
@@ -6828,7 +6828,7 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>malene_elleen</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B460">
         <v>0</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>leonardoo_paixao</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B461">
         <v>0</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>josita_bjj</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B462">
         <v>0</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>roxostrike</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B463">
         <v>0</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>ruanmiqueias</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B464">
         <v>0</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>babimaciel1</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B465">
         <v>0</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>manoel.brum</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B466">
         <v>0</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>horadopower</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B467">
         <v>0</v>
@@ -6940,21 +6940,259 @@
     </row>
     <row r="468">
       <c r="A468" t="str">
+        <v>dreamartpro</v>
+      </c>
+      <c r="B468">
+        <v>0</v>
+      </c>
+      <c r="C468">
+        <v>1</v>
+      </c>
+      <c r="D468">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="str">
+        <v>makelele_bjj</v>
+      </c>
+      <c r="B469">
+        <v>0</v>
+      </c>
+      <c r="C469">
+        <v>1</v>
+      </c>
+      <c r="D469">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="str">
+        <v>fdanieljj</v>
+      </c>
+      <c r="B470">
+        <v>0</v>
+      </c>
+      <c r="C470">
+        <v>1</v>
+      </c>
+      <c r="D470">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="str">
+        <v>jeferson_tijolo1</v>
+      </c>
+      <c r="B471">
+        <v>0</v>
+      </c>
+      <c r="C471">
+        <v>1</v>
+      </c>
+      <c r="D471">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="str">
+        <v>caioleonjj</v>
+      </c>
+      <c r="B472">
+        <v>0</v>
+      </c>
+      <c r="C472">
+        <v>1</v>
+      </c>
+      <c r="D472">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="str">
+        <v>kevinlopes_bjj</v>
+      </c>
+      <c r="B473">
+        <v>0</v>
+      </c>
+      <c r="C473">
+        <v>1</v>
+      </c>
+      <c r="D473">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="str">
+        <v>malene_elleen</v>
+      </c>
+      <c r="B474">
+        <v>0</v>
+      </c>
+      <c r="C474">
+        <v>1</v>
+      </c>
+      <c r="D474">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="str">
+        <v>leonardoo_paixao</v>
+      </c>
+      <c r="B475">
+        <v>0</v>
+      </c>
+      <c r="C475">
+        <v>1</v>
+      </c>
+      <c r="D475">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="str">
+        <v>josita_bjj</v>
+      </c>
+      <c r="B476">
+        <v>0</v>
+      </c>
+      <c r="C476">
+        <v>1</v>
+      </c>
+      <c r="D476">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="str">
+        <v>roxostrike</v>
+      </c>
+      <c r="B477">
+        <v>0</v>
+      </c>
+      <c r="C477">
+        <v>1</v>
+      </c>
+      <c r="D477">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="str">
+        <v>ruanmiqueias</v>
+      </c>
+      <c r="B478">
+        <v>0</v>
+      </c>
+      <c r="C478">
+        <v>1</v>
+      </c>
+      <c r="D478">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="str">
+        <v>babimaciel1</v>
+      </c>
+      <c r="B479">
+        <v>0</v>
+      </c>
+      <c r="C479">
+        <v>1</v>
+      </c>
+      <c r="D479">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="str">
+        <v>manoel.brum</v>
+      </c>
+      <c r="B480">
+        <v>0</v>
+      </c>
+      <c r="C480">
+        <v>1</v>
+      </c>
+      <c r="D480">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="str">
+        <v>horadopower</v>
+      </c>
+      <c r="B481">
+        <v>0</v>
+      </c>
+      <c r="C481">
+        <v>1</v>
+      </c>
+      <c r="D481">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="str">
         <v>lyvia_genuina</v>
       </c>
-      <c r="B468">
-        <v>0</v>
-      </c>
-      <c r="C468">
-        <v>1</v>
-      </c>
-      <c r="D468">
+      <c r="B482">
+        <v>0</v>
+      </c>
+      <c r="C482">
+        <v>1</v>
+      </c>
+      <c r="D482">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="str">
+        <v>joseochoa.mma</v>
+      </c>
+      <c r="B483">
+        <v>0</v>
+      </c>
+      <c r="C483">
+        <v>1</v>
+      </c>
+      <c r="D483">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="str">
+        <v>daniel_natel</v>
+      </c>
+      <c r="B484">
+        <v>0</v>
+      </c>
+      <c r="C484">
+        <v>1</v>
+      </c>
+      <c r="D484">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="str">
+        <v>clayton77silva</v>
+      </c>
+      <c r="B485">
+        <v>0</v>
+      </c>
+      <c r="C485">
+        <v>1</v>
+      </c>
+      <c r="D485">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D468"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D485"/>
   </ignoredErrors>
 </worksheet>
 </file>
